--- a/excel.xlsx
+++ b/excel.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226B0D3F-F282-4AF4-8744-36769E6DEAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27890F6-7971-419F-BD48-CB530AAB839B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="13126" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="13141" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ATLETA" sheetId="2" r:id="rId1"/>
     <sheet name="SJi BW - COLLI" sheetId="3" r:id="rId2"/>
     <sheet name="FVP profile - MORIN" sheetId="7" r:id="rId3"/>
     <sheet name="TABELLE NORMATIVE" sheetId="8" r:id="rId4"/>
-    <sheet name="TAB VELOCITY" sheetId="12" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="245">
   <si>
     <t>TEST INCREMENTALE DEPTH JUMP [DJa/ DJna]</t>
   </si>
@@ -133,9 +132,6 @@
     <t>PEDANA CHRONOJUMP</t>
   </si>
   <si>
-    <t>VITRUVE</t>
-  </si>
-  <si>
     <t>Diff DX/SX</t>
   </si>
   <si>
@@ -169,12 +165,6 @@
     <t>SJi</t>
   </si>
   <si>
-    <t>GAMBA DX</t>
-  </si>
-  <si>
-    <t>GAMBA SX</t>
-  </si>
-  <si>
     <t>FVP - SQUAT [VITRUVE]</t>
   </si>
   <si>
@@ -454,9 +444,6 @@
     <t>CMJ + 6 cm</t>
   </si>
   <si>
-    <t>TIME TO PEAK VELOCITY   [TTPV] (ms)</t>
-  </si>
-  <si>
     <t>Uomo</t>
   </si>
   <si>
@@ -553,21 +540,6 @@
     <t>&lt;25,9 cm</t>
   </si>
   <si>
-    <t>% 1RM</t>
-  </si>
-  <si>
-    <t>0% 1RM</t>
-  </si>
-  <si>
-    <t>10% 1RM</t>
-  </si>
-  <si>
-    <t>20% 1RM</t>
-  </si>
-  <si>
-    <t>30% 1RM</t>
-  </si>
-  <si>
     <t>40% 1RM</t>
   </si>
   <si>
@@ -589,192 +561,6 @@
     <t>100% 1RM</t>
   </si>
   <si>
-    <t>FORZA ESPLOSIVA</t>
-  </si>
-  <si>
-    <t>FORZA DINAMICA MASSIMA</t>
-  </si>
-  <si>
-    <t>BALISTICA</t>
-  </si>
-  <si>
-    <t>???</t>
-  </si>
-  <si>
-    <t>&lt; 0.250 s</t>
-  </si>
-  <si>
-    <t>0.200 &lt; x &lt; 0.400 s</t>
-  </si>
-  <si>
-    <t>0.300 &lt; x &lt; 0.600 s</t>
-  </si>
-  <si>
-    <t>0.500 &lt; x &lt; 0.800 s</t>
-  </si>
-  <si>
-    <t>&gt; 0.750 s</t>
-  </si>
-  <si>
-    <t>VBT</t>
-  </si>
-  <si>
-    <t>STARTING STRENGTH</t>
-  </si>
-  <si>
-    <t>ABSOLUTE STRENGTH</t>
-  </si>
-  <si>
-    <t>&gt; 1.3 m/s</t>
-  </si>
-  <si>
-    <t>1.3 m/s - 1.0 m/s</t>
-  </si>
-  <si>
-    <t>1.0 m/s - 0.8 m/s</t>
-  </si>
-  <si>
-    <t>0.75 m/s - 0.5 m/s</t>
-  </si>
-  <si>
-    <t>&lt; 0.5 m/s</t>
-  </si>
-  <si>
-    <t>ESERCIZI</t>
-  </si>
-  <si>
-    <t>ZONE</t>
-  </si>
-  <si>
-    <t>% RM + VELOCITY ZONES</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>Time To Peak Velocity</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (TTPV)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ACCELERATIVE STRENGTH             </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>Forza Massima</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mean Propulsive Velocity</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>(MPV)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>Light Power Zone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                                                                                         Tutte le velocità sotto il Peak Power</t>
-    </r>
-  </si>
-  <si>
-    <t>BOSCO      COLLI</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>Heavy Power Zone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                               Le velocità tra l' 80% dell' 1RM e il Peak Power</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>Strength Zone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                                      Velocità superiore all' 80% dell' 1RM</t>
-    </r>
-  </si>
-  <si>
     <t>UOMO</t>
   </si>
   <si>
@@ -829,34 +615,9 @@
     <t>&lt;10%</t>
   </si>
   <si>
-    <t>TEST COLLI: Inizio altezza di caduta ABK + 6/10 cm e incremento l'altezza di caduta fin quando l'altezza di salto raggiunta è uguale o maggiore all'ABK. ALLENAMENTO COLLI: Cadrò dalla prima altezza non "gestita" rispetto all'ABK.</t>
-  </si>
-  <si>
     <t>BOSCO: alzo l'altezza di caduta finchè miglioro l'altezza di salto. (BEST H)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MEAN PROPULSIVE VELOCITY </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>[MPV] (m/s)</t>
-    </r>
-  </si>
-  <si>
     <t>STIMA 1RM VITRUVE</t>
   </si>
   <si>
@@ -864,62 +625,6 @@
   </si>
   <si>
     <t>1RM/BW</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Metodo degli SFORZI DINAMICI                                                                                           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>Velocity Loss 10% del carico ottimale</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SPEED - STRENGTH                    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t>Forza Dinamica Massima Bassa</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">STRENGTH - SPEED                    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Forza Dinamica Massima Alta      </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Metodo degli SFORZI MASSIMALI                       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Avenir Next LT Pro Demi"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Velocity Loss 20% del carico ottimale</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">AVG MPV a vari angoli </t>
@@ -1248,15 +953,9 @@
     <t>CMJ HALF SQUAT BL [CMJ]</t>
   </si>
   <si>
-    <t>CMJ PARALLEL SQUAT BL [CMJ] - BLOCKER</t>
-  </si>
-  <si>
     <t>CMJ OPEN SQUAT NA [ABK]</t>
   </si>
   <si>
-    <t>CMJ PARALLEL SQUAT NA [CMJ] - BLOCKER</t>
-  </si>
-  <si>
     <t>DATA TEST:</t>
   </si>
   <si>
@@ -1270,6 +969,9 @@
   </si>
   <si>
     <t>PALLEGGIATORE</t>
+  </si>
+  <si>
+    <t>TEST COLLI: Inizio altezza di caduta ABK + 6 cm e incremento l'altezza di caduta fin quando l'altezza di salto raggiunta è uguale o maggiore all'ABK. ALLENAMENTO COLLI: Cadrò dalla prima altezza non "gestita" rispetto all'ABK.</t>
   </si>
 </sst>
 </file>
@@ -1282,7 +984,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="yy\ &quot;ANNI&quot;"/>
   </numFmts>
-  <fonts count="62">
+  <fonts count="54">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
@@ -1514,48 +1216,6 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Avenir Next LT Pro Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Avenir Next LT Pro Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="0"/>
-      <name val="Avenir Next LT Pro Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color theme="0"/>
-      <name val="Avenir Next LT Pro Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Avenir Next LT Pro Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="0"/>
-      <name val="Avenir Next LT Pro Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Avenir Next LT Pro Demi"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
@@ -1659,12 +1319,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="20"/>
       <color rgb="FFFF0000"/>
@@ -1685,7 +1339,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1814,24 +1468,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEE0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="97">
+  <borders count="79">
     <border>
       <left/>
       <right/>
@@ -2431,228 +2073,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right style="thick">
-        <color theme="6" tint="0.39997558519241921"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="6" tint="0.39997558519241921"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="6" tint="0.39997558519241921"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color theme="6" tint="0.39997558519241921"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="thick">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right style="thick">
-        <color theme="6" tint="0.39997558519241921"/>
-      </right>
-      <top style="thick">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFEE0000"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFFFF00"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFFFF00"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="thick">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right style="thick">
-        <color theme="6" tint="0.39997558519241921"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="thick">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right style="thick">
-        <color theme="0"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="thick">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2755,30 +2175,6 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top style="double">
-        <color theme="0"/>
-      </top>
-      <bottom style="double">
-        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3020,7 +2416,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="406">
+  <cellXfs count="380">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3209,30 +2605,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="9" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="23" borderId="50" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="23" borderId="50" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="50" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="23" borderId="51" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="9" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="9" borderId="53" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="23" borderId="65" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3385,9 +2757,6 @@
     </xf>
     <xf numFmtId="14" fontId="14" fillId="9" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="50" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3424,13 +2793,13 @@
     <xf numFmtId="0" fontId="33" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3454,7 +2823,7 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="57" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="50" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3489,14 +2858,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="48" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="41" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3525,22 +2894,22 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="12" borderId="43" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3559,25 +2928,25 @@
     <xf numFmtId="2" fontId="32" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="31" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="31" fillId="12" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="31" fillId="12" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="31" fillId="12" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="31" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="47" fillId="12" borderId="68" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="40" fillId="12" borderId="52" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
@@ -3589,20 +2958,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="43" fillId="4" borderId="43" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="36" fillId="4" borderId="43" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="9" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3620,75 +2976,187 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="95" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="96" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="94" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="77" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="78" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="76" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="12" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="12" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="12" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="43" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="12" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="12" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3697,144 +3165,97 @@
     <xf numFmtId="1" fontId="1" fillId="4" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="12" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="2" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="12" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="2" fillId="12" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="9" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="9" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="9" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="36" fillId="4" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="36" fillId="4" borderId="61" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="45" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="43" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="43" fillId="4" borderId="78" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="43" fillId="4" borderId="79" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3862,13 +3283,13 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="9" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="9" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="9" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="9" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="9" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="9" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="21" fillId="9" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4009,10 +3430,10 @@
     <xf numFmtId="0" fontId="26" fillId="16" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="60" fillId="13" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="60" fillId="13" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="52" fillId="13" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="52" fillId="13" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="17" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4063,49 +3484,49 @@
     <xf numFmtId="0" fontId="27" fillId="16" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="88" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="70" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="89" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="71" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="90" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="72" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="91" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="73" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="92" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="74" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="9" borderId="93" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="13" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4123,117 +3544,15 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="23" borderId="59" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="51" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="50" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="50" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="23" borderId="50" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="23" borderId="51" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="23" borderId="76" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="23" borderId="77" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="50" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="50" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="51" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="59" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="23" borderId="50" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="51" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="60" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="54" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="55" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="64" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="55" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="61" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="52" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="22" borderId="56" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="23" borderId="57" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="23" borderId="55" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="51" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="50" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="23" borderId="50" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="22" borderId="50" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="22" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -7085,1403 +6404,1354 @@
   <dimension ref="A1:AB29"/>
   <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="16.05" customHeight="1"/>
   <cols>
-    <col min="1" max="28" width="11.6875" style="184" customWidth="1"/>
-    <col min="29" max="29" width="10.8125" style="184" customWidth="1"/>
-    <col min="30" max="16384" width="10.8125" style="184"/>
+    <col min="1" max="28" width="11.6875" style="175" customWidth="1"/>
+    <col min="29" max="29" width="10.8125" style="175" customWidth="1"/>
+    <col min="30" max="16384" width="10.8125" style="175"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="35" customHeight="1">
-      <c r="A1" s="202" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="228"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="228"/>
-      <c r="F1" s="264"/>
-      <c r="G1" s="240" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="263"/>
-      <c r="I1" s="240" t="s">
-        <v>127</v>
-      </c>
-      <c r="J1" s="263"/>
-      <c r="K1" s="240" t="s">
-        <v>286</v>
-      </c>
-      <c r="L1" s="263"/>
-      <c r="M1" s="205" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="245"/>
-      <c r="O1" s="245"/>
-      <c r="P1" s="245"/>
-      <c r="Q1" s="245"/>
-      <c r="R1" s="245"/>
-      <c r="S1" s="245"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="245"/>
-      <c r="V1" s="245"/>
-      <c r="W1" s="245"/>
-      <c r="X1" s="245"/>
-      <c r="Y1" s="245"/>
-      <c r="Z1" s="245"/>
-      <c r="AA1" s="245"/>
-      <c r="AB1" s="246"/>
+      <c r="A1" s="195" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="196"/>
+      <c r="C1" s="197"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="191" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="192"/>
+      <c r="I1" s="191" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="192"/>
+      <c r="K1" s="191" t="s">
+        <v>242</v>
+      </c>
+      <c r="L1" s="192"/>
+      <c r="M1" s="199" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="200"/>
+      <c r="O1" s="200"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="200"/>
+      <c r="AA1" s="200"/>
+      <c r="AB1" s="263"/>
     </row>
     <row r="2" spans="1:28" ht="35" customHeight="1">
-      <c r="A2" s="125" t="s">
-        <v>277</v>
-      </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="125" t="s">
-        <v>278</v>
-      </c>
-      <c r="D2" s="152">
+      <c r="A2" s="116" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="176"/>
+      <c r="C2" s="116" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="143">
         <f ca="1">TODAY()-B2</f>
-        <v>45960</v>
-      </c>
-      <c r="E2" s="125" t="s">
-        <v>283</v>
-      </c>
-      <c r="F2" s="153"/>
-      <c r="G2" s="228" t="s">
-        <v>203</v>
-      </c>
-      <c r="H2" s="264"/>
-      <c r="I2" s="228" t="s">
-        <v>128</v>
-      </c>
-      <c r="J2" s="264"/>
-      <c r="K2" s="404" t="s">
-        <v>287</v>
-      </c>
-      <c r="L2" s="405"/>
-      <c r="M2" s="204" t="s">
+        <v>46072</v>
+      </c>
+      <c r="E2" s="116" t="s">
+        <v>239</v>
+      </c>
+      <c r="F2" s="144"/>
+      <c r="G2" s="197" t="s">
+        <v>167</v>
+      </c>
+      <c r="H2" s="198"/>
+      <c r="I2" s="197" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="198"/>
+      <c r="K2" s="193" t="s">
+        <v>243</v>
+      </c>
+      <c r="L2" s="194"/>
+      <c r="M2" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="203"/>
-      <c r="O2" s="202" t="s">
+      <c r="N2" s="196"/>
+      <c r="O2" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="244" t="s">
+      <c r="P2" s="262" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="203"/>
-      <c r="S2" s="203"/>
-      <c r="T2" s="244" t="s">
+      <c r="Q2" s="196"/>
+      <c r="R2" s="196"/>
+      <c r="S2" s="196"/>
+      <c r="T2" s="262" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="244"/>
-      <c r="V2" s="244"/>
-      <c r="W2" s="244"/>
-      <c r="X2" s="244"/>
-      <c r="Y2" s="247" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z2" s="247"/>
-      <c r="AA2" s="247"/>
-      <c r="AB2" s="248"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="264" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z2" s="264"/>
+      <c r="AA2" s="264"/>
+      <c r="AB2" s="265"/>
     </row>
     <row r="3" spans="1:28" ht="35" customHeight="1">
-      <c r="A3" s="202" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="203"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="151" t="s">
-        <v>264</v>
-      </c>
-      <c r="E3" s="151" t="s">
-        <v>270</v>
-      </c>
-      <c r="F3" s="154"/>
-      <c r="G3" s="240" t="s">
-        <v>265</v>
-      </c>
-      <c r="H3" s="240"/>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="201"/>
-      <c r="L3" s="183"/>
-      <c r="M3" s="203"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="203"/>
-      <c r="P3" s="125" t="s">
+      <c r="A3" s="195" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="196"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="142" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" s="142" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3" s="145"/>
+      <c r="G3" s="191" t="s">
+        <v>223</v>
+      </c>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="191"/>
+      <c r="K3" s="188"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="196"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="125" t="s">
+      <c r="Q3" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="R3" s="125" t="s">
+      <c r="R3" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="S3" s="137" t="s">
+      <c r="S3" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="T3" s="125" t="s">
+      <c r="T3" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="U3" s="125" t="s">
+      <c r="U3" s="116" t="s">
         <v>10</v>
       </c>
-      <c r="V3" s="125" t="s">
+      <c r="V3" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="W3" s="137" t="s">
-        <v>123</v>
-      </c>
-      <c r="X3" s="137" t="s">
+      <c r="W3" s="128" t="s">
+        <v>120</v>
+      </c>
+      <c r="X3" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="247"/>
-      <c r="Z3" s="247"/>
-      <c r="AA3" s="247"/>
-      <c r="AB3" s="248"/>
+      <c r="Y3" s="264"/>
+      <c r="Z3" s="264"/>
+      <c r="AA3" s="264"/>
+      <c r="AB3" s="265"/>
     </row>
     <row r="4" spans="1:28" ht="35" customHeight="1">
-      <c r="A4" s="202" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="203"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="144" t="e">
+      <c r="A4" s="195" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="196"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="135" t="e">
         <f>C4/(C3/100)^2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E4" s="151" t="s">
-        <v>271</v>
-      </c>
-      <c r="F4" s="154"/>
-      <c r="G4" s="151" t="s">
-        <v>266</v>
-      </c>
-      <c r="H4" s="151" t="s">
-        <v>267</v>
-      </c>
-      <c r="I4" s="151" t="s">
-        <v>268</v>
-      </c>
-      <c r="J4" s="151" t="s">
-        <v>269</v>
-      </c>
-      <c r="K4" s="201"/>
-      <c r="L4" s="183"/>
-      <c r="M4" s="203"/>
-      <c r="N4" s="203"/>
-      <c r="O4" s="127" t="s">
+      <c r="E4" s="142" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" s="145"/>
+      <c r="G4" s="142" t="s">
+        <v>224</v>
+      </c>
+      <c r="H4" s="142" t="s">
+        <v>225</v>
+      </c>
+      <c r="I4" s="142" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" s="142" t="s">
+        <v>227</v>
+      </c>
+      <c r="K4" s="188"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="196"/>
+      <c r="N4" s="196"/>
+      <c r="O4" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="155"/>
-      <c r="Q4" s="127"/>
-      <c r="R4" s="127"/>
-      <c r="S4" s="156">
+      <c r="P4" s="146"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="147">
         <f>MAX(P4,Q4,R4)</f>
         <v>0</v>
       </c>
-      <c r="T4" s="157"/>
-      <c r="U4" s="158"/>
-      <c r="V4" s="158"/>
-      <c r="W4" s="159" t="e">
+      <c r="T4" s="148"/>
+      <c r="U4" s="149"/>
+      <c r="V4" s="149"/>
+      <c r="W4" s="150" t="e">
         <f>AVERAGE(T4,U4,V4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X4" s="160" cm="1">
+      <c r="X4" s="151" cm="1">
         <f t="array" ref="X4">MIN(T4,U4,V4)</f>
         <v>0</v>
       </c>
-      <c r="Y4" s="249" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z4" s="249"/>
-      <c r="AA4" s="249"/>
-      <c r="AB4" s="250"/>
+      <c r="Y4" s="266" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z4" s="266"/>
+      <c r="AA4" s="266"/>
+      <c r="AB4" s="267"/>
     </row>
     <row r="5" spans="1:28" ht="35" customHeight="1">
-      <c r="A5" s="202" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="186">
+      <c r="A5" s="195" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="195"/>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="177">
         <f>G5-H5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="192" t="e">
+      <c r="J5" s="179" t="e">
         <f>(G5-H5)/H5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K5" s="201"/>
-      <c r="L5" s="183"/>
-      <c r="M5" s="203"/>
-      <c r="N5" s="203"/>
-      <c r="O5" s="127" t="s">
+      <c r="K5" s="188"/>
+      <c r="L5" s="174"/>
+      <c r="M5" s="196"/>
+      <c r="N5" s="196"/>
+      <c r="O5" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="127"/>
-      <c r="Q5" s="127"/>
-      <c r="R5" s="127"/>
-      <c r="S5" s="156" cm="1">
+      <c r="P5" s="118"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="118"/>
+      <c r="S5" s="147" cm="1">
         <f t="array" ref="S5">MAX(P5,Q5,R5)</f>
         <v>0</v>
       </c>
-      <c r="T5" s="158"/>
-      <c r="U5" s="158"/>
-      <c r="V5" s="158"/>
-      <c r="W5" s="159" t="e">
+      <c r="T5" s="149"/>
+      <c r="U5" s="149"/>
+      <c r="V5" s="149"/>
+      <c r="W5" s="150" t="e">
         <f t="shared" ref="W5:W9" si="0">AVERAGE(T5,U5,V5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X5" s="160" cm="1">
+      <c r="X5" s="151" cm="1">
         <f t="array" ref="X5">MIN(T5,U5,V5)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
-      <c r="AA5" s="249"/>
-      <c r="AB5" s="251"/>
+      <c r="Y5" s="266"/>
+      <c r="Z5" s="266"/>
+      <c r="AA5" s="266"/>
+      <c r="AB5" s="268"/>
     </row>
     <row r="6" spans="1:28" ht="35" customHeight="1">
-      <c r="A6" s="202" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="202"/>
-      <c r="C6" s="202"/>
-      <c r="D6" s="202"/>
-      <c r="E6" s="126"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="187"/>
-      <c r="J6" s="187"/>
-      <c r="K6" s="201"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="203"/>
-      <c r="N6" s="203"/>
-      <c r="O6" s="127" t="s">
+      <c r="A6" s="195" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="195"/>
+      <c r="C6" s="195"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="178"/>
+      <c r="K6" s="188"/>
+      <c r="L6" s="174"/>
+      <c r="M6" s="196"/>
+      <c r="N6" s="196"/>
+      <c r="O6" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="127"/>
-      <c r="Q6" s="127"/>
-      <c r="R6" s="127"/>
-      <c r="S6" s="156" cm="1">
+      <c r="P6" s="118"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="118"/>
+      <c r="S6" s="147" cm="1">
         <f t="array" ref="S6">MAX(P6,Q6,R6)</f>
         <v>0</v>
       </c>
-      <c r="T6" s="158"/>
-      <c r="U6" s="158"/>
-      <c r="V6" s="158"/>
-      <c r="W6" s="159" t="e">
+      <c r="T6" s="149"/>
+      <c r="U6" s="149"/>
+      <c r="V6" s="149"/>
+      <c r="W6" s="150" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X6" s="160" cm="1">
+      <c r="X6" s="151" cm="1">
         <f t="array" ref="X6">MIN(T6,U6,V6)</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="249"/>
-      <c r="Z6" s="249"/>
-      <c r="AA6" s="249"/>
-      <c r="AB6" s="252"/>
+      <c r="Y6" s="266"/>
+      <c r="Z6" s="266"/>
+      <c r="AA6" s="266"/>
+      <c r="AB6" s="269"/>
     </row>
     <row r="7" spans="1:28" ht="35" customHeight="1">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="199" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="165"/>
-      <c r="M7" s="203"/>
-      <c r="N7" s="203"/>
-      <c r="O7" s="127" t="s">
+      <c r="B7" s="199"/>
+      <c r="C7" s="199"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="199"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="199"/>
+      <c r="K7" s="199"/>
+      <c r="L7" s="156"/>
+      <c r="M7" s="196"/>
+      <c r="N7" s="196"/>
+      <c r="O7" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="127"/>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="127"/>
-      <c r="S7" s="156" cm="1">
+      <c r="P7" s="118"/>
+      <c r="Q7" s="118"/>
+      <c r="R7" s="118"/>
+      <c r="S7" s="147" cm="1">
         <f t="array" ref="S7">MAX(P7,Q7,R7)</f>
         <v>0</v>
       </c>
-      <c r="T7" s="158"/>
-      <c r="U7" s="158"/>
-      <c r="V7" s="158"/>
-      <c r="W7" s="159" t="e">
+      <c r="T7" s="149"/>
+      <c r="U7" s="149"/>
+      <c r="V7" s="149"/>
+      <c r="W7" s="150" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X7" s="160" cm="1">
+      <c r="X7" s="151" cm="1">
         <f t="array" ref="X7">MIN(T7,U7,V7)</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="253" t="s">
-        <v>222</v>
-      </c>
-      <c r="Z7" s="253"/>
-      <c r="AA7" s="253"/>
-      <c r="AB7" s="254"/>
+      <c r="Y7" s="270" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z7" s="270"/>
+      <c r="AA7" s="270"/>
+      <c r="AB7" s="271"/>
     </row>
     <row r="8" spans="1:28" ht="35" customHeight="1">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="203"/>
-      <c r="C8" s="202" t="s">
+      <c r="B8" s="196"/>
+      <c r="C8" s="195" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="203"/>
-      <c r="E8" s="267"/>
-      <c r="F8" s="125" t="s">
+      <c r="D8" s="196"/>
+      <c r="E8" s="280"/>
+      <c r="F8" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="125" t="s">
+      <c r="G8" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="125" t="s">
+      <c r="H8" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="145" t="s">
+      <c r="I8" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="137" t="s">
+      <c r="J8" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="146" t="s">
-        <v>130</v>
-      </c>
-      <c r="L8" s="146"/>
-      <c r="M8" s="203"/>
-      <c r="N8" s="203"/>
-      <c r="O8" s="127" t="s">
+      <c r="K8" s="137" t="s">
+        <v>127</v>
+      </c>
+      <c r="L8" s="137"/>
+      <c r="M8" s="196"/>
+      <c r="N8" s="196"/>
+      <c r="O8" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="P8" s="127"/>
-      <c r="Q8" s="127"/>
-      <c r="R8" s="127"/>
-      <c r="S8" s="156" cm="1">
+      <c r="P8" s="118"/>
+      <c r="Q8" s="118"/>
+      <c r="R8" s="118"/>
+      <c r="S8" s="147" cm="1">
         <f t="array" ref="S8">MAX(P8,Q8,R8)</f>
         <v>0</v>
       </c>
-      <c r="T8" s="158"/>
-      <c r="U8" s="158"/>
-      <c r="V8" s="158"/>
-      <c r="W8" s="159" t="e">
+      <c r="T8" s="149"/>
+      <c r="U8" s="149"/>
+      <c r="V8" s="149"/>
+      <c r="W8" s="150" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X8" s="160" cm="1">
+      <c r="X8" s="151" cm="1">
         <f t="array" ref="X8">MIN(T8,U8,V8)</f>
         <v>0</v>
       </c>
-      <c r="Y8" s="253"/>
-      <c r="Z8" s="253"/>
-      <c r="AA8" s="253"/>
-      <c r="AB8" s="255"/>
+      <c r="Y8" s="270"/>
+      <c r="Z8" s="270"/>
+      <c r="AA8" s="270"/>
+      <c r="AB8" s="272"/>
     </row>
     <row r="9" spans="1:28" ht="35" customHeight="1">
-      <c r="A9" s="203"/>
-      <c r="B9" s="203"/>
-      <c r="C9" s="202" t="s">
-        <v>281</v>
-      </c>
-      <c r="D9" s="268"/>
-      <c r="E9" s="269"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="147" t="e" cm="1">
+      <c r="A9" s="196"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="195" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="278"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="138" t="e" cm="1">
         <f t="array" ref="I9">AVERAGE(F9,G9,H9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="148">
-        <f t="shared" ref="J9:J14" si="1">MAX(F9,G9,H9)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="149">
+      <c r="J9" s="139">
+        <f t="shared" ref="J9:J13" si="1">MAX(F9,G9,H9)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="140">
         <f>J9+6</f>
         <v>6</v>
       </c>
-      <c r="L9" s="178"/>
-      <c r="M9" s="203"/>
-      <c r="N9" s="203"/>
-      <c r="O9" s="127" t="s">
+      <c r="L9" s="169"/>
+      <c r="M9" s="196"/>
+      <c r="N9" s="196"/>
+      <c r="O9" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="127"/>
-      <c r="Q9" s="127"/>
-      <c r="R9" s="127"/>
-      <c r="S9" s="156" cm="1">
+      <c r="P9" s="118"/>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="147" cm="1">
         <f t="array" ref="S9">MAX(P9,Q9,R9)</f>
         <v>0</v>
       </c>
-      <c r="T9" s="158"/>
-      <c r="U9" s="158"/>
-      <c r="V9" s="158"/>
-      <c r="W9" s="159" t="e">
+      <c r="T9" s="149"/>
+      <c r="U9" s="149"/>
+      <c r="V9" s="149"/>
+      <c r="W9" s="150" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X9" s="160" cm="1">
+      <c r="X9" s="151" cm="1">
         <f t="array" ref="X9">MIN(T9,U9,V9)</f>
         <v>0</v>
       </c>
-      <c r="Y9" s="253"/>
-      <c r="Z9" s="253"/>
-      <c r="AA9" s="253"/>
-      <c r="AB9" s="256"/>
+      <c r="Y9" s="270"/>
+      <c r="Z9" s="270"/>
+      <c r="AA9" s="270"/>
+      <c r="AB9" s="273"/>
     </row>
     <row r="10" spans="1:28" ht="35" customHeight="1">
-      <c r="A10" s="203"/>
-      <c r="B10" s="203"/>
-      <c r="C10" s="202" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="202"/>
-      <c r="E10" s="202"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="147" t="e" cm="1">
+      <c r="A10" s="196"/>
+      <c r="B10" s="196"/>
+      <c r="C10" s="195" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="195"/>
+      <c r="E10" s="195"/>
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="138" t="e" cm="1">
         <f t="array" ref="I10">AVERAGE(F10,G10,H10)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J10" s="147">
+      <c r="J10" s="138">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K10" s="150">
+      <c r="K10" s="141">
         <f>SUM(J10,6)</f>
         <v>6</v>
       </c>
-      <c r="L10" s="179"/>
-      <c r="M10" s="166" t="s">
-        <v>212</v>
-      </c>
-      <c r="N10" s="167"/>
-      <c r="O10" s="167"/>
-      <c r="P10" s="167"/>
-      <c r="Q10" s="167"/>
-      <c r="R10" s="167"/>
-      <c r="S10" s="167"/>
-      <c r="T10" s="167"/>
-      <c r="U10" s="167"/>
-      <c r="V10" s="167"/>
-      <c r="W10" s="167"/>
-      <c r="X10" s="167"/>
-      <c r="Y10" s="167"/>
-      <c r="Z10" s="167"/>
-      <c r="AA10" s="167"/>
-      <c r="AB10" s="168"/>
+      <c r="L10" s="170"/>
+      <c r="M10" s="157" t="s">
+        <v>176</v>
+      </c>
+      <c r="N10" s="158"/>
+      <c r="O10" s="158"/>
+      <c r="P10" s="158"/>
+      <c r="Q10" s="158"/>
+      <c r="R10" s="158"/>
+      <c r="S10" s="158"/>
+      <c r="T10" s="158"/>
+      <c r="U10" s="158"/>
+      <c r="V10" s="158"/>
+      <c r="W10" s="158"/>
+      <c r="X10" s="158"/>
+      <c r="Y10" s="158"/>
+      <c r="Z10" s="158"/>
+      <c r="AA10" s="158"/>
+      <c r="AB10" s="159"/>
     </row>
     <row r="11" spans="1:28" ht="35" customHeight="1">
-      <c r="A11" s="203"/>
-      <c r="B11" s="203"/>
-      <c r="C11" s="202" t="s">
-        <v>282</v>
-      </c>
-      <c r="D11" s="202"/>
-      <c r="E11" s="202"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="147" t="e" cm="1">
-        <f t="array" ref="I11">AVERAGE(F11,G11,H11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J11" s="147">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="150">
-        <f>SUM(J11,6)</f>
-        <v>6</v>
-      </c>
-      <c r="L11" s="178"/>
-      <c r="M11" s="205" t="s">
-        <v>212</v>
-      </c>
-      <c r="N11" s="245"/>
-      <c r="O11" s="245"/>
-      <c r="P11" s="245"/>
-      <c r="Q11" s="245"/>
-      <c r="R11" s="245"/>
-      <c r="S11" s="245"/>
-      <c r="T11" s="245"/>
-      <c r="U11" s="245"/>
-      <c r="V11" s="245"/>
-      <c r="W11" s="245"/>
-      <c r="X11" s="245"/>
-      <c r="Y11" s="261"/>
-      <c r="Z11" s="261"/>
-      <c r="AA11" s="261"/>
-      <c r="AB11" s="262"/>
+      <c r="A11" s="196"/>
+      <c r="B11" s="196"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="189"/>
+      <c r="G11" s="189"/>
+      <c r="H11" s="189"/>
+      <c r="I11" s="190"/>
+      <c r="J11" s="190"/>
+      <c r="K11" s="169"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="199" t="s">
+        <v>176</v>
+      </c>
+      <c r="N11" s="200"/>
+      <c r="O11" s="200"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="200"/>
+      <c r="S11" s="200"/>
+      <c r="T11" s="200"/>
+      <c r="U11" s="200"/>
+      <c r="V11" s="200"/>
+      <c r="W11" s="200"/>
+      <c r="X11" s="200"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
+      <c r="AA11" s="253"/>
+      <c r="AB11" s="254"/>
     </row>
     <row r="12" spans="1:28" ht="35" customHeight="1">
-      <c r="A12" s="203"/>
-      <c r="B12" s="203"/>
-      <c r="C12" s="202" t="s">
-        <v>210</v>
-      </c>
-      <c r="D12" s="268"/>
-      <c r="E12" s="269"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="147" t="e" cm="1">
+      <c r="A12" s="196"/>
+      <c r="B12" s="196"/>
+      <c r="C12" s="195" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="278"/>
+      <c r="E12" s="279"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="138" t="e" cm="1">
         <f t="array" ref="I12">AVERAGE(F12,G12,H12)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J12" s="148">
+      <c r="J12" s="139">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="149">
+      <c r="K12" s="140">
         <f>J12+6</f>
         <v>6</v>
       </c>
-      <c r="L12" s="179"/>
-      <c r="M12" s="235" t="s">
+      <c r="L12" s="170"/>
+      <c r="M12" s="201" t="s">
         <v>1</v>
       </c>
-      <c r="N12" s="236"/>
-      <c r="O12" s="207" t="s">
+      <c r="N12" s="202"/>
+      <c r="O12" s="218" t="s">
         <v>23</v>
       </c>
-      <c r="P12" s="208"/>
-      <c r="Q12" s="208"/>
-      <c r="R12" s="208"/>
-      <c r="S12" s="208"/>
-      <c r="T12" s="208"/>
-      <c r="U12" s="208"/>
-      <c r="V12" s="208"/>
-      <c r="W12" s="208"/>
-      <c r="X12" s="209"/>
-      <c r="Y12" s="210" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z12" s="210"/>
-      <c r="AA12" s="210"/>
-      <c r="AB12" s="210"/>
+      <c r="P12" s="219"/>
+      <c r="Q12" s="219"/>
+      <c r="R12" s="219"/>
+      <c r="S12" s="219"/>
+      <c r="T12" s="219"/>
+      <c r="U12" s="219"/>
+      <c r="V12" s="219"/>
+      <c r="W12" s="219"/>
+      <c r="X12" s="220"/>
+      <c r="Y12" s="228"/>
+      <c r="Z12" s="229"/>
+      <c r="AA12" s="229"/>
+      <c r="AB12" s="230"/>
     </row>
     <row r="13" spans="1:28" ht="35" customHeight="1">
-      <c r="A13" s="203"/>
-      <c r="B13" s="203"/>
-      <c r="C13" s="202" t="s">
-        <v>279</v>
-      </c>
-      <c r="D13" s="202"/>
-      <c r="E13" s="202"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="147" t="e" cm="1">
+      <c r="A13" s="196"/>
+      <c r="B13" s="196"/>
+      <c r="C13" s="195" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="195"/>
+      <c r="E13" s="195"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="138" t="e" cm="1">
         <f t="array" ref="I13">AVERAGE(F13,G13,H13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="138">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="141">
         <f>SUM(J13,6)</f>
         <v>6</v>
       </c>
-      <c r="L13" s="180"/>
-      <c r="M13" s="237"/>
-      <c r="N13" s="238"/>
-      <c r="O13" s="214" t="s">
+      <c r="L13" s="171"/>
+      <c r="M13" s="203"/>
+      <c r="N13" s="204"/>
+      <c r="O13" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="P13" s="214" t="s">
+      <c r="P13" s="224" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="Q13" s="214" t="s">
+      <c r="R13" s="224" t="s">
         <v>27</v>
       </c>
-      <c r="R13" s="214" t="s">
-        <v>28</v>
-      </c>
-      <c r="S13" s="211" t="s">
+      <c r="S13" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="T13" s="212"/>
-      <c r="U13" s="212"/>
-      <c r="V13" s="212"/>
-      <c r="W13" s="212"/>
-      <c r="X13" s="213"/>
-      <c r="Y13" s="222" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z13" s="222"/>
-      <c r="AA13" s="202" t="s">
-        <v>131</v>
-      </c>
-      <c r="AB13" s="202"/>
+      <c r="T13" s="222"/>
+      <c r="U13" s="222"/>
+      <c r="V13" s="222"/>
+      <c r="W13" s="222"/>
+      <c r="X13" s="223"/>
+      <c r="Y13" s="231"/>
+      <c r="Z13" s="232"/>
+      <c r="AA13" s="232"/>
+      <c r="AB13" s="233"/>
     </row>
     <row r="14" spans="1:28" ht="35" customHeight="1">
-      <c r="A14" s="203"/>
-      <c r="B14" s="203"/>
-      <c r="C14" s="202" t="s">
-        <v>280</v>
-      </c>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="147" t="e" cm="1">
-        <f t="array" ref="I14">AVERAGE(F14,G14,H14)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J14" s="147">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="150">
-        <f>SUM(J14,6)</f>
+      <c r="A14" s="196"/>
+      <c r="B14" s="196"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="189"/>
+      <c r="G14" s="189"/>
+      <c r="H14" s="189"/>
+      <c r="I14" s="190"/>
+      <c r="J14" s="190"/>
+      <c r="K14" s="169"/>
+      <c r="L14" s="171"/>
+      <c r="M14" s="203"/>
+      <c r="N14" s="204"/>
+      <c r="O14" s="225"/>
+      <c r="P14" s="225"/>
+      <c r="Q14" s="225"/>
+      <c r="R14" s="225"/>
+      <c r="S14" s="116" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="L14" s="180"/>
-      <c r="M14" s="237"/>
-      <c r="N14" s="238"/>
-      <c r="O14" s="215"/>
-      <c r="P14" s="215"/>
-      <c r="Q14" s="215"/>
-      <c r="R14" s="215"/>
-      <c r="S14" s="125" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="125" t="s">
-        <v>6</v>
-      </c>
-      <c r="U14" s="125" t="s">
+      <c r="U14" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="V14" s="137" t="s">
+      <c r="V14" s="128" t="s">
+        <v>123</v>
+      </c>
+      <c r="W14" s="128" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="137" t="s">
         <v>126</v>
       </c>
-      <c r="W14" s="137" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="146" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y14" s="222"/>
-      <c r="Z14" s="222"/>
-      <c r="AA14" s="202"/>
-      <c r="AB14" s="202"/>
+      <c r="Y14" s="231"/>
+      <c r="Z14" s="232"/>
+      <c r="AA14" s="232"/>
+      <c r="AB14" s="233"/>
     </row>
     <row r="15" spans="1:28" ht="35" customHeight="1">
-      <c r="A15" s="203"/>
-      <c r="B15" s="203"/>
-      <c r="C15" s="202" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="147" t="e" cm="1">
+      <c r="A15" s="196"/>
+      <c r="B15" s="196"/>
+      <c r="C15" s="195" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="138" t="e" cm="1">
         <f t="array" ref="I15">AVERAGE(F15,G15,H15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J15" s="270" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="270"/>
-      <c r="L15" s="181"/>
-      <c r="M15" s="237"/>
-      <c r="N15" s="238"/>
-      <c r="O15" s="161" t="s">
-        <v>29</v>
-      </c>
-      <c r="P15" s="162">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="163">
+      <c r="J15" s="258" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="258"/>
+      <c r="L15" s="172"/>
+      <c r="M15" s="203"/>
+      <c r="N15" s="204"/>
+      <c r="O15" s="152" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="154">
         <f>C4*P15</f>
         <v>0</v>
       </c>
-      <c r="R15" s="163">
-        <v>0</v>
-      </c>
-      <c r="S15" s="127"/>
-      <c r="T15" s="127"/>
-      <c r="U15" s="127"/>
-      <c r="V15" s="156" t="e">
+      <c r="R15" s="154">
+        <v>0</v>
+      </c>
+      <c r="S15" s="118"/>
+      <c r="T15" s="118"/>
+      <c r="U15" s="118"/>
+      <c r="V15" s="147" t="e">
         <f>AVERAGE(S15,T15,U15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W15" s="164">
+      <c r="W15" s="155">
         <f>MAX(S15,T15,U15)</f>
         <v>0</v>
       </c>
-      <c r="X15" s="164">
+      <c r="X15" s="155">
         <f>SUM(W15,6)</f>
         <v>6</v>
       </c>
-      <c r="Y15" s="259"/>
-      <c r="Z15" s="260"/>
-      <c r="AA15" s="259"/>
-      <c r="AB15" s="260"/>
+      <c r="Y15" s="231"/>
+      <c r="Z15" s="232"/>
+      <c r="AA15" s="232"/>
+      <c r="AB15" s="233"/>
     </row>
     <row r="16" spans="1:28" ht="35" customHeight="1">
-      <c r="A16" s="203"/>
-      <c r="B16" s="203"/>
-      <c r="C16" s="202" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="126"/>
-      <c r="I16" s="147" t="e" cm="1">
+      <c r="A16" s="196"/>
+      <c r="B16" s="196"/>
+      <c r="C16" s="195" t="s">
+        <v>171</v>
+      </c>
+      <c r="D16" s="196"/>
+      <c r="E16" s="196"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="138" t="e" cm="1">
         <f t="array" ref="I16">AVERAGE(F16,G16,H16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J16" s="271" t="e">
+      <c r="J16" s="276" t="e">
         <f>(I15-I16)/I16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K16" s="272"/>
-      <c r="L16" s="182"/>
-      <c r="M16" s="237"/>
-      <c r="N16" s="238"/>
-      <c r="O16" s="257" t="s">
-        <v>35</v>
-      </c>
-      <c r="P16" s="162">
+      <c r="K16" s="277"/>
+      <c r="L16" s="173"/>
+      <c r="M16" s="203"/>
+      <c r="N16" s="204"/>
+      <c r="O16" s="274" t="s">
+        <v>34</v>
+      </c>
+      <c r="P16" s="153">
         <v>0.25</v>
       </c>
-      <c r="Q16" s="163">
+      <c r="Q16" s="154">
         <f>C4*P16</f>
         <v>0</v>
       </c>
-      <c r="R16" s="127"/>
-      <c r="S16" s="127"/>
-      <c r="T16" s="127"/>
-      <c r="U16" s="127"/>
-      <c r="V16" s="156" t="e">
+      <c r="R16" s="118"/>
+      <c r="S16" s="118"/>
+      <c r="T16" s="118"/>
+      <c r="U16" s="118"/>
+      <c r="V16" s="147" t="e">
         <f t="shared" ref="V16:V19" si="2">AVERAGE(S16,T16,U16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W16" s="164">
+      <c r="W16" s="155">
         <f t="shared" ref="W16" si="3">MAX(S16,T16,U16)</f>
         <v>0</v>
       </c>
-      <c r="X16" s="156">
+      <c r="X16" s="147">
         <f t="shared" ref="X16:X19" si="4">SUM(W16,6)</f>
         <v>6</v>
       </c>
-      <c r="Y16" s="259"/>
-      <c r="Z16" s="260"/>
-      <c r="AA16" s="259"/>
-      <c r="AB16" s="260"/>
+      <c r="Y16" s="231"/>
+      <c r="Z16" s="232"/>
+      <c r="AA16" s="232"/>
+      <c r="AB16" s="233"/>
     </row>
     <row r="17" spans="1:28" ht="35" customHeight="1">
-      <c r="A17" s="205" t="s">
-        <v>204</v>
-      </c>
-      <c r="B17" s="245"/>
-      <c r="C17" s="245"/>
-      <c r="D17" s="245"/>
-      <c r="E17" s="245"/>
-      <c r="F17" s="245"/>
-      <c r="G17" s="245"/>
-      <c r="H17" s="245"/>
-      <c r="I17" s="245"/>
-      <c r="J17" s="188"/>
-      <c r="K17" s="188"/>
-      <c r="L17" s="189"/>
-      <c r="M17" s="237"/>
-      <c r="N17" s="238"/>
-      <c r="O17" s="258"/>
-      <c r="P17" s="162">
+      <c r="A17" s="199" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="200"/>
+      <c r="C17" s="200"/>
+      <c r="D17" s="200"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="200"/>
+      <c r="I17" s="200"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="206"/>
+      <c r="L17" s="207"/>
+      <c r="M17" s="203"/>
+      <c r="N17" s="204"/>
+      <c r="O17" s="275"/>
+      <c r="P17" s="153">
         <v>0.5</v>
       </c>
-      <c r="Q17" s="163">
+      <c r="Q17" s="154">
         <f>C4*P17</f>
         <v>0</v>
       </c>
-      <c r="R17" s="127"/>
-      <c r="S17" s="127"/>
-      <c r="T17" s="127"/>
-      <c r="U17" s="127"/>
-      <c r="V17" s="156" t="e">
+      <c r="R17" s="118"/>
+      <c r="S17" s="118"/>
+      <c r="T17" s="118"/>
+      <c r="U17" s="118"/>
+      <c r="V17" s="147" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W17" s="164">
+      <c r="W17" s="155">
         <f>MAX(S17,T17,U17)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="156">
+      <c r="X17" s="147">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="Y17" s="216"/>
-      <c r="Z17" s="216"/>
-      <c r="AA17" s="216"/>
-      <c r="AB17" s="216"/>
+      <c r="Y17" s="231"/>
+      <c r="Z17" s="232"/>
+      <c r="AA17" s="232"/>
+      <c r="AB17" s="233"/>
     </row>
     <row r="18" spans="1:28" ht="35" customHeight="1">
-      <c r="A18" s="204" t="s">
+      <c r="A18" s="201" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="202"/>
+      <c r="C18" s="195" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="203"/>
-      <c r="C18" s="202" t="s">
+      <c r="D18" s="196"/>
+      <c r="E18" s="196"/>
+      <c r="F18" s="221" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="203"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="125" t="s">
+      <c r="G18" s="223"/>
+      <c r="H18" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="125" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="125" t="s">
+      <c r="I18" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="125" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="188"/>
-      <c r="K18" s="188"/>
-      <c r="L18" s="189"/>
-      <c r="M18" s="237"/>
-      <c r="N18" s="238"/>
-      <c r="O18" s="258"/>
-      <c r="P18" s="162">
+      <c r="J18" s="205"/>
+      <c r="K18" s="206"/>
+      <c r="L18" s="207"/>
+      <c r="M18" s="203"/>
+      <c r="N18" s="204"/>
+      <c r="O18" s="275"/>
+      <c r="P18" s="153">
         <v>0.75</v>
       </c>
-      <c r="Q18" s="163">
+      <c r="Q18" s="154">
         <f>C4*P18</f>
         <v>0</v>
       </c>
-      <c r="R18" s="127"/>
-      <c r="S18" s="127"/>
-      <c r="T18" s="127"/>
-      <c r="U18" s="127"/>
-      <c r="V18" s="156" t="e">
+      <c r="R18" s="118"/>
+      <c r="S18" s="118"/>
+      <c r="T18" s="118"/>
+      <c r="U18" s="118"/>
+      <c r="V18" s="147" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W18" s="164">
+      <c r="W18" s="155">
         <f t="shared" ref="W18:W19" si="5">MAX(S18,T18,U18)</f>
         <v>0</v>
       </c>
-      <c r="X18" s="156">
+      <c r="X18" s="147">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="Y18" s="216"/>
-      <c r="Z18" s="216"/>
-      <c r="AA18" s="216"/>
-      <c r="AB18" s="216"/>
+      <c r="Y18" s="231"/>
+      <c r="Z18" s="232"/>
+      <c r="AA18" s="232"/>
+      <c r="AB18" s="233"/>
     </row>
     <row r="19" spans="1:28" ht="35" customHeight="1">
       <c r="A19" s="203"/>
-      <c r="B19" s="203"/>
-      <c r="C19" s="202" t="s">
-        <v>205</v>
-      </c>
-      <c r="D19" s="203"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="126"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="188"/>
-      <c r="L19" s="189"/>
-      <c r="M19" s="237"/>
-      <c r="N19" s="238"/>
-      <c r="O19" s="258"/>
-      <c r="P19" s="162">
+      <c r="B19" s="204"/>
+      <c r="C19" s="195" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="196"/>
+      <c r="E19" s="196"/>
+      <c r="F19" s="378"/>
+      <c r="G19" s="379"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="205"/>
+      <c r="K19" s="206"/>
+      <c r="L19" s="207"/>
+      <c r="M19" s="203"/>
+      <c r="N19" s="204"/>
+      <c r="O19" s="275"/>
+      <c r="P19" s="153">
         <v>1</v>
       </c>
-      <c r="Q19" s="163">
+      <c r="Q19" s="154">
         <f>C4*P19</f>
         <v>0</v>
       </c>
-      <c r="R19" s="127"/>
-      <c r="S19" s="127"/>
-      <c r="T19" s="127"/>
-      <c r="U19" s="127"/>
-      <c r="V19" s="156" t="e">
+      <c r="R19" s="118"/>
+      <c r="S19" s="118"/>
+      <c r="T19" s="118"/>
+      <c r="U19" s="118"/>
+      <c r="V19" s="147" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W19" s="164">
+      <c r="W19" s="155">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X19" s="156">
+      <c r="X19" s="147">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="Y19" s="216"/>
-      <c r="Z19" s="216"/>
-      <c r="AA19" s="216"/>
-      <c r="AB19" s="216"/>
+      <c r="Y19" s="234"/>
+      <c r="Z19" s="235"/>
+      <c r="AA19" s="235"/>
+      <c r="AB19" s="236"/>
     </row>
     <row r="20" spans="1:28" ht="35" customHeight="1">
-      <c r="A20" s="203"/>
-      <c r="B20" s="203"/>
-      <c r="C20" s="202" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="203"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="188"/>
-      <c r="K20" s="188"/>
-      <c r="L20" s="189"/>
-      <c r="M20" s="169"/>
-      <c r="N20" s="170"/>
-      <c r="O20" s="171"/>
-      <c r="P20" s="172"/>
-      <c r="Q20" s="173"/>
-      <c r="R20" s="174"/>
-      <c r="S20" s="174"/>
-      <c r="T20" s="174"/>
-      <c r="U20" s="174"/>
-      <c r="V20" s="175"/>
-      <c r="W20" s="176"/>
-      <c r="X20" s="175"/>
-      <c r="Y20" s="217"/>
-      <c r="Z20" s="218"/>
-      <c r="AA20" s="242"/>
-      <c r="AB20" s="243"/>
+      <c r="A20" s="211"/>
+      <c r="B20" s="212"/>
+      <c r="C20" s="212"/>
+      <c r="D20" s="212"/>
+      <c r="E20" s="212"/>
+      <c r="F20" s="212"/>
+      <c r="G20" s="212"/>
+      <c r="H20" s="212"/>
+      <c r="I20" s="213"/>
+      <c r="J20" s="205"/>
+      <c r="K20" s="206"/>
+      <c r="L20" s="207"/>
+      <c r="M20" s="160"/>
+      <c r="N20" s="161"/>
+      <c r="O20" s="162"/>
+      <c r="P20" s="163"/>
+      <c r="Q20" s="164"/>
+      <c r="R20" s="165"/>
+      <c r="S20" s="165"/>
+      <c r="T20" s="165"/>
+      <c r="U20" s="165"/>
+      <c r="V20" s="166"/>
+      <c r="W20" s="167"/>
+      <c r="X20" s="166"/>
+      <c r="Y20" s="226"/>
+      <c r="Z20" s="227"/>
+      <c r="AA20" s="260"/>
+      <c r="AB20" s="261"/>
     </row>
     <row r="21" spans="1:28" ht="35" customHeight="1">
-      <c r="A21" s="203"/>
-      <c r="B21" s="203"/>
-      <c r="C21" s="202" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="203"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="190"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="188"/>
-      <c r="K21" s="188"/>
-      <c r="L21" s="188"/>
-      <c r="M21" s="205" t="s">
-        <v>38</v>
-      </c>
-      <c r="N21" s="205"/>
-      <c r="O21" s="205"/>
-      <c r="P21" s="205"/>
-      <c r="Q21" s="205"/>
-      <c r="R21" s="205"/>
-      <c r="S21" s="205"/>
-      <c r="T21" s="205"/>
-      <c r="U21" s="205"/>
-      <c r="V21" s="205"/>
-      <c r="W21" s="205"/>
-      <c r="X21" s="205"/>
-      <c r="Y21" s="205"/>
-      <c r="Z21" s="205"/>
-      <c r="AA21" s="205"/>
-      <c r="AB21" s="206"/>
+      <c r="A21" s="214"/>
+      <c r="B21" s="215"/>
+      <c r="C21" s="215"/>
+      <c r="D21" s="215"/>
+      <c r="E21" s="215"/>
+      <c r="F21" s="215"/>
+      <c r="G21" s="215"/>
+      <c r="H21" s="215"/>
+      <c r="I21" s="216"/>
+      <c r="J21" s="205"/>
+      <c r="K21" s="206"/>
+      <c r="L21" s="207"/>
+      <c r="M21" s="199" t="s">
+        <v>35</v>
+      </c>
+      <c r="N21" s="199"/>
+      <c r="O21" s="199"/>
+      <c r="P21" s="199"/>
+      <c r="Q21" s="199"/>
+      <c r="R21" s="199"/>
+      <c r="S21" s="199"/>
+      <c r="T21" s="199"/>
+      <c r="U21" s="199"/>
+      <c r="V21" s="199"/>
+      <c r="W21" s="199"/>
+      <c r="X21" s="199"/>
+      <c r="Y21" s="199"/>
+      <c r="Z21" s="199"/>
+      <c r="AA21" s="199"/>
+      <c r="AB21" s="217"/>
     </row>
     <row r="22" spans="1:28" ht="35" customHeight="1">
-      <c r="A22" s="265" t="s">
-        <v>248</v>
-      </c>
-      <c r="B22" s="265"/>
-      <c r="C22" s="265"/>
-      <c r="D22" s="265"/>
-      <c r="E22" s="265"/>
-      <c r="F22" s="266" t="e">
+      <c r="A22" s="237" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" s="237"/>
+      <c r="C22" s="237"/>
+      <c r="D22" s="237"/>
+      <c r="E22" s="237"/>
+      <c r="F22" s="238" t="e">
         <f>(J10-W15)/W15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="266"/>
-      <c r="H22" s="266"/>
-      <c r="I22" s="266"/>
-      <c r="J22" s="188"/>
-      <c r="K22" s="188"/>
-      <c r="L22" s="191"/>
-      <c r="M22" s="235" t="s">
-        <v>39</v>
-      </c>
-      <c r="N22" s="236"/>
-      <c r="O22" s="240" t="s">
-        <v>213</v>
-      </c>
-      <c r="P22" s="240"/>
-      <c r="Q22" s="240" t="s">
+      <c r="G22" s="238"/>
+      <c r="H22" s="238"/>
+      <c r="I22" s="238"/>
+      <c r="J22" s="205"/>
+      <c r="K22" s="206"/>
+      <c r="L22" s="207"/>
+      <c r="M22" s="201" t="s">
+        <v>36</v>
+      </c>
+      <c r="N22" s="202"/>
+      <c r="O22" s="191" t="s">
+        <v>177</v>
+      </c>
+      <c r="P22" s="191"/>
+      <c r="Q22" s="191" t="s">
+        <v>26</v>
+      </c>
+      <c r="R22" s="191"/>
+      <c r="S22" s="191" t="s">
         <v>27</v>
       </c>
-      <c r="R22" s="240"/>
-      <c r="S22" s="240" t="s">
-        <v>28</v>
-      </c>
-      <c r="T22" s="240"/>
-      <c r="U22" s="202" t="s">
-        <v>209</v>
-      </c>
-      <c r="V22" s="202"/>
-      <c r="W22" s="202"/>
-      <c r="X22" s="202"/>
-      <c r="Y22" s="202" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z22" s="202"/>
-      <c r="AA22" s="202"/>
-      <c r="AB22" s="241"/>
+      <c r="T22" s="191"/>
+      <c r="U22" s="195" t="s">
+        <v>173</v>
+      </c>
+      <c r="V22" s="195"/>
+      <c r="W22" s="195"/>
+      <c r="X22" s="195"/>
+      <c r="Y22" s="195" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z22" s="195"/>
+      <c r="AA22" s="195"/>
+      <c r="AB22" s="259"/>
     </row>
     <row r="23" spans="1:28" ht="35" customHeight="1">
-      <c r="A23" s="205" t="s">
-        <v>263</v>
-      </c>
-      <c r="B23" s="205"/>
-      <c r="C23" s="205"/>
-      <c r="D23" s="205"/>
-      <c r="E23" s="205"/>
-      <c r="F23" s="205"/>
-      <c r="G23" s="205"/>
-      <c r="H23" s="205"/>
-      <c r="I23" s="205"/>
-      <c r="J23" s="188"/>
-      <c r="K23" s="188"/>
-      <c r="L23" s="189"/>
-      <c r="M23" s="237"/>
-      <c r="N23" s="238"/>
-      <c r="O23" s="232">
+      <c r="A23" s="199" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23" s="199"/>
+      <c r="C23" s="199"/>
+      <c r="D23" s="199"/>
+      <c r="E23" s="199"/>
+      <c r="F23" s="199"/>
+      <c r="G23" s="199"/>
+      <c r="H23" s="199"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="205"/>
+      <c r="K23" s="206"/>
+      <c r="L23" s="207"/>
+      <c r="M23" s="203"/>
+      <c r="N23" s="204"/>
+      <c r="O23" s="251">
         <v>1</v>
       </c>
-      <c r="P23" s="233"/>
-      <c r="Q23" s="227">
+      <c r="P23" s="252"/>
+      <c r="Q23" s="249">
         <f>C4*O23</f>
         <v>0</v>
       </c>
-      <c r="R23" s="227"/>
-      <c r="S23" s="228"/>
-      <c r="T23" s="228"/>
-      <c r="U23" s="229"/>
-      <c r="V23" s="229"/>
-      <c r="W23" s="229"/>
-      <c r="X23" s="229"/>
-      <c r="Y23" s="230"/>
-      <c r="Z23" s="230"/>
-      <c r="AA23" s="230"/>
-      <c r="AB23" s="231"/>
+      <c r="R23" s="249"/>
+      <c r="S23" s="197"/>
+      <c r="T23" s="197"/>
+      <c r="U23" s="250"/>
+      <c r="V23" s="250"/>
+      <c r="W23" s="250"/>
+      <c r="X23" s="250"/>
+      <c r="Y23" s="241"/>
+      <c r="Z23" s="241"/>
+      <c r="AA23" s="241"/>
+      <c r="AB23" s="242"/>
     </row>
     <row r="24" spans="1:28" ht="35" customHeight="1">
-      <c r="A24" s="202" t="s">
+      <c r="A24" s="195" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="222" t="s">
+      <c r="B24" s="246" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="222"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="222"/>
-      <c r="G24" s="222"/>
-      <c r="H24" s="222"/>
-      <c r="I24" s="141"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="177"/>
-      <c r="M24" s="237"/>
-      <c r="N24" s="238"/>
-      <c r="O24" s="232">
+      <c r="C24" s="246"/>
+      <c r="D24" s="246"/>
+      <c r="E24" s="246"/>
+      <c r="F24" s="246"/>
+      <c r="G24" s="246"/>
+      <c r="H24" s="246"/>
+      <c r="I24" s="132"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="206"/>
+      <c r="L24" s="207"/>
+      <c r="M24" s="203"/>
+      <c r="N24" s="204"/>
+      <c r="O24" s="251">
         <v>1.25</v>
       </c>
-      <c r="P24" s="233"/>
-      <c r="Q24" s="227">
+      <c r="P24" s="252"/>
+      <c r="Q24" s="249">
         <f>C4*O24</f>
         <v>0</v>
       </c>
-      <c r="R24" s="227"/>
-      <c r="S24" s="228"/>
-      <c r="T24" s="228"/>
-      <c r="U24" s="229"/>
-      <c r="V24" s="229"/>
-      <c r="W24" s="229"/>
-      <c r="X24" s="229"/>
-      <c r="Y24" s="230"/>
-      <c r="Z24" s="230"/>
-      <c r="AA24" s="230"/>
-      <c r="AB24" s="231"/>
+      <c r="R24" s="249"/>
+      <c r="S24" s="197"/>
+      <c r="T24" s="197"/>
+      <c r="U24" s="250"/>
+      <c r="V24" s="250"/>
+      <c r="W24" s="250"/>
+      <c r="X24" s="250"/>
+      <c r="Y24" s="241"/>
+      <c r="Z24" s="241"/>
+      <c r="AA24" s="241"/>
+      <c r="AB24" s="242"/>
     </row>
     <row r="25" spans="1:28" ht="35" customHeight="1">
-      <c r="A25" s="203"/>
-      <c r="B25" s="125" t="s">
+      <c r="A25" s="196"/>
+      <c r="B25" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="125" t="s">
+      <c r="C25" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="125" t="s">
+      <c r="D25" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="137" t="s">
+      <c r="E25" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="137" t="s">
-        <v>272</v>
-      </c>
-      <c r="G25" s="137" t="s">
-        <v>273</v>
-      </c>
-      <c r="H25" s="137" t="s">
-        <v>274</v>
-      </c>
-      <c r="I25" s="141"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="141"/>
-      <c r="L25" s="177"/>
-      <c r="M25" s="237"/>
-      <c r="N25" s="238"/>
-      <c r="O25" s="232">
+      <c r="F25" s="128" t="s">
+        <v>230</v>
+      </c>
+      <c r="G25" s="128" t="s">
+        <v>231</v>
+      </c>
+      <c r="H25" s="128" t="s">
+        <v>232</v>
+      </c>
+      <c r="I25" s="132"/>
+      <c r="J25" s="205"/>
+      <c r="K25" s="206"/>
+      <c r="L25" s="207"/>
+      <c r="M25" s="203"/>
+      <c r="N25" s="204"/>
+      <c r="O25" s="251">
         <v>1.45</v>
       </c>
-      <c r="P25" s="233"/>
-      <c r="Q25" s="227">
+      <c r="P25" s="252"/>
+      <c r="Q25" s="249">
         <f>C4*O25</f>
         <v>0</v>
       </c>
-      <c r="R25" s="227"/>
-      <c r="S25" s="228"/>
-      <c r="T25" s="228"/>
-      <c r="U25" s="229"/>
-      <c r="V25" s="229"/>
-      <c r="W25" s="229"/>
-      <c r="X25" s="229"/>
-      <c r="Y25" s="230"/>
-      <c r="Z25" s="230"/>
-      <c r="AA25" s="230"/>
-      <c r="AB25" s="231"/>
+      <c r="R25" s="249"/>
+      <c r="S25" s="197"/>
+      <c r="T25" s="197"/>
+      <c r="U25" s="250"/>
+      <c r="V25" s="250"/>
+      <c r="W25" s="250"/>
+      <c r="X25" s="250"/>
+      <c r="Y25" s="241"/>
+      <c r="Z25" s="241"/>
+      <c r="AA25" s="241"/>
+      <c r="AB25" s="242"/>
     </row>
     <row r="26" spans="1:28" ht="35" customHeight="1">
-      <c r="A26" s="142" t="s">
-        <v>261</v>
-      </c>
-      <c r="B26" s="126"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="139">
+      <c r="A26" s="133" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="117"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="130">
         <f>MAX(D26,B26,C26)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="140">
+      <c r="F26" s="131">
         <f>E26-F3</f>
         <v>0</v>
       </c>
-      <c r="G26" s="138"/>
-      <c r="H26" s="223">
+      <c r="G26" s="129"/>
+      <c r="H26" s="247">
         <f>G27-F26</f>
         <v>0</v>
       </c>
-      <c r="I26" s="141"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="141"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="237"/>
-      <c r="N26" s="238"/>
-      <c r="O26" s="232">
+      <c r="I26" s="132"/>
+      <c r="J26" s="205"/>
+      <c r="K26" s="206"/>
+      <c r="L26" s="207"/>
+      <c r="M26" s="203"/>
+      <c r="N26" s="204"/>
+      <c r="O26" s="251">
         <v>1.65</v>
       </c>
-      <c r="P26" s="233"/>
-      <c r="Q26" s="227">
+      <c r="P26" s="252"/>
+      <c r="Q26" s="249">
         <f>C4*O26</f>
         <v>0</v>
       </c>
-      <c r="R26" s="227"/>
-      <c r="S26" s="228"/>
-      <c r="T26" s="228"/>
-      <c r="U26" s="229"/>
-      <c r="V26" s="229"/>
-      <c r="W26" s="229"/>
-      <c r="X26" s="229"/>
-      <c r="Y26" s="230"/>
-      <c r="Z26" s="230"/>
-      <c r="AA26" s="230"/>
-      <c r="AB26" s="231"/>
+      <c r="R26" s="249"/>
+      <c r="S26" s="197"/>
+      <c r="T26" s="197"/>
+      <c r="U26" s="250"/>
+      <c r="V26" s="250"/>
+      <c r="W26" s="250"/>
+      <c r="X26" s="250"/>
+      <c r="Y26" s="241"/>
+      <c r="Z26" s="241"/>
+      <c r="AA26" s="241"/>
+      <c r="AB26" s="242"/>
     </row>
     <row r="27" spans="1:28" ht="35" customHeight="1">
-      <c r="A27" s="142" t="s">
-        <v>262</v>
-      </c>
-      <c r="B27" s="126"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="139">
+      <c r="A27" s="133" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" s="117"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="130">
         <f>MAX(D27,B27,C27)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="138"/>
-      <c r="G27" s="140">
+      <c r="F27" s="129"/>
+      <c r="G27" s="131">
         <f>E27-F4</f>
         <v>0</v>
       </c>
-      <c r="H27" s="223"/>
-      <c r="I27" s="141"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="177"/>
-      <c r="M27" s="237"/>
-      <c r="N27" s="238"/>
-      <c r="O27" s="226">
+      <c r="H27" s="247"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="205"/>
+      <c r="K27" s="206"/>
+      <c r="L27" s="207"/>
+      <c r="M27" s="203"/>
+      <c r="N27" s="204"/>
+      <c r="O27" s="248">
         <v>1.85</v>
       </c>
-      <c r="P27" s="226"/>
-      <c r="Q27" s="227">
+      <c r="P27" s="248"/>
+      <c r="Q27" s="249">
         <f>C4*O27</f>
         <v>0</v>
       </c>
-      <c r="R27" s="227"/>
-      <c r="S27" s="228"/>
-      <c r="T27" s="228"/>
-      <c r="U27" s="229"/>
-      <c r="V27" s="229"/>
-      <c r="W27" s="229"/>
-      <c r="X27" s="229"/>
-      <c r="Y27" s="230"/>
-      <c r="Z27" s="230"/>
-      <c r="AA27" s="230"/>
-      <c r="AB27" s="231"/>
+      <c r="R27" s="249"/>
+      <c r="S27" s="197"/>
+      <c r="T27" s="197"/>
+      <c r="U27" s="250"/>
+      <c r="V27" s="250"/>
+      <c r="W27" s="250"/>
+      <c r="X27" s="250"/>
+      <c r="Y27" s="241"/>
+      <c r="Z27" s="241"/>
+      <c r="AA27" s="241"/>
+      <c r="AB27" s="242"/>
     </row>
     <row r="28" spans="1:28" ht="35" customHeight="1">
-      <c r="A28" s="138"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="141"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="141"/>
-      <c r="L28" s="177"/>
-      <c r="M28" s="237"/>
-      <c r="N28" s="238"/>
-      <c r="O28" s="234" t="s">
-        <v>224</v>
-      </c>
-      <c r="P28" s="234"/>
-      <c r="Q28" s="234"/>
-      <c r="R28" s="234"/>
-      <c r="S28" s="234"/>
-      <c r="T28" s="234"/>
-      <c r="U28" s="239"/>
-      <c r="V28" s="239"/>
-      <c r="W28" s="239"/>
-      <c r="X28" s="239"/>
-      <c r="Y28" s="234" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z28" s="234"/>
-      <c r="AA28" s="224" t="e">
+      <c r="A28" s="208"/>
+      <c r="B28" s="209"/>
+      <c r="C28" s="209"/>
+      <c r="D28" s="209"/>
+      <c r="E28" s="209"/>
+      <c r="F28" s="209"/>
+      <c r="G28" s="209"/>
+      <c r="H28" s="209"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="206"/>
+      <c r="L28" s="207"/>
+      <c r="M28" s="203"/>
+      <c r="N28" s="204"/>
+      <c r="O28" s="240" t="s">
+        <v>186</v>
+      </c>
+      <c r="P28" s="240"/>
+      <c r="Q28" s="240"/>
+      <c r="R28" s="240"/>
+      <c r="S28" s="240"/>
+      <c r="T28" s="240"/>
+      <c r="U28" s="255"/>
+      <c r="V28" s="255"/>
+      <c r="W28" s="255"/>
+      <c r="X28" s="255"/>
+      <c r="Y28" s="240" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z28" s="240"/>
+      <c r="AA28" s="256" t="e">
         <f>U28/C4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB28" s="225"/>
+      <c r="AB28" s="257"/>
     </row>
     <row r="29" spans="1:28" ht="40.049999999999997" customHeight="1">
-      <c r="A29" s="219" t="s">
-        <v>225</v>
-      </c>
-      <c r="B29" s="219"/>
-      <c r="C29" s="220" t="s">
-        <v>275</v>
-      </c>
-      <c r="D29" s="221"/>
-      <c r="E29" s="221"/>
-      <c r="F29" s="221"/>
-      <c r="G29" s="221"/>
-      <c r="H29" s="221"/>
-      <c r="I29" s="221"/>
-      <c r="J29" s="221"/>
-      <c r="K29" s="177"/>
-      <c r="L29" s="143"/>
-      <c r="M29" s="143"/>
-      <c r="N29" s="143"/>
-      <c r="O29" s="143"/>
-      <c r="P29" s="143"/>
-      <c r="Q29" s="143"/>
-      <c r="R29" s="143"/>
-      <c r="S29" s="143"/>
-      <c r="T29" s="143"/>
-      <c r="U29" s="143"/>
-      <c r="V29" s="143"/>
-      <c r="W29" s="143"/>
-      <c r="X29" s="143"/>
-      <c r="Y29" s="143"/>
-      <c r="Z29" s="143"/>
-      <c r="AA29" s="143"/>
-      <c r="AB29" s="143"/>
+      <c r="A29" s="243" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="243"/>
+      <c r="C29" s="244" t="s">
+        <v>233</v>
+      </c>
+      <c r="D29" s="245"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
+      <c r="K29" s="168"/>
+      <c r="L29" s="134"/>
+      <c r="M29" s="134"/>
+      <c r="N29" s="134"/>
+      <c r="O29" s="134"/>
+      <c r="P29" s="134"/>
+      <c r="Q29" s="134"/>
+      <c r="R29" s="134"/>
+      <c r="S29" s="134"/>
+      <c r="T29" s="134"/>
+      <c r="U29" s="134"/>
+      <c r="V29" s="134"/>
+      <c r="W29" s="134"/>
+      <c r="X29" s="134"/>
+      <c r="Y29" s="134"/>
+      <c r="Z29" s="134"/>
+      <c r="AA29" s="134"/>
+      <c r="AB29" s="134"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vr8Fnabul31OV2wuTmhIwVS2oPZU0PLcGcSF8BoRPjV2N2BUm+XRhsl3KEAkCqOP1FGwUofN2/AKCpVE2BDbFQ==" saltValue="wBZj0mPmoQyxhD3Pql0nlw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="109">
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:S2"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xI0Db0vs6PLbgpjH2/q2YhbQhWgrlk5PFCLuMDM/Fhh2L8gGcBKl8X9ceg5O8ODyl8W4qTQyved7xHS2XVKkZg==" saltValue="eKg/5yS3KNoAxn89sAE6OA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="98">
     <mergeCell ref="M1:AB1"/>
     <mergeCell ref="M2:N9"/>
     <mergeCell ref="T2:X2"/>
     <mergeCell ref="Y2:AB3"/>
     <mergeCell ref="Y4:AB6"/>
     <mergeCell ref="Y7:AB9"/>
-    <mergeCell ref="Y13:Z14"/>
-    <mergeCell ref="AA13:AB14"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="Y22:AB22"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="M12:N19"/>
     <mergeCell ref="O16:O19"/>
-    <mergeCell ref="Y15:Z15"/>
-    <mergeCell ref="Y16:Z16"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="Y18:Z18"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="C13:E13"/>
     <mergeCell ref="M11:AB11"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AA18:AB18"/>
     <mergeCell ref="M22:N28"/>
     <mergeCell ref="O28:T28"/>
     <mergeCell ref="U28:X28"/>
@@ -8497,17 +7767,6 @@
     <mergeCell ref="S22:T22"/>
     <mergeCell ref="U22:X22"/>
     <mergeCell ref="U24:X24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="Y27:AB27"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="Q23:R23"/>
     <mergeCell ref="S23:T23"/>
     <mergeCell ref="U25:X25"/>
     <mergeCell ref="U26:X26"/>
@@ -8522,37 +7781,52 @@
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:R23"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A8:B16"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
     <mergeCell ref="M21:AB21"/>
     <mergeCell ref="O12:X12"/>
-    <mergeCell ref="Y12:AB12"/>
     <mergeCell ref="S13:X13"/>
     <mergeCell ref="O13:O14"/>
     <mergeCell ref="P13:P14"/>
     <mergeCell ref="Q13:Q14"/>
     <mergeCell ref="R13:R14"/>
-    <mergeCell ref="Y19:Z19"/>
     <mergeCell ref="Y20:Z20"/>
-    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="Y12:AB19"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="J17:L28"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A20:I21"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4">
     <cfRule type="cellIs" dxfId="60" priority="50" operator="between">
@@ -8803,38 +8077,38 @@
     <col min="23" max="16384" width="8.8125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="195" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="282" t="s">
-        <v>284</v>
-      </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+    <row r="1" spans="1:21" s="182" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A1" s="290" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="291"/>
+      <c r="C1" s="291"/>
+      <c r="D1" s="291"/>
+      <c r="E1" s="291"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="181"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="181"/>
+      <c r="T1" s="181"/>
+      <c r="U1" s="181"/>
     </row>
     <row r="2" spans="1:21" ht="17" customHeight="1">
-      <c r="A2" s="197"/>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
+      <c r="A2" s="184"/>
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
       <c r="I2" s="35"/>
@@ -8915,19 +8189,19 @@
     <row r="5" spans="1:21" ht="18" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="G5" s="35"/>
       <c r="H5" s="35"/>
@@ -8970,13 +8244,13 @@
       <c r="H6" s="35"/>
       <c r="I6" s="35"/>
       <c r="J6" s="38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L6" s="39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M6" s="35"/>
       <c r="N6" s="35"/>
@@ -8984,7 +8258,7 @@
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
       <c r="R6" s="39" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="S6" s="40">
         <v>0.36199999999999999</v>
@@ -9000,20 +8274,20 @@
     <row r="7" spans="1:21" ht="18" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="35"/>
       <c r="H7" s="39" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I7" s="41" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J7" s="42">
         <v>2.7</v>
@@ -9032,7 +8306,7 @@
       <c r="P7" s="35"/>
       <c r="Q7" s="35"/>
       <c r="R7" s="39" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="S7" s="40">
         <v>0.37619047619047602</v>
@@ -9081,7 +8355,7 @@
     </row>
     <row r="9" spans="1:21" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B9" s="17" t="e" cm="1">
         <f t="array" ref="B9">C6/B6</f>
@@ -9110,7 +8384,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="J9" s="39" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
@@ -9120,7 +8394,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
       <c r="R9" s="39" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="S9" s="40">
         <v>0.35875000000000001</v>
@@ -9161,7 +8435,7 @@
       <c r="P10" s="35"/>
       <c r="Q10" s="35"/>
       <c r="R10" s="39" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="S10" s="40">
         <v>0.36</v>
@@ -9176,7 +8450,7 @@
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B11" s="21" t="e" cm="1">
         <f t="array" ref="B11">B9</f>
@@ -9200,19 +8474,19 @@
       </c>
       <c r="G11" s="45"/>
       <c r="H11" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="L11" s="39" t="s">
         <v>58</v>
-      </c>
-      <c r="J11" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="39" t="s">
-        <v>61</v>
       </c>
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
@@ -9282,19 +8556,19 @@
     <row r="14" spans="1:21" ht="18" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="F14" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G14" s="35"/>
       <c r="H14" s="36">
@@ -9885,11 +9159,11 @@
       <c r="P26" s="35"/>
       <c r="Q26" s="35"/>
       <c r="R26" s="35"/>
-      <c r="S26" s="273" t="s">
-        <v>109</v>
-      </c>
-      <c r="T26" s="274"/>
-      <c r="U26" s="275"/>
+      <c r="S26" s="281" t="s">
+        <v>106</v>
+      </c>
+      <c r="T26" s="282"/>
+      <c r="U26" s="283"/>
     </row>
     <row r="27" spans="1:21" ht="18" customHeight="1">
       <c r="A27" s="2"/>
@@ -9910,9 +9184,9 @@
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="35"/>
-      <c r="S27" s="276"/>
-      <c r="T27" s="277"/>
-      <c r="U27" s="278"/>
+      <c r="S27" s="284"/>
+      <c r="T27" s="285"/>
+      <c r="U27" s="286"/>
     </row>
     <row r="28" spans="1:21" ht="18" customHeight="1">
       <c r="A28" s="2"/>
@@ -9936,9 +9210,9 @@
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="35"/>
-      <c r="S28" s="279"/>
-      <c r="T28" s="280"/>
-      <c r="U28" s="281"/>
+      <c r="S28" s="287"/>
+      <c r="T28" s="288"/>
+      <c r="U28" s="289"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="1Jbr8KdTSj6K9CIVh8UK70VWu0L4824cYTBAGn3+DzyCEDcz4uS5/RK1yBfY4JI7AY3uV/N5I7MipUQdAC5saQ==" saltValue="mVa6stWKywVOSKkr0IHNGA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -9962,1827 +9236,1827 @@
   <dimension ref="A1:AB782"/>
   <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="13.15"/>
   <cols>
-    <col min="1" max="1" width="18.8125" style="73" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26" style="73" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.8125" style="73" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="73" customWidth="1"/>
-    <col min="5" max="5" width="10.8125" style="73" customWidth="1"/>
-    <col min="6" max="7" width="12.5" style="73" customWidth="1"/>
-    <col min="8" max="8" width="12" style="73" customWidth="1"/>
-    <col min="9" max="9" width="13.6875" style="73" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.8125" style="73"/>
-    <col min="11" max="11" width="17.1875" style="73" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.8125" style="73"/>
-    <col min="14" max="14" width="13.8125" style="73" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8125" style="73"/>
-    <col min="16" max="16" width="18.3125" style="73" bestFit="1" customWidth="1"/>
-    <col min="17" max="24" width="10.8125" style="73"/>
-    <col min="25" max="25" width="12.5" style="73" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="10.8125" style="73"/>
+    <col min="1" max="1" width="18.8125" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.8125" style="65" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="65" customWidth="1"/>
+    <col min="5" max="5" width="10.8125" style="65" customWidth="1"/>
+    <col min="6" max="7" width="12.5" style="65" customWidth="1"/>
+    <col min="8" max="8" width="12" style="65" customWidth="1"/>
+    <col min="9" max="9" width="13.6875" style="65" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.8125" style="65"/>
+    <col min="11" max="11" width="17.1875" style="65" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10.8125" style="65"/>
+    <col min="14" max="14" width="13.8125" style="65" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8125" style="65"/>
+    <col min="16" max="16" width="18.3125" style="65" bestFit="1" customWidth="1"/>
+    <col min="17" max="24" width="10.8125" style="65"/>
+    <col min="25" max="25" width="12.5" style="65" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="10.8125" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="13.5" thickBot="1">
-      <c r="A1" s="71" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="121">
+      <c r="A1" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="113">
         <f>ATLETA!F2</f>
         <v>0</v>
       </c>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="316" t="s">
-        <v>106</v>
-      </c>
-      <c r="T1" s="316"/>
-      <c r="U1" s="316"/>
-      <c r="V1" s="316"/>
-      <c r="W1" s="316"/>
-      <c r="X1" s="316"/>
-      <c r="Y1" s="316"/>
-      <c r="Z1" s="316"/>
-      <c r="AA1" s="316"/>
-      <c r="AB1" s="316"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="324" t="s">
+        <v>103</v>
+      </c>
+      <c r="T1" s="324"/>
+      <c r="U1" s="324"/>
+      <c r="V1" s="324"/>
+      <c r="W1" s="324"/>
+      <c r="X1" s="324"/>
+      <c r="Y1" s="324"/>
+      <c r="Z1" s="324"/>
+      <c r="AA1" s="324"/>
+      <c r="AB1" s="324"/>
     </row>
     <row r="2" spans="1:28" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="A2" s="75" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" s="76"/>
-      <c r="D2" s="290" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="292">
+      <c r="A2" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="68"/>
+      <c r="D2" s="298" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="300">
         <f>ATLETA!E1</f>
         <v>0</v>
       </c>
-      <c r="F2" s="293"/>
-      <c r="G2" s="296" t="s">
-        <v>103</v>
-      </c>
-      <c r="H2" s="297"/>
-      <c r="I2" s="72">
+      <c r="F2" s="301"/>
+      <c r="G2" s="304" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="305"/>
+      <c r="I2" s="64">
         <f>ATLETA!C4</f>
         <v>0</v>
       </c>
-      <c r="K2" s="349" t="s">
-        <v>285</v>
-      </c>
-      <c r="L2" s="350"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="74"/>
+      <c r="K2" s="357" t="s">
+        <v>241</v>
+      </c>
+      <c r="L2" s="358"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
+      <c r="W2" s="66"/>
+      <c r="X2" s="66"/>
+      <c r="Y2" s="66"/>
+      <c r="Z2" s="66"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="D3" s="291"/>
-      <c r="E3" s="294"/>
-      <c r="F3" s="295"/>
-      <c r="G3" s="298" t="s">
-        <v>102</v>
-      </c>
-      <c r="H3" s="299"/>
-      <c r="I3" s="78">
+      <c r="D3" s="299"/>
+      <c r="E3" s="302"/>
+      <c r="F3" s="303"/>
+      <c r="G3" s="306" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="307"/>
+      <c r="I3" s="70">
         <f>ATLETA!E5/100</f>
         <v>0</v>
       </c>
-      <c r="K3" s="351"/>
-      <c r="L3" s="352"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
-      <c r="Y3" s="74"/>
-      <c r="Z3" s="74"/>
-      <c r="AA3" s="74"/>
-      <c r="AB3" s="74"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="360"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="66"/>
+      <c r="Y3" s="66"/>
+      <c r="Z3" s="66"/>
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="66"/>
     </row>
     <row r="4" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A4" s="79"/>
-      <c r="D4" s="291" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="301">
+      <c r="A4" s="71"/>
+      <c r="D4" s="299" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="309">
         <f>ATLETA!C1</f>
         <v>0</v>
       </c>
-      <c r="F4" s="302"/>
-      <c r="G4" s="298" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="299"/>
-      <c r="I4" s="78">
+      <c r="F4" s="310"/>
+      <c r="G4" s="306" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="307"/>
+      <c r="I4" s="70">
         <f>ATLETA!E6/100</f>
         <v>0</v>
       </c>
-      <c r="K4" s="351"/>
-      <c r="L4" s="352"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="T4" s="74">
+      <c r="K4" s="359"/>
+      <c r="L4" s="360"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="T4" s="66">
         <v>30</v>
       </c>
-      <c r="U4" s="74">
+      <c r="U4" s="66">
         <f>9.81*SIN(RADIANS(T4))</f>
         <v>4.9049999999999994</v>
       </c>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="66"/>
+      <c r="Y4" s="66"/>
+      <c r="Z4" s="66"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
     </row>
     <row r="5" spans="1:28" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="A5" s="79"/>
-      <c r="D5" s="300"/>
-      <c r="E5" s="303"/>
-      <c r="F5" s="304"/>
-      <c r="G5" s="305" t="s">
-        <v>99</v>
-      </c>
-      <c r="H5" s="306"/>
-      <c r="I5" s="76">
+      <c r="A5" s="71"/>
+      <c r="D5" s="308"/>
+      <c r="E5" s="311"/>
+      <c r="F5" s="312"/>
+      <c r="G5" s="313" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="314"/>
+      <c r="I5" s="68">
         <f>I3-I4</f>
         <v>0</v>
       </c>
-      <c r="K5" s="353"/>
-      <c r="L5" s="354"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
-      <c r="W5" s="74"/>
-      <c r="X5" s="74"/>
-      <c r="Y5" s="74"/>
-      <c r="Z5" s="74"/>
-      <c r="AA5" s="74"/>
-      <c r="AB5" s="74"/>
+      <c r="K5" s="361"/>
+      <c r="L5" s="362"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="66"/>
+      <c r="U5" s="66"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="66"/>
+      <c r="X5" s="66"/>
+      <c r="Y5" s="66"/>
+      <c r="Z5" s="66"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
     </row>
     <row r="6" spans="1:28" ht="13.5" thickBot="1">
-      <c r="Q6" s="74"/>
-      <c r="R6" s="74"/>
-      <c r="S6" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="T6" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="U6" s="74" t="s">
-        <v>76</v>
-      </c>
-      <c r="V6" s="74"/>
-      <c r="W6" s="74" t="s">
+      <c r="Q6" s="66"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="X6" s="74"/>
-      <c r="Y6" s="74"/>
-      <c r="Z6" s="74" t="s">
+      <c r="T6" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="AA6" s="74" t="s">
+      <c r="U6" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="AB6" s="74"/>
+      <c r="V6" s="66"/>
+      <c r="W6" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="X6" s="66"/>
+      <c r="Y6" s="66"/>
+      <c r="Z6" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA6" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB6" s="66"/>
     </row>
     <row r="7" spans="1:28" ht="15.75">
-      <c r="A7" s="81" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="82" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="82" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="82" t="s">
+      <c r="A7" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="82" t="s">
+      <c r="B7" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="82" t="s">
+      <c r="C7" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="82" t="s">
+      <c r="D7" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="H7" s="82" t="s">
+      <c r="E7" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="82" t="s">
+      <c r="F7" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="83" t="s">
+      <c r="G7" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="K7" s="71" t="s">
+      <c r="H7" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="L7" s="84" t="e">
+      <c r="I7" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="75" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="76" t="e">
         <f>RSQ(H8:H13,I8:I13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q7" s="74"/>
-      <c r="R7" s="74"/>
-      <c r="S7" s="85" t="e">
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="77" t="e">
         <f>(-($U$4^6)*$I$5^6-18*$U$4^3*$I$5^5*$L$15^2-54*$I$5^4*$L$15^4+6*SQRT(3)*SQRT(2*$U$4^3*$I$5^9*$L$15^6+27*$I$5^8*$L$15^8))^(1/3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T7" s="86" t="e">
+      <c r="T7" s="78" t="e">
         <f>-($U$4^2/(3*$L$15))-(-($U$4^4)*$I$5^4-12*$U$4*$I$5^3*$L$15^2)/(3*$I$5^2*$L$15*$S$7)+$S$7/(3*$I$5^2*$L$15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U7" s="87" t="e">
+      <c r="U7" s="79" t="e">
         <f>L12/T7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V7" s="74"/>
-      <c r="W7" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="X7" s="74"/>
-      <c r="Y7" s="74"/>
-      <c r="Z7" s="86" t="e">
+      <c r="V7" s="66"/>
+      <c r="W7" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="X7" s="66"/>
+      <c r="Y7" s="66"/>
+      <c r="Z7" s="78" t="e">
         <f>2*SQRT(-L15*T7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA7" s="86" t="e">
+      <c r="AA7" s="78" t="e">
         <f>4*L15/Z7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB7" s="74"/>
+      <c r="AB7" s="66"/>
     </row>
     <row r="8" spans="1:28" ht="14.25">
-      <c r="A8" s="88">
+      <c r="A8" s="80">
         <f>ATLETA!P15</f>
         <v>0</v>
       </c>
-      <c r="B8" s="193">
+      <c r="B8" s="180">
         <f>ATLETA!R15</f>
         <v>0</v>
       </c>
-      <c r="C8" s="89">
+      <c r="C8" s="81">
         <f>B8+$I$2</f>
         <v>0</v>
       </c>
-      <c r="D8" s="90">
+      <c r="D8" s="82">
         <f>ATLETA!S15/100</f>
         <v>0</v>
       </c>
-      <c r="E8" s="90">
+      <c r="E8" s="82">
         <f>ATLETA!T15/100</f>
         <v>0</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="82">
         <f>ATLETA!U15/100</f>
         <v>0</v>
       </c>
-      <c r="G8" s="91">
+      <c r="G8" s="83">
         <f>MAX(D8:F8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="92" t="e">
+      <c r="H8" s="84" t="e">
         <f>C8*9.81*((G8/$I$5)+1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I8" s="93">
+      <c r="I8" s="85">
         <f>SQRT((9.81*G8)/2)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="94" t="e">
+      <c r="J8" s="86" t="e">
         <f>I8*H8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K8" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="95" t="e">
+      <c r="K8" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" s="87" t="e">
         <f>CORREL(H8:H13,I8:I13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="74"/>
-      <c r="S8" s="74"/>
-      <c r="T8" s="74"/>
-      <c r="U8" s="74"/>
-      <c r="V8" s="74"/>
-      <c r="W8" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="X8" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y8" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z8" s="74"/>
-      <c r="AA8" s="74"/>
-      <c r="AB8" s="74"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="66"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="X8" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y8" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="66"/>
+      <c r="AB8" s="66"/>
     </row>
     <row r="9" spans="1:28" ht="14.25">
-      <c r="A9" s="88">
+      <c r="A9" s="80">
         <f>ATLETA!P16</f>
         <v>0.25</v>
       </c>
-      <c r="B9" s="193">
+      <c r="B9" s="180">
         <f>ATLETA!R16</f>
         <v>0</v>
       </c>
-      <c r="C9" s="89">
+      <c r="C9" s="81">
         <f>B9+$I$2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="90">
+      <c r="D9" s="82">
         <f>ATLETA!S16/100</f>
         <v>0</v>
       </c>
-      <c r="E9" s="90">
+      <c r="E9" s="82">
         <f>ATLETA!T16/100</f>
         <v>0</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="82">
         <f>ATLETA!U16/100</f>
         <v>0</v>
       </c>
-      <c r="G9" s="91">
+      <c r="G9" s="83">
         <f>MAX(D9:F9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="92" t="e">
+      <c r="H9" s="84" t="e">
         <f>C9*9.81*((G9/$I$5)+1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="85">
         <f>SQRT((9.81*G9)/2)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="94" t="e">
+      <c r="J9" s="86" t="e">
         <f>I9*H9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K9" s="77" t="s">
-        <v>86</v>
-      </c>
-      <c r="L9" s="96" t="e">
+      <c r="K9" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="L9" s="88" t="e">
         <f>INTERCEPT(H8:H13,I8:I13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="74"/>
-      <c r="S9" s="74"/>
-      <c r="T9" s="74"/>
-      <c r="U9" s="74"/>
-      <c r="V9" s="74"/>
-      <c r="W9" s="74"/>
-      <c r="X9" s="86">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="74" t="e">
+      <c r="Q9" s="66"/>
+      <c r="R9" s="66"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="66"/>
+      <c r="U9" s="66"/>
+      <c r="V9" s="66"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="78">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="66" t="e">
         <f>($T$7*X9+$Z$7)*$I$2/I2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z9" s="74"/>
-      <c r="AA9" s="74"/>
-      <c r="AB9" s="74"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="66"/>
+      <c r="AB9" s="66"/>
     </row>
     <row r="10" spans="1:28" ht="14.25">
-      <c r="A10" s="88">
+      <c r="A10" s="80">
         <f>ATLETA!P17</f>
         <v>0.5</v>
       </c>
-      <c r="B10" s="193">
+      <c r="B10" s="180">
         <f>ATLETA!R17</f>
         <v>0</v>
       </c>
-      <c r="C10" s="89">
+      <c r="C10" s="81">
         <f>B10+$I$2</f>
         <v>0</v>
       </c>
-      <c r="D10" s="90">
+      <c r="D10" s="82">
         <f>ATLETA!S17/100</f>
         <v>0</v>
       </c>
-      <c r="E10" s="90">
+      <c r="E10" s="82">
         <f>ATLETA!T17/100</f>
         <v>0</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="82">
         <f>ATLETA!U17/100</f>
         <v>0</v>
       </c>
-      <c r="G10" s="91">
+      <c r="G10" s="83">
         <f>MAX(D10:F10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="92" t="e">
+      <c r="H10" s="84" t="e">
         <f>C10*9.81*((G10/$I$5)+1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="93">
+      <c r="I10" s="85">
         <f>SQRT((9.81*G10)/2)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="94" t="e">
+      <c r="J10" s="86" t="e">
         <f>I10*H10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K10" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="97" t="e">
+      <c r="K10" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="89" t="e">
         <f>L9/I2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q10" s="74"/>
-      <c r="R10" s="74"/>
-      <c r="S10" s="86"/>
-      <c r="T10" s="86"/>
-      <c r="U10" s="86"/>
-      <c r="V10" s="74"/>
-      <c r="W10" s="74"/>
-      <c r="X10" s="86" t="e">
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="78"/>
+      <c r="U10" s="78"/>
+      <c r="V10" s="66"/>
+      <c r="W10" s="66"/>
+      <c r="X10" s="78" t="e">
         <f>AA7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y10" s="74" t="e">
+      <c r="Y10" s="66" t="e">
         <f>($T$7*X10+$Z$7)*$I$2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z10" s="74"/>
-      <c r="AA10" s="74"/>
-      <c r="AB10" s="74"/>
+      <c r="Z10" s="66"/>
+      <c r="AA10" s="66"/>
+      <c r="AB10" s="66"/>
     </row>
     <row r="11" spans="1:28" ht="14.25">
-      <c r="A11" s="88">
+      <c r="A11" s="80">
         <f>ATLETA!P18</f>
         <v>0.75</v>
       </c>
-      <c r="B11" s="193">
+      <c r="B11" s="180">
         <f>ATLETA!R18</f>
         <v>0</v>
       </c>
-      <c r="C11" s="89">
+      <c r="C11" s="81">
         <f>B11+$I$2</f>
         <v>0</v>
       </c>
-      <c r="D11" s="90">
+      <c r="D11" s="82">
         <f>ATLETA!S18/100</f>
         <v>0</v>
       </c>
-      <c r="E11" s="90">
+      <c r="E11" s="82">
         <f>ATLETA!T18/100</f>
         <v>0</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="82">
         <f>ATLETA!U18/100</f>
         <v>0</v>
       </c>
-      <c r="G11" s="91">
+      <c r="G11" s="83">
         <f>MAX(D11:F11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="92" t="e">
+      <c r="H11" s="84" t="e">
         <f>C11*9.81*((G11/$I$5)+1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="93">
+      <c r="I11" s="85">
         <f>SQRT((9.81*G11)/2)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="94" t="e">
+      <c r="J11" s="86" t="e">
         <f>I11*H11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K11" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="L11" s="96" t="e">
+      <c r="K11" s="69" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" s="88" t="e">
         <f>SLOPE(H8:H13,I8:I13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
-      <c r="S11" s="74"/>
-      <c r="T11" s="74"/>
-      <c r="U11" s="74"/>
-      <c r="V11" s="74"/>
-      <c r="W11" s="74"/>
-      <c r="X11" s="74"/>
-      <c r="Y11" s="74"/>
-      <c r="Z11" s="74"/>
-      <c r="AA11" s="74"/>
-      <c r="AB11" s="74"/>
+      <c r="Q11" s="66"/>
+      <c r="R11" s="66"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="66"/>
+      <c r="U11" s="66"/>
+      <c r="V11" s="66"/>
+      <c r="W11" s="66"/>
+      <c r="X11" s="66"/>
+      <c r="Y11" s="66"/>
+      <c r="Z11" s="66"/>
+      <c r="AA11" s="66"/>
+      <c r="AB11" s="66"/>
     </row>
     <row r="12" spans="1:28" ht="14.25">
-      <c r="A12" s="88">
+      <c r="A12" s="80">
         <f>ATLETA!P19</f>
         <v>1</v>
       </c>
-      <c r="B12" s="193">
+      <c r="B12" s="180">
         <f>ATLETA!R19</f>
         <v>0</v>
       </c>
-      <c r="C12" s="89">
+      <c r="C12" s="81">
         <f>B12+$I$2</f>
         <v>0</v>
       </c>
-      <c r="D12" s="90">
+      <c r="D12" s="82">
         <f>ATLETA!S19/100</f>
         <v>0</v>
       </c>
-      <c r="E12" s="90">
+      <c r="E12" s="82">
         <f>ATLETA!T19/100</f>
         <v>0</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="82">
         <f>ATLETA!U19/100</f>
         <v>0</v>
       </c>
-      <c r="G12" s="91">
+      <c r="G12" s="83">
         <f>MAX(D12:F12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="92" t="e">
+      <c r="H12" s="84" t="e">
         <f>C12*9.81*((G12/$I$5)+1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I12" s="93">
+      <c r="I12" s="85">
         <f>SQRT((9.81*G12)/2)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="94" t="e">
+      <c r="J12" s="86" t="e">
         <f>I12*H12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K12" s="77" t="s">
-        <v>83</v>
-      </c>
-      <c r="L12" s="95" t="e">
+      <c r="K12" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="87" t="e">
         <f>L11/I2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="74"/>
-      <c r="S12" s="74"/>
-      <c r="T12" s="74"/>
-      <c r="U12" s="74"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="74"/>
-      <c r="X12" s="74"/>
-      <c r="Y12" s="74"/>
-      <c r="Z12" s="74"/>
-      <c r="AA12" s="74"/>
-      <c r="AB12" s="74"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="66"/>
+      <c r="S12" s="66"/>
+      <c r="T12" s="66"/>
+      <c r="U12" s="66"/>
+      <c r="V12" s="66"/>
+      <c r="W12" s="66"/>
+      <c r="X12" s="66"/>
+      <c r="Y12" s="66"/>
+      <c r="Z12" s="66"/>
+      <c r="AA12" s="66"/>
+      <c r="AB12" s="66"/>
     </row>
     <row r="13" spans="1:28" ht="14.65" thickBot="1">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="77" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" s="95" t="e">
+      <c r="A13" s="90"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="L13" s="87" t="e">
         <f>-L9/L11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="74"/>
-      <c r="S13" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="T13" s="74">
+      <c r="Q13" s="66"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="T13" s="66">
         <v>90</v>
       </c>
-      <c r="U13" s="74">
+      <c r="U13" s="66">
         <f>9.81*SIN(RADIANS(T13))</f>
         <v>9.81</v>
       </c>
-      <c r="V13" s="74"/>
-      <c r="W13" s="74"/>
-      <c r="X13" s="74"/>
-      <c r="Y13" s="74"/>
-      <c r="Z13" s="74"/>
-      <c r="AA13" s="74"/>
-      <c r="AB13" s="74"/>
+      <c r="V13" s="66"/>
+      <c r="W13" s="66"/>
+      <c r="X13" s="66"/>
+      <c r="Y13" s="66"/>
+      <c r="Z13" s="66"/>
+      <c r="AA13" s="66"/>
+      <c r="AB13" s="66"/>
     </row>
     <row r="14" spans="1:28" ht="14.25">
-      <c r="A14" s="105"/>
-      <c r="B14" s="105"/>
-      <c r="C14" s="106"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="109"/>
-      <c r="K14" s="77" t="s">
-        <v>80</v>
-      </c>
-      <c r="L14" s="96" t="e">
+      <c r="A14" s="97"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="98"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14" s="88" t="e">
         <f>(L9*L13)/4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="74"/>
-      <c r="T14" s="74"/>
-      <c r="U14" s="74"/>
-      <c r="V14" s="74"/>
-      <c r="W14" s="74"/>
-      <c r="X14" s="74"/>
-      <c r="Y14" s="74"/>
-      <c r="Z14" s="74"/>
-      <c r="AA14" s="74"/>
-      <c r="AB14" s="74"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="66"/>
+      <c r="Y14" s="66"/>
+      <c r="Z14" s="66"/>
+      <c r="AA14" s="66"/>
+      <c r="AB14" s="66"/>
     </row>
     <row r="15" spans="1:28" ht="14.65" thickBot="1">
-      <c r="A15" s="105"/>
-      <c r="B15" s="105"/>
-      <c r="C15" s="106"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="199" t="s">
-        <v>79</v>
-      </c>
-      <c r="L15" s="110" t="e">
+      <c r="A15" s="97"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="186" t="s">
+        <v>76</v>
+      </c>
+      <c r="L15" s="102" t="e">
         <f>L14/I2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="74"/>
-      <c r="S15" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="T15" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="U15" s="74" t="s">
-        <v>76</v>
-      </c>
-      <c r="V15" s="74"/>
-      <c r="W15" s="74" t="s">
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="X15" s="74"/>
-      <c r="Y15" s="74"/>
-      <c r="Z15" s="74" t="s">
+      <c r="T15" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="AA15" s="74" t="s">
+      <c r="U15" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="AB15" s="74"/>
+      <c r="V15" s="66"/>
+      <c r="W15" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="X15" s="66"/>
+      <c r="Y15" s="66"/>
+      <c r="Z15" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA15" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB15" s="66"/>
     </row>
     <row r="16" spans="1:28" ht="16.149999999999999" thickBot="1">
-      <c r="A16" s="73">
+      <c r="A16" s="65">
         <f>I2</f>
         <v>0</v>
       </c>
-      <c r="K16" s="200" t="s">
-        <v>72</v>
-      </c>
-      <c r="L16" s="198" t="e">
+      <c r="K16" s="187" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="185" t="e">
         <f>T16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="74"/>
-      <c r="S16" s="85" t="e">
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="77" t="e">
         <f>(-($U$13^6)*$I$5^6-18*$U$13^3*$I$5^5*$L$15^2-54*$I$5^4*$L$15^4+6*SQRT(3)*SQRT(2*$U$13^3*$I$5^9*$L$15^6+27*$I$5^8*$L$15^8))^(1/3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T16" s="86" t="e">
+      <c r="T16" s="78" t="e">
         <f>-($U$13^2/(3*$L$15))-(-($U$13^4)*$I$5^4-12*$U$13*$I$5^3*$L$15^2)/(3*$I$5^2*$L$15*$S$16)+$S$16/(3*$I$5^2*$L$15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U16" s="87" t="e">
+      <c r="U16" s="79" t="e">
         <f>L12/T16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V16" s="74"/>
-      <c r="W16" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="X16" s="74"/>
-      <c r="Y16" s="74"/>
-      <c r="Z16" s="86" t="e">
+      <c r="V16" s="66"/>
+      <c r="W16" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="X16" s="66"/>
+      <c r="Y16" s="66"/>
+      <c r="Z16" s="78" t="e">
         <f>2*SQRT(-L15*T16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA16" s="86" t="e">
+      <c r="AA16" s="78" t="e">
         <f>4*L15/Z16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB16" s="74"/>
+      <c r="AB16" s="66"/>
     </row>
     <row r="17" spans="4:28">
-      <c r="D17" s="307" t="str">
+      <c r="D17" s="315" t="str">
         <f>K10</f>
         <v>Fo (N/kg)</v>
       </c>
-      <c r="E17" s="308"/>
-      <c r="F17" s="311" t="e">
+      <c r="E17" s="316"/>
+      <c r="F17" s="319" t="e">
         <f>L10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="111"/>
-      <c r="K17" s="108"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="74"/>
-      <c r="S17" s="74"/>
-      <c r="T17" s="74"/>
-      <c r="U17" s="74"/>
-      <c r="V17" s="74"/>
-      <c r="W17" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="X17" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y17" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z17" s="74"/>
-      <c r="AA17" s="74"/>
-      <c r="AB17" s="74"/>
+      <c r="G17" s="103"/>
+      <c r="K17" s="100"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
+      <c r="V17" s="66"/>
+      <c r="W17" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="X17" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y17" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z17" s="66"/>
+      <c r="AA17" s="66"/>
+      <c r="AB17" s="66"/>
     </row>
     <row r="18" spans="4:28" ht="12.75" customHeight="1" thickBot="1">
-      <c r="D18" s="309"/>
-      <c r="E18" s="310"/>
-      <c r="F18" s="312"/>
-      <c r="G18" s="112"/>
-      <c r="K18" s="109"/>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="74"/>
-      <c r="S18" s="74"/>
-      <c r="T18" s="74"/>
-      <c r="U18" s="74"/>
-      <c r="V18" s="74"/>
-      <c r="W18" s="74"/>
-      <c r="X18" s="86">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="74" t="e">
+      <c r="D18" s="317"/>
+      <c r="E18" s="318"/>
+      <c r="F18" s="320"/>
+      <c r="G18" s="104"/>
+      <c r="K18" s="101"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="66"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="66"/>
+      <c r="U18" s="66"/>
+      <c r="V18" s="66"/>
+      <c r="W18" s="66"/>
+      <c r="X18" s="78">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="66" t="e">
         <f>($T$16*X18+$Z$16)*$I$2/I2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z18" s="74"/>
-      <c r="AA18" s="74"/>
-      <c r="AB18" s="74"/>
+      <c r="Z18" s="66"/>
+      <c r="AA18" s="66"/>
+      <c r="AB18" s="66"/>
     </row>
     <row r="19" spans="4:28" ht="12.75" customHeight="1">
-      <c r="D19" s="307" t="str">
+      <c r="D19" s="315" t="str">
         <f>K13</f>
         <v>Vo (m/s)</v>
       </c>
-      <c r="E19" s="308"/>
-      <c r="F19" s="314" t="e">
+      <c r="E19" s="316"/>
+      <c r="F19" s="322" t="e">
         <f>L13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="111"/>
-      <c r="K19" s="109"/>
-      <c r="L19" s="108"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="74"/>
-      <c r="S19" s="86"/>
-      <c r="T19" s="86"/>
-      <c r="U19" s="86"/>
-      <c r="V19" s="74"/>
-      <c r="W19" s="74"/>
-      <c r="X19" s="86" t="e">
+      <c r="G19" s="103"/>
+      <c r="K19" s="101"/>
+      <c r="L19" s="100"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="66"/>
+      <c r="S19" s="78"/>
+      <c r="T19" s="78"/>
+      <c r="U19" s="78"/>
+      <c r="V19" s="66"/>
+      <c r="W19" s="66"/>
+      <c r="X19" s="78" t="e">
         <f>AA16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y19" s="74" t="e">
+      <c r="Y19" s="66" t="e">
         <f>($T$16*X19+$Z$16)*$I$2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z19" s="74"/>
-      <c r="AA19" s="74"/>
-      <c r="AB19" s="74"/>
+      <c r="Z19" s="66"/>
+      <c r="AA19" s="66"/>
+      <c r="AB19" s="66"/>
     </row>
     <row r="20" spans="4:28" ht="12.75" customHeight="1" thickBot="1">
-      <c r="D20" s="289"/>
-      <c r="E20" s="313"/>
-      <c r="F20" s="287"/>
-      <c r="G20" s="80"/>
-      <c r="K20" s="108"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="74"/>
-      <c r="S20" s="74"/>
-      <c r="T20" s="74"/>
-      <c r="U20" s="74"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="74"/>
-      <c r="X20" s="74"/>
-      <c r="Y20" s="74"/>
-      <c r="Z20" s="74"/>
-      <c r="AA20" s="74"/>
-      <c r="AB20" s="74"/>
+      <c r="D20" s="297"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="72"/>
+      <c r="K20" s="100"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
+      <c r="V20" s="66"/>
+      <c r="W20" s="66"/>
+      <c r="X20" s="66"/>
+      <c r="Y20" s="66"/>
+      <c r="Z20" s="66"/>
+      <c r="AA20" s="66"/>
+      <c r="AB20" s="66"/>
     </row>
     <row r="21" spans="4:28" ht="12.75" customHeight="1">
-      <c r="D21" s="307" t="str">
+      <c r="D21" s="315" t="str">
         <f>K15</f>
         <v>Pmax (W/kg)</v>
       </c>
-      <c r="E21" s="308"/>
-      <c r="F21" s="311" t="e">
+      <c r="E21" s="316"/>
+      <c r="F21" s="319" t="e">
         <f>L15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="111"/>
-      <c r="K21" s="109"/>
-      <c r="Q21" s="74"/>
-      <c r="R21" s="74"/>
-      <c r="S21" s="74"/>
-      <c r="T21" s="74"/>
-      <c r="U21" s="74"/>
-      <c r="V21" s="74"/>
-      <c r="W21" s="74"/>
-      <c r="X21" s="74"/>
-      <c r="Y21" s="74"/>
-      <c r="Z21" s="74"/>
-      <c r="AA21" s="74"/>
-      <c r="AB21" s="74"/>
+      <c r="G21" s="103"/>
+      <c r="K21" s="101"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66"/>
+      <c r="U21" s="66"/>
+      <c r="V21" s="66"/>
+      <c r="W21" s="66"/>
+      <c r="X21" s="66"/>
+      <c r="Y21" s="66"/>
+      <c r="Z21" s="66"/>
+      <c r="AA21" s="66"/>
+      <c r="AB21" s="66"/>
     </row>
     <row r="22" spans="4:28" ht="12.75" customHeight="1" thickBot="1">
-      <c r="D22" s="289"/>
-      <c r="E22" s="313"/>
-      <c r="F22" s="315"/>
-      <c r="G22" s="80"/>
-      <c r="K22" s="107"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="74"/>
-      <c r="S22" s="74"/>
-      <c r="T22" s="74"/>
-      <c r="U22" s="74"/>
-      <c r="V22" s="74"/>
-      <c r="W22" s="74"/>
-      <c r="X22" s="74"/>
-      <c r="Y22" s="74"/>
-      <c r="Z22" s="74"/>
-      <c r="AA22" s="74"/>
-      <c r="AB22" s="74"/>
+      <c r="D22" s="297"/>
+      <c r="E22" s="321"/>
+      <c r="F22" s="323"/>
+      <c r="G22" s="72"/>
+      <c r="K22" s="99"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
     </row>
     <row r="23" spans="4:28" ht="12.75" customHeight="1">
-      <c r="D23" s="285" t="str">
+      <c r="D23" s="293" t="str">
         <f>K12</f>
         <v>Sfv (N.s/m/kg)</v>
       </c>
-      <c r="E23" s="286"/>
-      <c r="F23" s="285" t="e">
+      <c r="E23" s="294"/>
+      <c r="F23" s="293" t="e">
         <f>L12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G23" s="112"/>
-      <c r="Q23" s="74"/>
-      <c r="R23" s="74"/>
-      <c r="S23" s="74"/>
-      <c r="T23" s="74"/>
-      <c r="U23" s="74"/>
-      <c r="V23" s="74"/>
-      <c r="W23" s="74"/>
-      <c r="X23" s="113" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y23" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z23" s="74"/>
-      <c r="AA23" s="74"/>
-      <c r="AB23" s="74"/>
+      <c r="G23" s="104"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66"/>
+      <c r="V23" s="66"/>
+      <c r="W23" s="66"/>
+      <c r="X23" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y23" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z23" s="66"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="66"/>
     </row>
     <row r="24" spans="4:28" ht="13.5" thickBot="1">
-      <c r="D24" s="287"/>
-      <c r="E24" s="288"/>
-      <c r="F24" s="289"/>
-      <c r="G24" s="80"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="74"/>
-      <c r="S24" s="74"/>
-      <c r="T24" s="74"/>
-      <c r="U24" s="74"/>
-      <c r="V24" s="74"/>
-      <c r="W24" s="74"/>
-      <c r="X24" s="114">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="113" t="e">
+      <c r="D24" s="295"/>
+      <c r="E24" s="296"/>
+      <c r="F24" s="297"/>
+      <c r="G24" s="72"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="66"/>
+      <c r="U24" s="66"/>
+      <c r="V24" s="66"/>
+      <c r="W24" s="66"/>
+      <c r="X24" s="106">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="105" t="e">
         <f>L9/I2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z24" s="74"/>
-      <c r="AA24" s="74"/>
-      <c r="AB24" s="74"/>
+      <c r="Z24" s="66"/>
+      <c r="AA24" s="66"/>
+      <c r="AB24" s="66"/>
     </row>
     <row r="25" spans="4:28">
-      <c r="D25" s="115"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="327" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25" s="328"/>
-      <c r="Q25" s="74"/>
-      <c r="R25" s="74"/>
-      <c r="S25" s="74"/>
-      <c r="T25" s="74"/>
-      <c r="U25" s="74"/>
-      <c r="V25" s="74"/>
-      <c r="W25" s="74"/>
-      <c r="X25" s="86" t="e">
+      <c r="D25" s="107"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="335" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="336"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66"/>
+      <c r="U25" s="66"/>
+      <c r="V25" s="66"/>
+      <c r="W25" s="66"/>
+      <c r="X25" s="78" t="e">
         <f>L13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y25" s="74">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="74"/>
-      <c r="AA25" s="74"/>
-      <c r="AB25" s="74"/>
+      <c r="Y25" s="66">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="66"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="66"/>
     </row>
     <row r="26" spans="4:28" ht="12.75" customHeight="1">
-      <c r="D26" s="117"/>
-      <c r="F26" s="329"/>
-      <c r="G26" s="330"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="74"/>
-      <c r="S26" s="74"/>
-      <c r="T26" s="74"/>
-      <c r="U26" s="74"/>
-      <c r="V26" s="74"/>
-      <c r="W26" s="74"/>
-      <c r="X26" s="74"/>
-      <c r="Y26" s="74"/>
-      <c r="Z26" s="74"/>
-      <c r="AA26" s="74"/>
-      <c r="AB26" s="74"/>
+      <c r="D26" s="109"/>
+      <c r="F26" s="337"/>
+      <c r="G26" s="338"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
+      <c r="V26" s="66"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="66"/>
+      <c r="Y26" s="66"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="66"/>
+      <c r="AB26" s="66"/>
     </row>
     <row r="27" spans="4:28" ht="12.75" customHeight="1">
-      <c r="D27" s="117"/>
-      <c r="F27" s="331" t="e">
+      <c r="D27" s="109"/>
+      <c r="F27" s="339" t="e">
         <f>U7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G27" s="332"/>
+      <c r="G27" s="340"/>
     </row>
     <row r="28" spans="4:28" ht="12.75" customHeight="1">
-      <c r="D28" s="117"/>
-      <c r="F28" s="331"/>
-      <c r="G28" s="332"/>
+      <c r="D28" s="109"/>
+      <c r="F28" s="339"/>
+      <c r="G28" s="340"/>
     </row>
     <row r="29" spans="4:28" ht="12.75" customHeight="1">
-      <c r="D29" s="117"/>
-      <c r="F29" s="339" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" s="340"/>
+      <c r="D29" s="109"/>
+      <c r="F29" s="347" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="348"/>
     </row>
     <row r="30" spans="4:28" ht="13.5" thickBot="1">
-      <c r="D30" s="117"/>
-      <c r="F30" s="341"/>
-      <c r="G30" s="342"/>
+      <c r="D30" s="109"/>
+      <c r="F30" s="349"/>
+      <c r="G30" s="350"/>
     </row>
     <row r="31" spans="4:28">
-      <c r="D31" s="117"/>
-      <c r="F31" s="343" t="e">
+      <c r="D31" s="109"/>
+      <c r="F31" s="351" t="e">
         <f>IF(F27&lt;1,"FORCE is to be developped","VELOCITY is to be developped")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G31" s="344"/>
+      <c r="G31" s="352"/>
     </row>
     <row r="32" spans="4:28">
-      <c r="D32" s="117"/>
-      <c r="F32" s="345"/>
-      <c r="G32" s="346"/>
+      <c r="D32" s="109"/>
+      <c r="F32" s="353"/>
+      <c r="G32" s="354"/>
     </row>
     <row r="33" spans="1:7" ht="13.5" thickBot="1">
-      <c r="D33" s="118"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="347"/>
-      <c r="G33" s="348"/>
+      <c r="D33" s="110"/>
+      <c r="E33" s="111"/>
+      <c r="F33" s="355"/>
+      <c r="G33" s="356"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="D34" s="115"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="333" t="s">
-        <v>65</v>
-      </c>
-      <c r="G34" s="334"/>
+      <c r="D34" s="107"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="341" t="s">
+        <v>62</v>
+      </c>
+      <c r="G34" s="342"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="D35" s="117"/>
-      <c r="F35" s="335"/>
-      <c r="G35" s="336"/>
+      <c r="D35" s="109"/>
+      <c r="F35" s="343"/>
+      <c r="G35" s="344"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="D36" s="117"/>
-      <c r="F36" s="337" t="e">
+      <c r="D36" s="109"/>
+      <c r="F36" s="345" t="e">
         <f>U16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G36" s="338"/>
+      <c r="G36" s="346"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="D37" s="117"/>
-      <c r="F37" s="337"/>
-      <c r="G37" s="338"/>
+      <c r="D37" s="109"/>
+      <c r="F37" s="345"/>
+      <c r="G37" s="346"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="D38" s="117"/>
-      <c r="F38" s="317" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38" s="318"/>
+      <c r="D38" s="109"/>
+      <c r="F38" s="325" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="326"/>
     </row>
     <row r="39" spans="1:7" ht="13.5" thickBot="1">
-      <c r="D39" s="117"/>
-      <c r="F39" s="319"/>
-      <c r="G39" s="320"/>
+      <c r="D39" s="109"/>
+      <c r="F39" s="327"/>
+      <c r="G39" s="328"/>
     </row>
     <row r="40" spans="1:7" ht="12.75" customHeight="1">
-      <c r="D40" s="117"/>
-      <c r="F40" s="321" t="e">
+      <c r="D40" s="109"/>
+      <c r="F40" s="329" t="e">
         <f>IF(F36&lt;1,"FORCE is to be developped","VELOCITY is to be developped")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G40" s="322"/>
+      <c r="G40" s="330"/>
     </row>
     <row r="41" spans="1:7" ht="12.75" customHeight="1">
-      <c r="D41" s="117"/>
-      <c r="F41" s="323"/>
-      <c r="G41" s="324"/>
+      <c r="D41" s="109"/>
+      <c r="F41" s="331"/>
+      <c r="G41" s="332"/>
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" thickBot="1">
-      <c r="D42" s="118"/>
-      <c r="E42" s="119"/>
-      <c r="F42" s="325"/>
-      <c r="G42" s="326"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="333"/>
+      <c r="G42" s="334"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="B45" s="79"/>
+      <c r="B45" s="71"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="120"/>
+      <c r="A47" s="112"/>
     </row>
     <row r="49" spans="2:2" ht="19.25" customHeight="1">
-      <c r="B49" s="79"/>
+      <c r="B49" s="71"/>
     </row>
     <row r="50" spans="2:2" ht="18" customHeight="1">
-      <c r="B50" s="79"/>
+      <c r="B50" s="71"/>
     </row>
     <row r="51" spans="2:2" ht="21" customHeight="1">
-      <c r="B51" s="79"/>
+      <c r="B51" s="71"/>
     </row>
     <row r="52" spans="2:2" ht="21" customHeight="1">
-      <c r="B52" s="79"/>
+      <c r="B52" s="71"/>
     </row>
     <row r="53" spans="2:2" ht="17.55" customHeight="1">
-      <c r="B53" s="79"/>
+      <c r="B53" s="71"/>
     </row>
     <row r="54" spans="2:2" ht="21" customHeight="1"/>
-    <row r="65" s="73" customFormat="1"/>
-    <row r="66" s="73" customFormat="1"/>
-    <row r="67" s="73" customFormat="1"/>
-    <row r="68" s="73" customFormat="1"/>
-    <row r="69" s="73" customFormat="1"/>
-    <row r="70" s="73" customFormat="1"/>
-    <row r="71" s="73" customFormat="1"/>
-    <row r="72" s="73" customFormat="1"/>
-    <row r="73" s="73" customFormat="1"/>
-    <row r="74" s="73" customFormat="1"/>
-    <row r="75" s="73" customFormat="1"/>
-    <row r="76" s="73" customFormat="1"/>
-    <row r="77" s="73" customFormat="1"/>
-    <row r="78" s="73" customFormat="1"/>
-    <row r="79" s="73" customFormat="1"/>
-    <row r="80" s="73" customFormat="1"/>
-    <row r="81" s="73" customFormat="1"/>
-    <row r="82" s="73" customFormat="1"/>
-    <row r="83" s="73" customFormat="1"/>
-    <row r="84" s="73" customFormat="1"/>
-    <row r="85" s="73" customFormat="1"/>
-    <row r="86" s="73" customFormat="1"/>
-    <row r="87" s="73" customFormat="1"/>
-    <row r="88" s="73" customFormat="1"/>
-    <row r="89" s="73" customFormat="1"/>
-    <row r="90" s="73" customFormat="1"/>
-    <row r="91" s="73" customFormat="1"/>
-    <row r="92" s="73" customFormat="1"/>
-    <row r="93" s="73" customFormat="1"/>
-    <row r="94" s="73" customFormat="1"/>
-    <row r="95" s="73" customFormat="1"/>
-    <row r="96" s="73" customFormat="1"/>
-    <row r="97" s="73" customFormat="1"/>
-    <row r="98" s="73" customFormat="1"/>
-    <row r="99" s="73" customFormat="1"/>
-    <row r="100" s="73" customFormat="1"/>
-    <row r="101" s="73" customFormat="1"/>
-    <row r="102" s="73" customFormat="1"/>
-    <row r="103" s="73" customFormat="1"/>
-    <row r="104" s="73" customFormat="1"/>
-    <row r="105" s="73" customFormat="1"/>
-    <row r="106" s="73" customFormat="1"/>
-    <row r="107" s="73" customFormat="1"/>
-    <row r="108" s="73" customFormat="1"/>
-    <row r="109" s="73" customFormat="1"/>
-    <row r="110" s="73" customFormat="1"/>
-    <row r="111" s="73" customFormat="1"/>
-    <row r="112" s="73" customFormat="1"/>
-    <row r="113" s="73" customFormat="1"/>
-    <row r="114" s="73" customFormat="1"/>
-    <row r="115" s="73" customFormat="1"/>
-    <row r="116" s="73" customFormat="1"/>
-    <row r="117" s="73" customFormat="1"/>
-    <row r="118" s="73" customFormat="1"/>
-    <row r="119" s="73" customFormat="1"/>
-    <row r="120" s="73" customFormat="1"/>
-    <row r="121" s="73" customFormat="1"/>
-    <row r="122" s="73" customFormat="1"/>
-    <row r="123" s="73" customFormat="1"/>
-    <row r="124" s="73" customFormat="1"/>
-    <row r="125" s="73" customFormat="1"/>
-    <row r="126" s="73" customFormat="1"/>
-    <row r="127" s="73" customFormat="1"/>
-    <row r="128" s="73" customFormat="1"/>
-    <row r="129" s="73" customFormat="1"/>
-    <row r="130" s="73" customFormat="1"/>
-    <row r="131" s="73" customFormat="1"/>
-    <row r="132" s="73" customFormat="1"/>
-    <row r="133" s="73" customFormat="1"/>
-    <row r="134" s="73" customFormat="1"/>
-    <row r="135" s="73" customFormat="1"/>
-    <row r="136" s="73" customFormat="1"/>
-    <row r="137" s="73" customFormat="1"/>
-    <row r="138" s="73" customFormat="1"/>
-    <row r="139" s="73" customFormat="1"/>
-    <row r="140" s="73" customFormat="1"/>
-    <row r="141" s="73" customFormat="1"/>
-    <row r="142" s="73" customFormat="1"/>
-    <row r="143" s="73" customFormat="1"/>
-    <row r="144" s="73" customFormat="1"/>
-    <row r="145" s="73" customFormat="1"/>
-    <row r="146" s="73" customFormat="1"/>
-    <row r="147" s="73" customFormat="1"/>
-    <row r="148" s="73" customFormat="1"/>
-    <row r="149" s="73" customFormat="1"/>
-    <row r="150" s="73" customFormat="1"/>
-    <row r="151" s="73" customFormat="1"/>
-    <row r="152" s="73" customFormat="1"/>
-    <row r="153" s="73" customFormat="1"/>
-    <row r="154" s="73" customFormat="1"/>
-    <row r="155" s="73" customFormat="1"/>
-    <row r="156" s="73" customFormat="1"/>
-    <row r="157" s="73" customFormat="1"/>
-    <row r="158" s="73" customFormat="1"/>
-    <row r="159" s="73" customFormat="1"/>
-    <row r="160" s="73" customFormat="1"/>
-    <row r="161" s="73" customFormat="1"/>
-    <row r="162" s="73" customFormat="1"/>
-    <row r="163" s="73" customFormat="1"/>
-    <row r="164" s="73" customFormat="1"/>
-    <row r="165" s="73" customFormat="1"/>
-    <row r="166" s="73" customFormat="1"/>
-    <row r="167" s="73" customFormat="1"/>
-    <row r="168" s="73" customFormat="1"/>
-    <row r="169" s="73" customFormat="1"/>
-    <row r="170" s="73" customFormat="1"/>
-    <row r="171" s="73" customFormat="1"/>
-    <row r="172" s="73" customFormat="1"/>
-    <row r="173" s="73" customFormat="1"/>
-    <row r="174" s="73" customFormat="1"/>
-    <row r="175" s="73" customFormat="1"/>
-    <row r="176" s="73" customFormat="1"/>
-    <row r="177" s="73" customFormat="1"/>
-    <row r="178" s="73" customFormat="1"/>
-    <row r="179" s="73" customFormat="1"/>
-    <row r="180" s="73" customFormat="1"/>
-    <row r="181" s="73" customFormat="1"/>
-    <row r="182" s="73" customFormat="1"/>
-    <row r="183" s="73" customFormat="1"/>
-    <row r="184" s="73" customFormat="1"/>
-    <row r="185" s="73" customFormat="1"/>
-    <row r="186" s="73" customFormat="1"/>
-    <row r="187" s="73" customFormat="1"/>
-    <row r="188" s="73" customFormat="1"/>
-    <row r="189" s="73" customFormat="1"/>
-    <row r="190" s="73" customFormat="1"/>
-    <row r="191" s="73" customFormat="1"/>
-    <row r="192" s="73" customFormat="1"/>
-    <row r="193" s="73" customFormat="1"/>
-    <row r="194" s="73" customFormat="1"/>
-    <row r="195" s="73" customFormat="1"/>
-    <row r="196" s="73" customFormat="1"/>
-    <row r="197" s="73" customFormat="1"/>
-    <row r="198" s="73" customFormat="1"/>
-    <row r="199" s="73" customFormat="1"/>
-    <row r="200" s="73" customFormat="1"/>
-    <row r="201" s="73" customFormat="1"/>
-    <row r="202" s="73" customFormat="1"/>
-    <row r="203" s="73" customFormat="1"/>
-    <row r="204" s="73" customFormat="1"/>
-    <row r="205" s="73" customFormat="1"/>
-    <row r="206" s="73" customFormat="1"/>
-    <row r="207" s="73" customFormat="1"/>
-    <row r="208" s="73" customFormat="1"/>
-    <row r="209" s="73" customFormat="1"/>
-    <row r="210" s="73" customFormat="1"/>
-    <row r="211" s="73" customFormat="1"/>
-    <row r="212" s="73" customFormat="1"/>
-    <row r="213" s="73" customFormat="1"/>
-    <row r="214" s="73" customFormat="1"/>
-    <row r="215" s="73" customFormat="1"/>
-    <row r="216" s="73" customFormat="1"/>
-    <row r="217" s="73" customFormat="1"/>
-    <row r="218" s="73" customFormat="1"/>
-    <row r="219" s="73" customFormat="1"/>
-    <row r="220" s="73" customFormat="1"/>
-    <row r="221" s="73" customFormat="1"/>
-    <row r="222" s="73" customFormat="1"/>
-    <row r="223" s="73" customFormat="1"/>
-    <row r="224" s="73" customFormat="1"/>
-    <row r="225" s="73" customFormat="1"/>
-    <row r="226" s="73" customFormat="1"/>
-    <row r="227" s="73" customFormat="1"/>
-    <row r="228" s="73" customFormat="1"/>
-    <row r="229" s="73" customFormat="1"/>
-    <row r="230" s="73" customFormat="1"/>
-    <row r="231" s="73" customFormat="1"/>
-    <row r="232" s="73" customFormat="1"/>
-    <row r="233" s="73" customFormat="1"/>
-    <row r="234" s="73" customFormat="1"/>
-    <row r="235" s="73" customFormat="1"/>
-    <row r="236" s="73" customFormat="1"/>
-    <row r="237" s="73" customFormat="1"/>
-    <row r="238" s="73" customFormat="1"/>
-    <row r="239" s="73" customFormat="1"/>
-    <row r="240" s="73" customFormat="1"/>
-    <row r="241" s="73" customFormat="1"/>
-    <row r="242" s="73" customFormat="1"/>
-    <row r="243" s="73" customFormat="1"/>
-    <row r="244" s="73" customFormat="1"/>
-    <row r="245" s="73" customFormat="1"/>
-    <row r="246" s="73" customFormat="1"/>
-    <row r="247" s="73" customFormat="1"/>
-    <row r="248" s="73" customFormat="1"/>
-    <row r="249" s="73" customFormat="1"/>
-    <row r="250" s="73" customFormat="1"/>
-    <row r="251" s="73" customFormat="1"/>
-    <row r="252" s="73" customFormat="1"/>
-    <row r="253" s="73" customFormat="1"/>
-    <row r="254" s="73" customFormat="1"/>
-    <row r="255" s="73" customFormat="1"/>
-    <row r="256" s="73" customFormat="1"/>
-    <row r="257" s="73" customFormat="1"/>
-    <row r="258" s="73" customFormat="1"/>
-    <row r="259" s="73" customFormat="1"/>
-    <row r="260" s="73" customFormat="1"/>
-    <row r="261" s="73" customFormat="1"/>
-    <row r="262" s="73" customFormat="1"/>
-    <row r="263" s="73" customFormat="1"/>
-    <row r="264" s="73" customFormat="1"/>
-    <row r="265" s="73" customFormat="1"/>
-    <row r="266" s="73" customFormat="1"/>
-    <row r="267" s="73" customFormat="1"/>
-    <row r="268" s="73" customFormat="1"/>
-    <row r="269" s="73" customFormat="1"/>
-    <row r="270" s="73" customFormat="1"/>
-    <row r="271" s="73" customFormat="1"/>
-    <row r="272" s="73" customFormat="1"/>
-    <row r="273" s="73" customFormat="1"/>
-    <row r="274" s="73" customFormat="1"/>
-    <row r="275" s="73" customFormat="1"/>
-    <row r="276" s="73" customFormat="1"/>
-    <row r="277" s="73" customFormat="1"/>
-    <row r="278" s="73" customFormat="1"/>
-    <row r="279" s="73" customFormat="1"/>
-    <row r="280" s="73" customFormat="1"/>
-    <row r="281" s="73" customFormat="1"/>
-    <row r="282" s="73" customFormat="1"/>
-    <row r="283" s="73" customFormat="1"/>
-    <row r="284" s="73" customFormat="1"/>
-    <row r="285" s="73" customFormat="1"/>
-    <row r="286" s="73" customFormat="1"/>
-    <row r="287" s="73" customFormat="1"/>
-    <row r="288" s="73" customFormat="1"/>
-    <row r="289" s="73" customFormat="1"/>
-    <row r="290" s="73" customFormat="1"/>
-    <row r="291" s="73" customFormat="1"/>
-    <row r="292" s="73" customFormat="1"/>
-    <row r="293" s="73" customFormat="1"/>
-    <row r="294" s="73" customFormat="1"/>
-    <row r="295" s="73" customFormat="1"/>
-    <row r="296" s="73" customFormat="1"/>
-    <row r="297" s="73" customFormat="1"/>
-    <row r="298" s="73" customFormat="1"/>
-    <row r="299" s="73" customFormat="1"/>
-    <row r="300" s="73" customFormat="1"/>
-    <row r="301" s="73" customFormat="1"/>
-    <row r="302" s="73" customFormat="1"/>
-    <row r="303" s="73" customFormat="1"/>
-    <row r="304" s="73" customFormat="1"/>
-    <row r="305" s="73" customFormat="1"/>
-    <row r="306" s="73" customFormat="1"/>
-    <row r="307" s="73" customFormat="1"/>
-    <row r="308" s="73" customFormat="1"/>
-    <row r="309" s="73" customFormat="1"/>
-    <row r="310" s="73" customFormat="1"/>
-    <row r="311" s="73" customFormat="1"/>
-    <row r="312" s="73" customFormat="1"/>
-    <row r="313" s="73" customFormat="1"/>
-    <row r="314" s="73" customFormat="1"/>
-    <row r="315" s="73" customFormat="1"/>
-    <row r="316" s="73" customFormat="1"/>
-    <row r="317" s="73" customFormat="1"/>
-    <row r="318" s="73" customFormat="1"/>
-    <row r="319" s="73" customFormat="1"/>
-    <row r="320" s="73" customFormat="1"/>
-    <row r="321" s="73" customFormat="1"/>
-    <row r="322" s="73" customFormat="1"/>
-    <row r="323" s="73" customFormat="1"/>
-    <row r="324" s="73" customFormat="1"/>
-    <row r="325" s="73" customFormat="1"/>
-    <row r="326" s="73" customFormat="1"/>
-    <row r="327" s="73" customFormat="1"/>
-    <row r="328" s="73" customFormat="1"/>
-    <row r="329" s="73" customFormat="1"/>
-    <row r="330" s="73" customFormat="1"/>
-    <row r="331" s="73" customFormat="1"/>
-    <row r="332" s="73" customFormat="1"/>
-    <row r="333" s="73" customFormat="1"/>
-    <row r="334" s="73" customFormat="1"/>
-    <row r="335" s="73" customFormat="1"/>
-    <row r="336" s="73" customFormat="1"/>
-    <row r="337" s="73" customFormat="1"/>
-    <row r="338" s="73" customFormat="1"/>
-    <row r="339" s="73" customFormat="1"/>
-    <row r="340" s="73" customFormat="1"/>
-    <row r="341" s="73" customFormat="1"/>
-    <row r="342" s="73" customFormat="1"/>
-    <row r="343" s="73" customFormat="1"/>
-    <row r="344" s="73" customFormat="1"/>
-    <row r="345" s="73" customFormat="1"/>
-    <row r="346" s="73" customFormat="1"/>
-    <row r="347" s="73" customFormat="1"/>
-    <row r="348" s="73" customFormat="1"/>
-    <row r="349" s="73" customFormat="1"/>
-    <row r="350" s="73" customFormat="1"/>
-    <row r="351" s="73" customFormat="1"/>
-    <row r="352" s="73" customFormat="1"/>
-    <row r="353" s="73" customFormat="1"/>
-    <row r="354" s="73" customFormat="1"/>
-    <row r="355" s="73" customFormat="1"/>
-    <row r="356" s="73" customFormat="1"/>
-    <row r="357" s="73" customFormat="1"/>
-    <row r="358" s="73" customFormat="1"/>
-    <row r="359" s="73" customFormat="1"/>
-    <row r="360" s="73" customFormat="1"/>
-    <row r="361" s="73" customFormat="1"/>
-    <row r="362" s="73" customFormat="1"/>
-    <row r="363" s="73" customFormat="1"/>
-    <row r="364" s="73" customFormat="1"/>
-    <row r="365" s="73" customFormat="1"/>
-    <row r="366" s="73" customFormat="1"/>
-    <row r="367" s="73" customFormat="1"/>
-    <row r="368" s="73" customFormat="1"/>
-    <row r="369" s="73" customFormat="1"/>
-    <row r="370" s="73" customFormat="1"/>
-    <row r="371" s="73" customFormat="1"/>
-    <row r="372" s="73" customFormat="1"/>
-    <row r="373" s="73" customFormat="1"/>
-    <row r="374" s="73" customFormat="1"/>
-    <row r="375" s="73" customFormat="1"/>
-    <row r="376" s="73" customFormat="1"/>
-    <row r="377" s="73" customFormat="1"/>
-    <row r="378" s="73" customFormat="1"/>
-    <row r="379" s="73" customFormat="1"/>
-    <row r="380" s="73" customFormat="1"/>
-    <row r="381" s="73" customFormat="1"/>
-    <row r="382" s="73" customFormat="1"/>
-    <row r="383" s="73" customFormat="1"/>
-    <row r="384" s="73" customFormat="1"/>
-    <row r="385" s="73" customFormat="1"/>
-    <row r="386" s="73" customFormat="1"/>
-    <row r="387" s="73" customFormat="1"/>
-    <row r="388" s="73" customFormat="1"/>
-    <row r="389" s="73" customFormat="1"/>
-    <row r="390" s="73" customFormat="1"/>
-    <row r="391" s="73" customFormat="1"/>
-    <row r="392" s="73" customFormat="1"/>
-    <row r="393" s="73" customFormat="1"/>
-    <row r="394" s="73" customFormat="1"/>
-    <row r="395" s="73" customFormat="1"/>
-    <row r="396" s="73" customFormat="1"/>
-    <row r="397" s="73" customFormat="1"/>
-    <row r="398" s="73" customFormat="1"/>
-    <row r="399" s="73" customFormat="1"/>
-    <row r="400" s="73" customFormat="1"/>
-    <row r="401" s="73" customFormat="1"/>
-    <row r="402" s="73" customFormat="1"/>
-    <row r="403" s="73" customFormat="1"/>
-    <row r="404" s="73" customFormat="1"/>
-    <row r="405" s="73" customFormat="1"/>
-    <row r="406" s="73" customFormat="1"/>
-    <row r="407" s="73" customFormat="1"/>
-    <row r="408" s="73" customFormat="1"/>
-    <row r="409" s="73" customFormat="1"/>
-    <row r="410" s="73" customFormat="1"/>
-    <row r="411" s="73" customFormat="1"/>
-    <row r="412" s="73" customFormat="1"/>
-    <row r="413" s="73" customFormat="1"/>
-    <row r="414" s="73" customFormat="1"/>
-    <row r="415" s="73" customFormat="1"/>
-    <row r="416" s="73" customFormat="1"/>
-    <row r="417" s="73" customFormat="1"/>
-    <row r="418" s="73" customFormat="1"/>
-    <row r="419" s="73" customFormat="1"/>
-    <row r="420" s="73" customFormat="1"/>
-    <row r="421" s="73" customFormat="1"/>
-    <row r="422" s="73" customFormat="1"/>
-    <row r="423" s="73" customFormat="1"/>
-    <row r="424" s="73" customFormat="1"/>
-    <row r="425" s="73" customFormat="1"/>
-    <row r="426" s="73" customFormat="1"/>
-    <row r="427" s="73" customFormat="1"/>
-    <row r="428" s="73" customFormat="1"/>
-    <row r="429" s="73" customFormat="1"/>
-    <row r="430" s="73" customFormat="1"/>
-    <row r="431" s="73" customFormat="1"/>
-    <row r="432" s="73" customFormat="1"/>
-    <row r="433" s="73" customFormat="1"/>
-    <row r="434" s="73" customFormat="1"/>
-    <row r="435" s="73" customFormat="1"/>
-    <row r="436" s="73" customFormat="1"/>
-    <row r="437" s="73" customFormat="1"/>
-    <row r="438" s="73" customFormat="1"/>
-    <row r="439" s="73" customFormat="1"/>
-    <row r="440" s="73" customFormat="1"/>
-    <row r="441" s="73" customFormat="1"/>
-    <row r="442" s="73" customFormat="1"/>
-    <row r="443" s="73" customFormat="1"/>
-    <row r="444" s="73" customFormat="1"/>
-    <row r="445" s="73" customFormat="1"/>
-    <row r="446" s="73" customFormat="1"/>
-    <row r="447" s="73" customFormat="1"/>
-    <row r="448" s="73" customFormat="1"/>
-    <row r="449" s="73" customFormat="1"/>
-    <row r="450" s="73" customFormat="1"/>
-    <row r="451" s="73" customFormat="1"/>
-    <row r="452" s="73" customFormat="1"/>
-    <row r="453" s="73" customFormat="1"/>
-    <row r="454" s="73" customFormat="1"/>
-    <row r="455" s="73" customFormat="1"/>
-    <row r="456" s="73" customFormat="1"/>
-    <row r="457" s="73" customFormat="1"/>
-    <row r="458" s="73" customFormat="1"/>
-    <row r="459" s="73" customFormat="1"/>
-    <row r="460" s="73" customFormat="1"/>
-    <row r="461" s="73" customFormat="1"/>
-    <row r="462" s="73" customFormat="1"/>
-    <row r="463" s="73" customFormat="1"/>
-    <row r="464" s="73" customFormat="1"/>
-    <row r="465" s="73" customFormat="1"/>
-    <row r="466" s="73" customFormat="1"/>
-    <row r="467" s="73" customFormat="1"/>
-    <row r="468" s="73" customFormat="1"/>
-    <row r="469" s="73" customFormat="1"/>
-    <row r="470" s="73" customFormat="1"/>
-    <row r="471" s="73" customFormat="1"/>
-    <row r="472" s="73" customFormat="1"/>
-    <row r="473" s="73" customFormat="1"/>
-    <row r="474" s="73" customFormat="1"/>
-    <row r="475" s="73" customFormat="1"/>
-    <row r="476" s="73" customFormat="1"/>
-    <row r="477" s="73" customFormat="1"/>
-    <row r="478" s="73" customFormat="1"/>
-    <row r="479" s="73" customFormat="1"/>
-    <row r="480" s="73" customFormat="1"/>
-    <row r="481" s="73" customFormat="1"/>
-    <row r="482" s="73" customFormat="1"/>
-    <row r="483" s="73" customFormat="1"/>
-    <row r="484" s="73" customFormat="1"/>
-    <row r="485" s="73" customFormat="1"/>
-    <row r="486" s="73" customFormat="1"/>
-    <row r="487" s="73" customFormat="1"/>
-    <row r="488" s="73" customFormat="1"/>
-    <row r="489" s="73" customFormat="1"/>
-    <row r="490" s="73" customFormat="1"/>
-    <row r="491" s="73" customFormat="1"/>
-    <row r="492" s="73" customFormat="1"/>
-    <row r="493" s="73" customFormat="1"/>
-    <row r="494" s="73" customFormat="1"/>
-    <row r="495" s="73" customFormat="1"/>
-    <row r="496" s="73" customFormat="1"/>
-    <row r="497" s="73" customFormat="1"/>
-    <row r="498" s="73" customFormat="1"/>
-    <row r="499" s="73" customFormat="1"/>
-    <row r="500" s="73" customFormat="1"/>
-    <row r="501" s="73" customFormat="1"/>
-    <row r="502" s="73" customFormat="1"/>
-    <row r="503" s="73" customFormat="1"/>
-    <row r="504" s="73" customFormat="1"/>
-    <row r="505" s="73" customFormat="1"/>
-    <row r="506" s="73" customFormat="1"/>
-    <row r="507" s="73" customFormat="1"/>
-    <row r="508" s="73" customFormat="1"/>
-    <row r="509" s="73" customFormat="1"/>
-    <row r="510" s="73" customFormat="1"/>
-    <row r="511" s="73" customFormat="1"/>
-    <row r="512" s="73" customFormat="1"/>
-    <row r="513" s="73" customFormat="1"/>
-    <row r="514" s="73" customFormat="1"/>
-    <row r="515" s="73" customFormat="1"/>
-    <row r="516" s="73" customFormat="1"/>
-    <row r="517" s="73" customFormat="1"/>
-    <row r="518" s="73" customFormat="1"/>
-    <row r="519" s="73" customFormat="1"/>
-    <row r="520" s="73" customFormat="1"/>
-    <row r="521" s="73" customFormat="1"/>
-    <row r="522" s="73" customFormat="1"/>
-    <row r="523" s="73" customFormat="1"/>
-    <row r="524" s="73" customFormat="1"/>
-    <row r="525" s="73" customFormat="1"/>
-    <row r="526" s="73" customFormat="1"/>
-    <row r="527" s="73" customFormat="1"/>
-    <row r="528" s="73" customFormat="1"/>
-    <row r="529" s="73" customFormat="1"/>
-    <row r="530" s="73" customFormat="1"/>
-    <row r="531" s="73" customFormat="1"/>
-    <row r="532" s="73" customFormat="1"/>
-    <row r="533" s="73" customFormat="1"/>
-    <row r="534" s="73" customFormat="1"/>
-    <row r="535" s="73" customFormat="1"/>
-    <row r="536" s="73" customFormat="1"/>
-    <row r="537" s="73" customFormat="1"/>
-    <row r="538" s="73" customFormat="1"/>
-    <row r="539" s="73" customFormat="1"/>
-    <row r="540" s="73" customFormat="1"/>
-    <row r="541" s="73" customFormat="1"/>
-    <row r="542" s="73" customFormat="1"/>
-    <row r="543" s="73" customFormat="1"/>
-    <row r="544" s="73" customFormat="1"/>
-    <row r="545" s="73" customFormat="1"/>
-    <row r="546" s="73" customFormat="1"/>
-    <row r="547" s="73" customFormat="1"/>
-    <row r="548" s="73" customFormat="1"/>
-    <row r="549" s="73" customFormat="1"/>
-    <row r="550" s="73" customFormat="1"/>
-    <row r="551" s="73" customFormat="1"/>
-    <row r="552" s="73" customFormat="1"/>
-    <row r="553" s="73" customFormat="1"/>
-    <row r="554" s="73" customFormat="1"/>
-    <row r="555" s="73" customFormat="1"/>
-    <row r="556" s="73" customFormat="1"/>
-    <row r="557" s="73" customFormat="1"/>
-    <row r="558" s="73" customFormat="1"/>
-    <row r="559" s="73" customFormat="1"/>
-    <row r="560" s="73" customFormat="1"/>
-    <row r="561" s="73" customFormat="1"/>
-    <row r="562" s="73" customFormat="1"/>
-    <row r="563" s="73" customFormat="1"/>
-    <row r="564" s="73" customFormat="1"/>
-    <row r="565" s="73" customFormat="1"/>
-    <row r="566" s="73" customFormat="1"/>
-    <row r="567" s="73" customFormat="1"/>
-    <row r="568" s="73" customFormat="1"/>
-    <row r="569" s="73" customFormat="1"/>
-    <row r="570" s="73" customFormat="1"/>
-    <row r="571" s="73" customFormat="1"/>
-    <row r="572" s="73" customFormat="1"/>
-    <row r="573" s="73" customFormat="1"/>
-    <row r="574" s="73" customFormat="1"/>
-    <row r="575" s="73" customFormat="1"/>
-    <row r="576" s="73" customFormat="1"/>
-    <row r="577" s="73" customFormat="1"/>
-    <row r="578" s="73" customFormat="1"/>
-    <row r="579" s="73" customFormat="1"/>
-    <row r="580" s="73" customFormat="1"/>
-    <row r="581" s="73" customFormat="1"/>
-    <row r="582" s="73" customFormat="1"/>
-    <row r="583" s="73" customFormat="1"/>
-    <row r="584" s="73" customFormat="1"/>
-    <row r="585" s="73" customFormat="1"/>
-    <row r="586" s="73" customFormat="1"/>
-    <row r="587" s="73" customFormat="1"/>
-    <row r="588" s="73" customFormat="1"/>
-    <row r="589" s="73" customFormat="1"/>
-    <row r="590" s="73" customFormat="1"/>
-    <row r="591" s="73" customFormat="1"/>
-    <row r="592" s="73" customFormat="1"/>
-    <row r="593" s="73" customFormat="1"/>
-    <row r="594" s="73" customFormat="1"/>
-    <row r="595" s="73" customFormat="1"/>
-    <row r="596" s="73" customFormat="1"/>
-    <row r="597" s="73" customFormat="1"/>
-    <row r="598" s="73" customFormat="1"/>
-    <row r="599" s="73" customFormat="1"/>
-    <row r="600" s="73" customFormat="1"/>
-    <row r="601" s="73" customFormat="1"/>
-    <row r="602" s="73" customFormat="1"/>
-    <row r="603" s="73" customFormat="1"/>
-    <row r="604" s="73" customFormat="1"/>
-    <row r="605" s="73" customFormat="1"/>
-    <row r="606" s="73" customFormat="1"/>
-    <row r="607" s="73" customFormat="1"/>
-    <row r="608" s="73" customFormat="1"/>
-    <row r="609" s="73" customFormat="1"/>
-    <row r="610" s="73" customFormat="1"/>
-    <row r="611" s="73" customFormat="1"/>
-    <row r="612" s="73" customFormat="1"/>
-    <row r="613" s="73" customFormat="1"/>
-    <row r="614" s="73" customFormat="1"/>
-    <row r="615" s="73" customFormat="1"/>
-    <row r="616" s="73" customFormat="1"/>
-    <row r="617" s="73" customFormat="1"/>
-    <row r="618" s="73" customFormat="1"/>
-    <row r="619" s="73" customFormat="1"/>
-    <row r="620" s="73" customFormat="1"/>
-    <row r="621" s="73" customFormat="1"/>
-    <row r="622" s="73" customFormat="1"/>
-    <row r="623" s="73" customFormat="1"/>
-    <row r="624" s="73" customFormat="1"/>
-    <row r="625" s="73" customFormat="1"/>
-    <row r="626" s="73" customFormat="1"/>
-    <row r="627" s="73" customFormat="1"/>
-    <row r="628" s="73" customFormat="1"/>
-    <row r="629" s="73" customFormat="1"/>
-    <row r="630" s="73" customFormat="1"/>
-    <row r="631" s="73" customFormat="1"/>
-    <row r="632" s="73" customFormat="1"/>
-    <row r="633" s="73" customFormat="1"/>
-    <row r="634" s="73" customFormat="1"/>
-    <row r="635" s="73" customFormat="1"/>
-    <row r="636" s="73" customFormat="1"/>
-    <row r="637" s="73" customFormat="1"/>
-    <row r="638" s="73" customFormat="1"/>
-    <row r="639" s="73" customFormat="1"/>
-    <row r="640" s="73" customFormat="1"/>
-    <row r="641" s="73" customFormat="1"/>
-    <row r="642" s="73" customFormat="1"/>
-    <row r="643" s="73" customFormat="1"/>
-    <row r="644" s="73" customFormat="1"/>
-    <row r="645" s="73" customFormat="1"/>
-    <row r="646" s="73" customFormat="1"/>
-    <row r="647" s="73" customFormat="1"/>
-    <row r="648" s="73" customFormat="1"/>
-    <row r="649" s="73" customFormat="1"/>
-    <row r="650" s="73" customFormat="1"/>
-    <row r="651" s="73" customFormat="1"/>
-    <row r="652" s="73" customFormat="1"/>
-    <row r="653" s="73" customFormat="1"/>
-    <row r="654" s="73" customFormat="1"/>
-    <row r="655" s="73" customFormat="1"/>
-    <row r="656" s="73" customFormat="1"/>
-    <row r="657" s="73" customFormat="1"/>
-    <row r="658" s="73" customFormat="1"/>
-    <row r="659" s="73" customFormat="1"/>
-    <row r="660" s="73" customFormat="1"/>
-    <row r="661" s="73" customFormat="1"/>
-    <row r="662" s="73" customFormat="1"/>
-    <row r="663" s="73" customFormat="1"/>
-    <row r="664" s="73" customFormat="1"/>
-    <row r="665" s="73" customFormat="1"/>
-    <row r="666" s="73" customFormat="1"/>
-    <row r="667" s="73" customFormat="1"/>
-    <row r="668" s="73" customFormat="1"/>
-    <row r="669" s="73" customFormat="1"/>
-    <row r="670" s="73" customFormat="1"/>
-    <row r="671" s="73" customFormat="1"/>
-    <row r="672" s="73" customFormat="1"/>
-    <row r="673" s="73" customFormat="1"/>
-    <row r="674" s="73" customFormat="1"/>
-    <row r="675" s="73" customFormat="1"/>
-    <row r="676" s="73" customFormat="1"/>
-    <row r="677" s="73" customFormat="1"/>
-    <row r="678" s="73" customFormat="1"/>
-    <row r="679" s="73" customFormat="1"/>
-    <row r="680" s="73" customFormat="1"/>
-    <row r="681" s="73" customFormat="1"/>
-    <row r="682" s="73" customFormat="1"/>
-    <row r="683" s="73" customFormat="1"/>
-    <row r="684" s="73" customFormat="1"/>
-    <row r="685" s="73" customFormat="1"/>
-    <row r="686" s="73" customFormat="1"/>
-    <row r="687" s="73" customFormat="1"/>
-    <row r="688" s="73" customFormat="1"/>
-    <row r="689" s="73" customFormat="1"/>
-    <row r="690" s="73" customFormat="1"/>
-    <row r="691" s="73" customFormat="1"/>
-    <row r="692" s="73" customFormat="1"/>
-    <row r="693" s="73" customFormat="1"/>
-    <row r="694" s="73" customFormat="1"/>
-    <row r="695" s="73" customFormat="1"/>
-    <row r="696" s="73" customFormat="1"/>
-    <row r="697" s="73" customFormat="1"/>
-    <row r="698" s="73" customFormat="1"/>
-    <row r="699" s="73" customFormat="1"/>
-    <row r="700" s="73" customFormat="1"/>
-    <row r="701" s="73" customFormat="1"/>
-    <row r="702" s="73" customFormat="1"/>
-    <row r="703" s="73" customFormat="1"/>
-    <row r="704" s="73" customFormat="1"/>
-    <row r="705" s="73" customFormat="1"/>
-    <row r="706" s="73" customFormat="1"/>
-    <row r="707" s="73" customFormat="1"/>
-    <row r="708" s="73" customFormat="1"/>
-    <row r="709" s="73" customFormat="1"/>
-    <row r="710" s="73" customFormat="1"/>
-    <row r="711" s="73" customFormat="1"/>
-    <row r="712" s="73" customFormat="1"/>
-    <row r="713" s="73" customFormat="1"/>
-    <row r="714" s="73" customFormat="1"/>
-    <row r="715" s="73" customFormat="1"/>
-    <row r="716" s="73" customFormat="1"/>
-    <row r="717" s="73" customFormat="1"/>
-    <row r="718" s="73" customFormat="1"/>
-    <row r="719" s="73" customFormat="1"/>
-    <row r="720" s="73" customFormat="1"/>
-    <row r="721" s="73" customFormat="1"/>
-    <row r="722" s="73" customFormat="1"/>
-    <row r="723" s="73" customFormat="1"/>
-    <row r="724" s="73" customFormat="1"/>
-    <row r="725" s="73" customFormat="1"/>
-    <row r="726" s="73" customFormat="1"/>
-    <row r="727" s="73" customFormat="1"/>
-    <row r="728" s="73" customFormat="1"/>
-    <row r="729" s="73" customFormat="1"/>
-    <row r="730" s="73" customFormat="1"/>
-    <row r="731" s="73" customFormat="1"/>
-    <row r="732" s="73" customFormat="1"/>
-    <row r="733" s="73" customFormat="1"/>
-    <row r="734" s="73" customFormat="1"/>
-    <row r="735" s="73" customFormat="1"/>
-    <row r="736" s="73" customFormat="1"/>
-    <row r="737" s="73" customFormat="1"/>
-    <row r="738" s="73" customFormat="1"/>
-    <row r="739" s="73" customFormat="1"/>
-    <row r="740" s="73" customFormat="1"/>
-    <row r="741" s="73" customFormat="1"/>
-    <row r="742" s="73" customFormat="1"/>
-    <row r="743" s="73" customFormat="1"/>
-    <row r="744" s="73" customFormat="1"/>
-    <row r="745" s="73" customFormat="1"/>
-    <row r="746" s="73" customFormat="1"/>
-    <row r="747" s="73" customFormat="1"/>
-    <row r="748" s="73" customFormat="1"/>
-    <row r="749" s="73" customFormat="1"/>
-    <row r="750" s="73" customFormat="1"/>
-    <row r="751" s="73" customFormat="1"/>
-    <row r="752" s="73" customFormat="1"/>
-    <row r="753" s="73" customFormat="1"/>
-    <row r="754" s="73" customFormat="1"/>
-    <row r="755" s="73" customFormat="1"/>
-    <row r="756" s="73" customFormat="1"/>
-    <row r="757" s="73" customFormat="1"/>
-    <row r="758" s="73" customFormat="1"/>
-    <row r="759" s="73" customFormat="1"/>
-    <row r="760" s="73" customFormat="1"/>
-    <row r="761" s="73" customFormat="1"/>
-    <row r="762" s="73" customFormat="1"/>
-    <row r="763" s="73" customFormat="1"/>
-    <row r="764" s="73" customFormat="1"/>
-    <row r="765" s="73" customFormat="1"/>
-    <row r="766" s="73" customFormat="1"/>
-    <row r="767" s="73" customFormat="1"/>
-    <row r="768" s="73" customFormat="1"/>
-    <row r="769" s="73" customFormat="1"/>
-    <row r="770" s="73" customFormat="1"/>
-    <row r="771" s="73" customFormat="1"/>
-    <row r="772" s="73" customFormat="1"/>
-    <row r="773" s="73" customFormat="1"/>
-    <row r="774" s="73" customFormat="1"/>
-    <row r="775" s="73" customFormat="1"/>
-    <row r="776" s="73" customFormat="1"/>
-    <row r="777" s="73" customFormat="1"/>
-    <row r="778" s="73" customFormat="1"/>
-    <row r="779" s="73" customFormat="1"/>
-    <row r="780" s="73" customFormat="1"/>
-    <row r="781" s="73" customFormat="1"/>
-    <row r="782" s="73" customFormat="1"/>
+    <row r="65" s="65" customFormat="1"/>
+    <row r="66" s="65" customFormat="1"/>
+    <row r="67" s="65" customFormat="1"/>
+    <row r="68" s="65" customFormat="1"/>
+    <row r="69" s="65" customFormat="1"/>
+    <row r="70" s="65" customFormat="1"/>
+    <row r="71" s="65" customFormat="1"/>
+    <row r="72" s="65" customFormat="1"/>
+    <row r="73" s="65" customFormat="1"/>
+    <row r="74" s="65" customFormat="1"/>
+    <row r="75" s="65" customFormat="1"/>
+    <row r="76" s="65" customFormat="1"/>
+    <row r="77" s="65" customFormat="1"/>
+    <row r="78" s="65" customFormat="1"/>
+    <row r="79" s="65" customFormat="1"/>
+    <row r="80" s="65" customFormat="1"/>
+    <row r="81" s="65" customFormat="1"/>
+    <row r="82" s="65" customFormat="1"/>
+    <row r="83" s="65" customFormat="1"/>
+    <row r="84" s="65" customFormat="1"/>
+    <row r="85" s="65" customFormat="1"/>
+    <row r="86" s="65" customFormat="1"/>
+    <row r="87" s="65" customFormat="1"/>
+    <row r="88" s="65" customFormat="1"/>
+    <row r="89" s="65" customFormat="1"/>
+    <row r="90" s="65" customFormat="1"/>
+    <row r="91" s="65" customFormat="1"/>
+    <row r="92" s="65" customFormat="1"/>
+    <row r="93" s="65" customFormat="1"/>
+    <row r="94" s="65" customFormat="1"/>
+    <row r="95" s="65" customFormat="1"/>
+    <row r="96" s="65" customFormat="1"/>
+    <row r="97" s="65" customFormat="1"/>
+    <row r="98" s="65" customFormat="1"/>
+    <row r="99" s="65" customFormat="1"/>
+    <row r="100" s="65" customFormat="1"/>
+    <row r="101" s="65" customFormat="1"/>
+    <row r="102" s="65" customFormat="1"/>
+    <row r="103" s="65" customFormat="1"/>
+    <row r="104" s="65" customFormat="1"/>
+    <row r="105" s="65" customFormat="1"/>
+    <row r="106" s="65" customFormat="1"/>
+    <row r="107" s="65" customFormat="1"/>
+    <row r="108" s="65" customFormat="1"/>
+    <row r="109" s="65" customFormat="1"/>
+    <row r="110" s="65" customFormat="1"/>
+    <row r="111" s="65" customFormat="1"/>
+    <row r="112" s="65" customFormat="1"/>
+    <row r="113" s="65" customFormat="1"/>
+    <row r="114" s="65" customFormat="1"/>
+    <row r="115" s="65" customFormat="1"/>
+    <row r="116" s="65" customFormat="1"/>
+    <row r="117" s="65" customFormat="1"/>
+    <row r="118" s="65" customFormat="1"/>
+    <row r="119" s="65" customFormat="1"/>
+    <row r="120" s="65" customFormat="1"/>
+    <row r="121" s="65" customFormat="1"/>
+    <row r="122" s="65" customFormat="1"/>
+    <row r="123" s="65" customFormat="1"/>
+    <row r="124" s="65" customFormat="1"/>
+    <row r="125" s="65" customFormat="1"/>
+    <row r="126" s="65" customFormat="1"/>
+    <row r="127" s="65" customFormat="1"/>
+    <row r="128" s="65" customFormat="1"/>
+    <row r="129" s="65" customFormat="1"/>
+    <row r="130" s="65" customFormat="1"/>
+    <row r="131" s="65" customFormat="1"/>
+    <row r="132" s="65" customFormat="1"/>
+    <row r="133" s="65" customFormat="1"/>
+    <row r="134" s="65" customFormat="1"/>
+    <row r="135" s="65" customFormat="1"/>
+    <row r="136" s="65" customFormat="1"/>
+    <row r="137" s="65" customFormat="1"/>
+    <row r="138" s="65" customFormat="1"/>
+    <row r="139" s="65" customFormat="1"/>
+    <row r="140" s="65" customFormat="1"/>
+    <row r="141" s="65" customFormat="1"/>
+    <row r="142" s="65" customFormat="1"/>
+    <row r="143" s="65" customFormat="1"/>
+    <row r="144" s="65" customFormat="1"/>
+    <row r="145" s="65" customFormat="1"/>
+    <row r="146" s="65" customFormat="1"/>
+    <row r="147" s="65" customFormat="1"/>
+    <row r="148" s="65" customFormat="1"/>
+    <row r="149" s="65" customFormat="1"/>
+    <row r="150" s="65" customFormat="1"/>
+    <row r="151" s="65" customFormat="1"/>
+    <row r="152" s="65" customFormat="1"/>
+    <row r="153" s="65" customFormat="1"/>
+    <row r="154" s="65" customFormat="1"/>
+    <row r="155" s="65" customFormat="1"/>
+    <row r="156" s="65" customFormat="1"/>
+    <row r="157" s="65" customFormat="1"/>
+    <row r="158" s="65" customFormat="1"/>
+    <row r="159" s="65" customFormat="1"/>
+    <row r="160" s="65" customFormat="1"/>
+    <row r="161" s="65" customFormat="1"/>
+    <row r="162" s="65" customFormat="1"/>
+    <row r="163" s="65" customFormat="1"/>
+    <row r="164" s="65" customFormat="1"/>
+    <row r="165" s="65" customFormat="1"/>
+    <row r="166" s="65" customFormat="1"/>
+    <row r="167" s="65" customFormat="1"/>
+    <row r="168" s="65" customFormat="1"/>
+    <row r="169" s="65" customFormat="1"/>
+    <row r="170" s="65" customFormat="1"/>
+    <row r="171" s="65" customFormat="1"/>
+    <row r="172" s="65" customFormat="1"/>
+    <row r="173" s="65" customFormat="1"/>
+    <row r="174" s="65" customFormat="1"/>
+    <row r="175" s="65" customFormat="1"/>
+    <row r="176" s="65" customFormat="1"/>
+    <row r="177" s="65" customFormat="1"/>
+    <row r="178" s="65" customFormat="1"/>
+    <row r="179" s="65" customFormat="1"/>
+    <row r="180" s="65" customFormat="1"/>
+    <row r="181" s="65" customFormat="1"/>
+    <row r="182" s="65" customFormat="1"/>
+    <row r="183" s="65" customFormat="1"/>
+    <row r="184" s="65" customFormat="1"/>
+    <row r="185" s="65" customFormat="1"/>
+    <row r="186" s="65" customFormat="1"/>
+    <row r="187" s="65" customFormat="1"/>
+    <row r="188" s="65" customFormat="1"/>
+    <row r="189" s="65" customFormat="1"/>
+    <row r="190" s="65" customFormat="1"/>
+    <row r="191" s="65" customFormat="1"/>
+    <row r="192" s="65" customFormat="1"/>
+    <row r="193" s="65" customFormat="1"/>
+    <row r="194" s="65" customFormat="1"/>
+    <row r="195" s="65" customFormat="1"/>
+    <row r="196" s="65" customFormat="1"/>
+    <row r="197" s="65" customFormat="1"/>
+    <row r="198" s="65" customFormat="1"/>
+    <row r="199" s="65" customFormat="1"/>
+    <row r="200" s="65" customFormat="1"/>
+    <row r="201" s="65" customFormat="1"/>
+    <row r="202" s="65" customFormat="1"/>
+    <row r="203" s="65" customFormat="1"/>
+    <row r="204" s="65" customFormat="1"/>
+    <row r="205" s="65" customFormat="1"/>
+    <row r="206" s="65" customFormat="1"/>
+    <row r="207" s="65" customFormat="1"/>
+    <row r="208" s="65" customFormat="1"/>
+    <row r="209" s="65" customFormat="1"/>
+    <row r="210" s="65" customFormat="1"/>
+    <row r="211" s="65" customFormat="1"/>
+    <row r="212" s="65" customFormat="1"/>
+    <row r="213" s="65" customFormat="1"/>
+    <row r="214" s="65" customFormat="1"/>
+    <row r="215" s="65" customFormat="1"/>
+    <row r="216" s="65" customFormat="1"/>
+    <row r="217" s="65" customFormat="1"/>
+    <row r="218" s="65" customFormat="1"/>
+    <row r="219" s="65" customFormat="1"/>
+    <row r="220" s="65" customFormat="1"/>
+    <row r="221" s="65" customFormat="1"/>
+    <row r="222" s="65" customFormat="1"/>
+    <row r="223" s="65" customFormat="1"/>
+    <row r="224" s="65" customFormat="1"/>
+    <row r="225" s="65" customFormat="1"/>
+    <row r="226" s="65" customFormat="1"/>
+    <row r="227" s="65" customFormat="1"/>
+    <row r="228" s="65" customFormat="1"/>
+    <row r="229" s="65" customFormat="1"/>
+    <row r="230" s="65" customFormat="1"/>
+    <row r="231" s="65" customFormat="1"/>
+    <row r="232" s="65" customFormat="1"/>
+    <row r="233" s="65" customFormat="1"/>
+    <row r="234" s="65" customFormat="1"/>
+    <row r="235" s="65" customFormat="1"/>
+    <row r="236" s="65" customFormat="1"/>
+    <row r="237" s="65" customFormat="1"/>
+    <row r="238" s="65" customFormat="1"/>
+    <row r="239" s="65" customFormat="1"/>
+    <row r="240" s="65" customFormat="1"/>
+    <row r="241" s="65" customFormat="1"/>
+    <row r="242" s="65" customFormat="1"/>
+    <row r="243" s="65" customFormat="1"/>
+    <row r="244" s="65" customFormat="1"/>
+    <row r="245" s="65" customFormat="1"/>
+    <row r="246" s="65" customFormat="1"/>
+    <row r="247" s="65" customFormat="1"/>
+    <row r="248" s="65" customFormat="1"/>
+    <row r="249" s="65" customFormat="1"/>
+    <row r="250" s="65" customFormat="1"/>
+    <row r="251" s="65" customFormat="1"/>
+    <row r="252" s="65" customFormat="1"/>
+    <row r="253" s="65" customFormat="1"/>
+    <row r="254" s="65" customFormat="1"/>
+    <row r="255" s="65" customFormat="1"/>
+    <row r="256" s="65" customFormat="1"/>
+    <row r="257" s="65" customFormat="1"/>
+    <row r="258" s="65" customFormat="1"/>
+    <row r="259" s="65" customFormat="1"/>
+    <row r="260" s="65" customFormat="1"/>
+    <row r="261" s="65" customFormat="1"/>
+    <row r="262" s="65" customFormat="1"/>
+    <row r="263" s="65" customFormat="1"/>
+    <row r="264" s="65" customFormat="1"/>
+    <row r="265" s="65" customFormat="1"/>
+    <row r="266" s="65" customFormat="1"/>
+    <row r="267" s="65" customFormat="1"/>
+    <row r="268" s="65" customFormat="1"/>
+    <row r="269" s="65" customFormat="1"/>
+    <row r="270" s="65" customFormat="1"/>
+    <row r="271" s="65" customFormat="1"/>
+    <row r="272" s="65" customFormat="1"/>
+    <row r="273" s="65" customFormat="1"/>
+    <row r="274" s="65" customFormat="1"/>
+    <row r="275" s="65" customFormat="1"/>
+    <row r="276" s="65" customFormat="1"/>
+    <row r="277" s="65" customFormat="1"/>
+    <row r="278" s="65" customFormat="1"/>
+    <row r="279" s="65" customFormat="1"/>
+    <row r="280" s="65" customFormat="1"/>
+    <row r="281" s="65" customFormat="1"/>
+    <row r="282" s="65" customFormat="1"/>
+    <row r="283" s="65" customFormat="1"/>
+    <row r="284" s="65" customFormat="1"/>
+    <row r="285" s="65" customFormat="1"/>
+    <row r="286" s="65" customFormat="1"/>
+    <row r="287" s="65" customFormat="1"/>
+    <row r="288" s="65" customFormat="1"/>
+    <row r="289" s="65" customFormat="1"/>
+    <row r="290" s="65" customFormat="1"/>
+    <row r="291" s="65" customFormat="1"/>
+    <row r="292" s="65" customFormat="1"/>
+    <row r="293" s="65" customFormat="1"/>
+    <row r="294" s="65" customFormat="1"/>
+    <row r="295" s="65" customFormat="1"/>
+    <row r="296" s="65" customFormat="1"/>
+    <row r="297" s="65" customFormat="1"/>
+    <row r="298" s="65" customFormat="1"/>
+    <row r="299" s="65" customFormat="1"/>
+    <row r="300" s="65" customFormat="1"/>
+    <row r="301" s="65" customFormat="1"/>
+    <row r="302" s="65" customFormat="1"/>
+    <row r="303" s="65" customFormat="1"/>
+    <row r="304" s="65" customFormat="1"/>
+    <row r="305" s="65" customFormat="1"/>
+    <row r="306" s="65" customFormat="1"/>
+    <row r="307" s="65" customFormat="1"/>
+    <row r="308" s="65" customFormat="1"/>
+    <row r="309" s="65" customFormat="1"/>
+    <row r="310" s="65" customFormat="1"/>
+    <row r="311" s="65" customFormat="1"/>
+    <row r="312" s="65" customFormat="1"/>
+    <row r="313" s="65" customFormat="1"/>
+    <row r="314" s="65" customFormat="1"/>
+    <row r="315" s="65" customFormat="1"/>
+    <row r="316" s="65" customFormat="1"/>
+    <row r="317" s="65" customFormat="1"/>
+    <row r="318" s="65" customFormat="1"/>
+    <row r="319" s="65" customFormat="1"/>
+    <row r="320" s="65" customFormat="1"/>
+    <row r="321" s="65" customFormat="1"/>
+    <row r="322" s="65" customFormat="1"/>
+    <row r="323" s="65" customFormat="1"/>
+    <row r="324" s="65" customFormat="1"/>
+    <row r="325" s="65" customFormat="1"/>
+    <row r="326" s="65" customFormat="1"/>
+    <row r="327" s="65" customFormat="1"/>
+    <row r="328" s="65" customFormat="1"/>
+    <row r="329" s="65" customFormat="1"/>
+    <row r="330" s="65" customFormat="1"/>
+    <row r="331" s="65" customFormat="1"/>
+    <row r="332" s="65" customFormat="1"/>
+    <row r="333" s="65" customFormat="1"/>
+    <row r="334" s="65" customFormat="1"/>
+    <row r="335" s="65" customFormat="1"/>
+    <row r="336" s="65" customFormat="1"/>
+    <row r="337" s="65" customFormat="1"/>
+    <row r="338" s="65" customFormat="1"/>
+    <row r="339" s="65" customFormat="1"/>
+    <row r="340" s="65" customFormat="1"/>
+    <row r="341" s="65" customFormat="1"/>
+    <row r="342" s="65" customFormat="1"/>
+    <row r="343" s="65" customFormat="1"/>
+    <row r="344" s="65" customFormat="1"/>
+    <row r="345" s="65" customFormat="1"/>
+    <row r="346" s="65" customFormat="1"/>
+    <row r="347" s="65" customFormat="1"/>
+    <row r="348" s="65" customFormat="1"/>
+    <row r="349" s="65" customFormat="1"/>
+    <row r="350" s="65" customFormat="1"/>
+    <row r="351" s="65" customFormat="1"/>
+    <row r="352" s="65" customFormat="1"/>
+    <row r="353" s="65" customFormat="1"/>
+    <row r="354" s="65" customFormat="1"/>
+    <row r="355" s="65" customFormat="1"/>
+    <row r="356" s="65" customFormat="1"/>
+    <row r="357" s="65" customFormat="1"/>
+    <row r="358" s="65" customFormat="1"/>
+    <row r="359" s="65" customFormat="1"/>
+    <row r="360" s="65" customFormat="1"/>
+    <row r="361" s="65" customFormat="1"/>
+    <row r="362" s="65" customFormat="1"/>
+    <row r="363" s="65" customFormat="1"/>
+    <row r="364" s="65" customFormat="1"/>
+    <row r="365" s="65" customFormat="1"/>
+    <row r="366" s="65" customFormat="1"/>
+    <row r="367" s="65" customFormat="1"/>
+    <row r="368" s="65" customFormat="1"/>
+    <row r="369" s="65" customFormat="1"/>
+    <row r="370" s="65" customFormat="1"/>
+    <row r="371" s="65" customFormat="1"/>
+    <row r="372" s="65" customFormat="1"/>
+    <row r="373" s="65" customFormat="1"/>
+    <row r="374" s="65" customFormat="1"/>
+    <row r="375" s="65" customFormat="1"/>
+    <row r="376" s="65" customFormat="1"/>
+    <row r="377" s="65" customFormat="1"/>
+    <row r="378" s="65" customFormat="1"/>
+    <row r="379" s="65" customFormat="1"/>
+    <row r="380" s="65" customFormat="1"/>
+    <row r="381" s="65" customFormat="1"/>
+    <row r="382" s="65" customFormat="1"/>
+    <row r="383" s="65" customFormat="1"/>
+    <row r="384" s="65" customFormat="1"/>
+    <row r="385" s="65" customFormat="1"/>
+    <row r="386" s="65" customFormat="1"/>
+    <row r="387" s="65" customFormat="1"/>
+    <row r="388" s="65" customFormat="1"/>
+    <row r="389" s="65" customFormat="1"/>
+    <row r="390" s="65" customFormat="1"/>
+    <row r="391" s="65" customFormat="1"/>
+    <row r="392" s="65" customFormat="1"/>
+    <row r="393" s="65" customFormat="1"/>
+    <row r="394" s="65" customFormat="1"/>
+    <row r="395" s="65" customFormat="1"/>
+    <row r="396" s="65" customFormat="1"/>
+    <row r="397" s="65" customFormat="1"/>
+    <row r="398" s="65" customFormat="1"/>
+    <row r="399" s="65" customFormat="1"/>
+    <row r="400" s="65" customFormat="1"/>
+    <row r="401" s="65" customFormat="1"/>
+    <row r="402" s="65" customFormat="1"/>
+    <row r="403" s="65" customFormat="1"/>
+    <row r="404" s="65" customFormat="1"/>
+    <row r="405" s="65" customFormat="1"/>
+    <row r="406" s="65" customFormat="1"/>
+    <row r="407" s="65" customFormat="1"/>
+    <row r="408" s="65" customFormat="1"/>
+    <row r="409" s="65" customFormat="1"/>
+    <row r="410" s="65" customFormat="1"/>
+    <row r="411" s="65" customFormat="1"/>
+    <row r="412" s="65" customFormat="1"/>
+    <row r="413" s="65" customFormat="1"/>
+    <row r="414" s="65" customFormat="1"/>
+    <row r="415" s="65" customFormat="1"/>
+    <row r="416" s="65" customFormat="1"/>
+    <row r="417" s="65" customFormat="1"/>
+    <row r="418" s="65" customFormat="1"/>
+    <row r="419" s="65" customFormat="1"/>
+    <row r="420" s="65" customFormat="1"/>
+    <row r="421" s="65" customFormat="1"/>
+    <row r="422" s="65" customFormat="1"/>
+    <row r="423" s="65" customFormat="1"/>
+    <row r="424" s="65" customFormat="1"/>
+    <row r="425" s="65" customFormat="1"/>
+    <row r="426" s="65" customFormat="1"/>
+    <row r="427" s="65" customFormat="1"/>
+    <row r="428" s="65" customFormat="1"/>
+    <row r="429" s="65" customFormat="1"/>
+    <row r="430" s="65" customFormat="1"/>
+    <row r="431" s="65" customFormat="1"/>
+    <row r="432" s="65" customFormat="1"/>
+    <row r="433" s="65" customFormat="1"/>
+    <row r="434" s="65" customFormat="1"/>
+    <row r="435" s="65" customFormat="1"/>
+    <row r="436" s="65" customFormat="1"/>
+    <row r="437" s="65" customFormat="1"/>
+    <row r="438" s="65" customFormat="1"/>
+    <row r="439" s="65" customFormat="1"/>
+    <row r="440" s="65" customFormat="1"/>
+    <row r="441" s="65" customFormat="1"/>
+    <row r="442" s="65" customFormat="1"/>
+    <row r="443" s="65" customFormat="1"/>
+    <row r="444" s="65" customFormat="1"/>
+    <row r="445" s="65" customFormat="1"/>
+    <row r="446" s="65" customFormat="1"/>
+    <row r="447" s="65" customFormat="1"/>
+    <row r="448" s="65" customFormat="1"/>
+    <row r="449" s="65" customFormat="1"/>
+    <row r="450" s="65" customFormat="1"/>
+    <row r="451" s="65" customFormat="1"/>
+    <row r="452" s="65" customFormat="1"/>
+    <row r="453" s="65" customFormat="1"/>
+    <row r="454" s="65" customFormat="1"/>
+    <row r="455" s="65" customFormat="1"/>
+    <row r="456" s="65" customFormat="1"/>
+    <row r="457" s="65" customFormat="1"/>
+    <row r="458" s="65" customFormat="1"/>
+    <row r="459" s="65" customFormat="1"/>
+    <row r="460" s="65" customFormat="1"/>
+    <row r="461" s="65" customFormat="1"/>
+    <row r="462" s="65" customFormat="1"/>
+    <row r="463" s="65" customFormat="1"/>
+    <row r="464" s="65" customFormat="1"/>
+    <row r="465" s="65" customFormat="1"/>
+    <row r="466" s="65" customFormat="1"/>
+    <row r="467" s="65" customFormat="1"/>
+    <row r="468" s="65" customFormat="1"/>
+    <row r="469" s="65" customFormat="1"/>
+    <row r="470" s="65" customFormat="1"/>
+    <row r="471" s="65" customFormat="1"/>
+    <row r="472" s="65" customFormat="1"/>
+    <row r="473" s="65" customFormat="1"/>
+    <row r="474" s="65" customFormat="1"/>
+    <row r="475" s="65" customFormat="1"/>
+    <row r="476" s="65" customFormat="1"/>
+    <row r="477" s="65" customFormat="1"/>
+    <row r="478" s="65" customFormat="1"/>
+    <row r="479" s="65" customFormat="1"/>
+    <row r="480" s="65" customFormat="1"/>
+    <row r="481" s="65" customFormat="1"/>
+    <row r="482" s="65" customFormat="1"/>
+    <row r="483" s="65" customFormat="1"/>
+    <row r="484" s="65" customFormat="1"/>
+    <row r="485" s="65" customFormat="1"/>
+    <row r="486" s="65" customFormat="1"/>
+    <row r="487" s="65" customFormat="1"/>
+    <row r="488" s="65" customFormat="1"/>
+    <row r="489" s="65" customFormat="1"/>
+    <row r="490" s="65" customFormat="1"/>
+    <row r="491" s="65" customFormat="1"/>
+    <row r="492" s="65" customFormat="1"/>
+    <row r="493" s="65" customFormat="1"/>
+    <row r="494" s="65" customFormat="1"/>
+    <row r="495" s="65" customFormat="1"/>
+    <row r="496" s="65" customFormat="1"/>
+    <row r="497" s="65" customFormat="1"/>
+    <row r="498" s="65" customFormat="1"/>
+    <row r="499" s="65" customFormat="1"/>
+    <row r="500" s="65" customFormat="1"/>
+    <row r="501" s="65" customFormat="1"/>
+    <row r="502" s="65" customFormat="1"/>
+    <row r="503" s="65" customFormat="1"/>
+    <row r="504" s="65" customFormat="1"/>
+    <row r="505" s="65" customFormat="1"/>
+    <row r="506" s="65" customFormat="1"/>
+    <row r="507" s="65" customFormat="1"/>
+    <row r="508" s="65" customFormat="1"/>
+    <row r="509" s="65" customFormat="1"/>
+    <row r="510" s="65" customFormat="1"/>
+    <row r="511" s="65" customFormat="1"/>
+    <row r="512" s="65" customFormat="1"/>
+    <row r="513" s="65" customFormat="1"/>
+    <row r="514" s="65" customFormat="1"/>
+    <row r="515" s="65" customFormat="1"/>
+    <row r="516" s="65" customFormat="1"/>
+    <row r="517" s="65" customFormat="1"/>
+    <row r="518" s="65" customFormat="1"/>
+    <row r="519" s="65" customFormat="1"/>
+    <row r="520" s="65" customFormat="1"/>
+    <row r="521" s="65" customFormat="1"/>
+    <row r="522" s="65" customFormat="1"/>
+    <row r="523" s="65" customFormat="1"/>
+    <row r="524" s="65" customFormat="1"/>
+    <row r="525" s="65" customFormat="1"/>
+    <row r="526" s="65" customFormat="1"/>
+    <row r="527" s="65" customFormat="1"/>
+    <row r="528" s="65" customFormat="1"/>
+    <row r="529" s="65" customFormat="1"/>
+    <row r="530" s="65" customFormat="1"/>
+    <row r="531" s="65" customFormat="1"/>
+    <row r="532" s="65" customFormat="1"/>
+    <row r="533" s="65" customFormat="1"/>
+    <row r="534" s="65" customFormat="1"/>
+    <row r="535" s="65" customFormat="1"/>
+    <row r="536" s="65" customFormat="1"/>
+    <row r="537" s="65" customFormat="1"/>
+    <row r="538" s="65" customFormat="1"/>
+    <row r="539" s="65" customFormat="1"/>
+    <row r="540" s="65" customFormat="1"/>
+    <row r="541" s="65" customFormat="1"/>
+    <row r="542" s="65" customFormat="1"/>
+    <row r="543" s="65" customFormat="1"/>
+    <row r="544" s="65" customFormat="1"/>
+    <row r="545" s="65" customFormat="1"/>
+    <row r="546" s="65" customFormat="1"/>
+    <row r="547" s="65" customFormat="1"/>
+    <row r="548" s="65" customFormat="1"/>
+    <row r="549" s="65" customFormat="1"/>
+    <row r="550" s="65" customFormat="1"/>
+    <row r="551" s="65" customFormat="1"/>
+    <row r="552" s="65" customFormat="1"/>
+    <row r="553" s="65" customFormat="1"/>
+    <row r="554" s="65" customFormat="1"/>
+    <row r="555" s="65" customFormat="1"/>
+    <row r="556" s="65" customFormat="1"/>
+    <row r="557" s="65" customFormat="1"/>
+    <row r="558" s="65" customFormat="1"/>
+    <row r="559" s="65" customFormat="1"/>
+    <row r="560" s="65" customFormat="1"/>
+    <row r="561" s="65" customFormat="1"/>
+    <row r="562" s="65" customFormat="1"/>
+    <row r="563" s="65" customFormat="1"/>
+    <row r="564" s="65" customFormat="1"/>
+    <row r="565" s="65" customFormat="1"/>
+    <row r="566" s="65" customFormat="1"/>
+    <row r="567" s="65" customFormat="1"/>
+    <row r="568" s="65" customFormat="1"/>
+    <row r="569" s="65" customFormat="1"/>
+    <row r="570" s="65" customFormat="1"/>
+    <row r="571" s="65" customFormat="1"/>
+    <row r="572" s="65" customFormat="1"/>
+    <row r="573" s="65" customFormat="1"/>
+    <row r="574" s="65" customFormat="1"/>
+    <row r="575" s="65" customFormat="1"/>
+    <row r="576" s="65" customFormat="1"/>
+    <row r="577" s="65" customFormat="1"/>
+    <row r="578" s="65" customFormat="1"/>
+    <row r="579" s="65" customFormat="1"/>
+    <row r="580" s="65" customFormat="1"/>
+    <row r="581" s="65" customFormat="1"/>
+    <row r="582" s="65" customFormat="1"/>
+    <row r="583" s="65" customFormat="1"/>
+    <row r="584" s="65" customFormat="1"/>
+    <row r="585" s="65" customFormat="1"/>
+    <row r="586" s="65" customFormat="1"/>
+    <row r="587" s="65" customFormat="1"/>
+    <row r="588" s="65" customFormat="1"/>
+    <row r="589" s="65" customFormat="1"/>
+    <row r="590" s="65" customFormat="1"/>
+    <row r="591" s="65" customFormat="1"/>
+    <row r="592" s="65" customFormat="1"/>
+    <row r="593" s="65" customFormat="1"/>
+    <row r="594" s="65" customFormat="1"/>
+    <row r="595" s="65" customFormat="1"/>
+    <row r="596" s="65" customFormat="1"/>
+    <row r="597" s="65" customFormat="1"/>
+    <row r="598" s="65" customFormat="1"/>
+    <row r="599" s="65" customFormat="1"/>
+    <row r="600" s="65" customFormat="1"/>
+    <row r="601" s="65" customFormat="1"/>
+    <row r="602" s="65" customFormat="1"/>
+    <row r="603" s="65" customFormat="1"/>
+    <row r="604" s="65" customFormat="1"/>
+    <row r="605" s="65" customFormat="1"/>
+    <row r="606" s="65" customFormat="1"/>
+    <row r="607" s="65" customFormat="1"/>
+    <row r="608" s="65" customFormat="1"/>
+    <row r="609" s="65" customFormat="1"/>
+    <row r="610" s="65" customFormat="1"/>
+    <row r="611" s="65" customFormat="1"/>
+    <row r="612" s="65" customFormat="1"/>
+    <row r="613" s="65" customFormat="1"/>
+    <row r="614" s="65" customFormat="1"/>
+    <row r="615" s="65" customFormat="1"/>
+    <row r="616" s="65" customFormat="1"/>
+    <row r="617" s="65" customFormat="1"/>
+    <row r="618" s="65" customFormat="1"/>
+    <row r="619" s="65" customFormat="1"/>
+    <row r="620" s="65" customFormat="1"/>
+    <row r="621" s="65" customFormat="1"/>
+    <row r="622" s="65" customFormat="1"/>
+    <row r="623" s="65" customFormat="1"/>
+    <row r="624" s="65" customFormat="1"/>
+    <row r="625" s="65" customFormat="1"/>
+    <row r="626" s="65" customFormat="1"/>
+    <row r="627" s="65" customFormat="1"/>
+    <row r="628" s="65" customFormat="1"/>
+    <row r="629" s="65" customFormat="1"/>
+    <row r="630" s="65" customFormat="1"/>
+    <row r="631" s="65" customFormat="1"/>
+    <row r="632" s="65" customFormat="1"/>
+    <row r="633" s="65" customFormat="1"/>
+    <row r="634" s="65" customFormat="1"/>
+    <row r="635" s="65" customFormat="1"/>
+    <row r="636" s="65" customFormat="1"/>
+    <row r="637" s="65" customFormat="1"/>
+    <row r="638" s="65" customFormat="1"/>
+    <row r="639" s="65" customFormat="1"/>
+    <row r="640" s="65" customFormat="1"/>
+    <row r="641" s="65" customFormat="1"/>
+    <row r="642" s="65" customFormat="1"/>
+    <row r="643" s="65" customFormat="1"/>
+    <row r="644" s="65" customFormat="1"/>
+    <row r="645" s="65" customFormat="1"/>
+    <row r="646" s="65" customFormat="1"/>
+    <row r="647" s="65" customFormat="1"/>
+    <row r="648" s="65" customFormat="1"/>
+    <row r="649" s="65" customFormat="1"/>
+    <row r="650" s="65" customFormat="1"/>
+    <row r="651" s="65" customFormat="1"/>
+    <row r="652" s="65" customFormat="1"/>
+    <row r="653" s="65" customFormat="1"/>
+    <row r="654" s="65" customFormat="1"/>
+    <row r="655" s="65" customFormat="1"/>
+    <row r="656" s="65" customFormat="1"/>
+    <row r="657" s="65" customFormat="1"/>
+    <row r="658" s="65" customFormat="1"/>
+    <row r="659" s="65" customFormat="1"/>
+    <row r="660" s="65" customFormat="1"/>
+    <row r="661" s="65" customFormat="1"/>
+    <row r="662" s="65" customFormat="1"/>
+    <row r="663" s="65" customFormat="1"/>
+    <row r="664" s="65" customFormat="1"/>
+    <row r="665" s="65" customFormat="1"/>
+    <row r="666" s="65" customFormat="1"/>
+    <row r="667" s="65" customFormat="1"/>
+    <row r="668" s="65" customFormat="1"/>
+    <row r="669" s="65" customFormat="1"/>
+    <row r="670" s="65" customFormat="1"/>
+    <row r="671" s="65" customFormat="1"/>
+    <row r="672" s="65" customFormat="1"/>
+    <row r="673" s="65" customFormat="1"/>
+    <row r="674" s="65" customFormat="1"/>
+    <row r="675" s="65" customFormat="1"/>
+    <row r="676" s="65" customFormat="1"/>
+    <row r="677" s="65" customFormat="1"/>
+    <row r="678" s="65" customFormat="1"/>
+    <row r="679" s="65" customFormat="1"/>
+    <row r="680" s="65" customFormat="1"/>
+    <row r="681" s="65" customFormat="1"/>
+    <row r="682" s="65" customFormat="1"/>
+    <row r="683" s="65" customFormat="1"/>
+    <row r="684" s="65" customFormat="1"/>
+    <row r="685" s="65" customFormat="1"/>
+    <row r="686" s="65" customFormat="1"/>
+    <row r="687" s="65" customFormat="1"/>
+    <row r="688" s="65" customFormat="1"/>
+    <row r="689" s="65" customFormat="1"/>
+    <row r="690" s="65" customFormat="1"/>
+    <row r="691" s="65" customFormat="1"/>
+    <row r="692" s="65" customFormat="1"/>
+    <row r="693" s="65" customFormat="1"/>
+    <row r="694" s="65" customFormat="1"/>
+    <row r="695" s="65" customFormat="1"/>
+    <row r="696" s="65" customFormat="1"/>
+    <row r="697" s="65" customFormat="1"/>
+    <row r="698" s="65" customFormat="1"/>
+    <row r="699" s="65" customFormat="1"/>
+    <row r="700" s="65" customFormat="1"/>
+    <row r="701" s="65" customFormat="1"/>
+    <row r="702" s="65" customFormat="1"/>
+    <row r="703" s="65" customFormat="1"/>
+    <row r="704" s="65" customFormat="1"/>
+    <row r="705" s="65" customFormat="1"/>
+    <row r="706" s="65" customFormat="1"/>
+    <row r="707" s="65" customFormat="1"/>
+    <row r="708" s="65" customFormat="1"/>
+    <row r="709" s="65" customFormat="1"/>
+    <row r="710" s="65" customFormat="1"/>
+    <row r="711" s="65" customFormat="1"/>
+    <row r="712" s="65" customFormat="1"/>
+    <row r="713" s="65" customFormat="1"/>
+    <row r="714" s="65" customFormat="1"/>
+    <row r="715" s="65" customFormat="1"/>
+    <row r="716" s="65" customFormat="1"/>
+    <row r="717" s="65" customFormat="1"/>
+    <row r="718" s="65" customFormat="1"/>
+    <row r="719" s="65" customFormat="1"/>
+    <row r="720" s="65" customFormat="1"/>
+    <row r="721" s="65" customFormat="1"/>
+    <row r="722" s="65" customFormat="1"/>
+    <row r="723" s="65" customFormat="1"/>
+    <row r="724" s="65" customFormat="1"/>
+    <row r="725" s="65" customFormat="1"/>
+    <row r="726" s="65" customFormat="1"/>
+    <row r="727" s="65" customFormat="1"/>
+    <row r="728" s="65" customFormat="1"/>
+    <row r="729" s="65" customFormat="1"/>
+    <row r="730" s="65" customFormat="1"/>
+    <row r="731" s="65" customFormat="1"/>
+    <row r="732" s="65" customFormat="1"/>
+    <row r="733" s="65" customFormat="1"/>
+    <row r="734" s="65" customFormat="1"/>
+    <row r="735" s="65" customFormat="1"/>
+    <row r="736" s="65" customFormat="1"/>
+    <row r="737" s="65" customFormat="1"/>
+    <row r="738" s="65" customFormat="1"/>
+    <row r="739" s="65" customFormat="1"/>
+    <row r="740" s="65" customFormat="1"/>
+    <row r="741" s="65" customFormat="1"/>
+    <row r="742" s="65" customFormat="1"/>
+    <row r="743" s="65" customFormat="1"/>
+    <row r="744" s="65" customFormat="1"/>
+    <row r="745" s="65" customFormat="1"/>
+    <row r="746" s="65" customFormat="1"/>
+    <row r="747" s="65" customFormat="1"/>
+    <row r="748" s="65" customFormat="1"/>
+    <row r="749" s="65" customFormat="1"/>
+    <row r="750" s="65" customFormat="1"/>
+    <row r="751" s="65" customFormat="1"/>
+    <row r="752" s="65" customFormat="1"/>
+    <row r="753" s="65" customFormat="1"/>
+    <row r="754" s="65" customFormat="1"/>
+    <row r="755" s="65" customFormat="1"/>
+    <row r="756" s="65" customFormat="1"/>
+    <row r="757" s="65" customFormat="1"/>
+    <row r="758" s="65" customFormat="1"/>
+    <row r="759" s="65" customFormat="1"/>
+    <row r="760" s="65" customFormat="1"/>
+    <row r="761" s="65" customFormat="1"/>
+    <row r="762" s="65" customFormat="1"/>
+    <row r="763" s="65" customFormat="1"/>
+    <row r="764" s="65" customFormat="1"/>
+    <row r="765" s="65" customFormat="1"/>
+    <row r="766" s="65" customFormat="1"/>
+    <row r="767" s="65" customFormat="1"/>
+    <row r="768" s="65" customFormat="1"/>
+    <row r="769" s="65" customFormat="1"/>
+    <row r="770" s="65" customFormat="1"/>
+    <row r="771" s="65" customFormat="1"/>
+    <row r="772" s="65" customFormat="1"/>
+    <row r="773" s="65" customFormat="1"/>
+    <row r="774" s="65" customFormat="1"/>
+    <row r="775" s="65" customFormat="1"/>
+    <row r="776" s="65" customFormat="1"/>
+    <row r="777" s="65" customFormat="1"/>
+    <row r="778" s="65" customFormat="1"/>
+    <row r="779" s="65" customFormat="1"/>
+    <row r="780" s="65" customFormat="1"/>
+    <row r="781" s="65" customFormat="1"/>
+    <row r="782" s="65" customFormat="1"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="ARtKEHjGwCyaq6uaIYzIr/GfEB8D0HCrMM8aQQekrEnrQulrEZhkDfKXW/T/JfXAKde6V4A+oMNAHiQi65VRKw==" saltValue="PLVyGEC2PFpWgeh9+98m5g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="26">
@@ -11832,165 +11106,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1">
-      <c r="A1" s="355" t="s">
+      <c r="A1" s="363" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="363"/>
+      <c r="C1" s="363"/>
+      <c r="D1" s="363"/>
+      <c r="E1" s="363"/>
+      <c r="G1" s="364" t="s">
+        <v>178</v>
+      </c>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1">
+      <c r="A2" s="376" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="373" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="374"/>
+      <c r="D2" s="375" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="373"/>
+      <c r="G2" s="366" t="s">
+        <v>180</v>
+      </c>
+      <c r="H2" s="367"/>
+      <c r="I2" s="114" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18" customHeight="1">
+      <c r="A3" s="376"/>
+      <c r="B3" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="368" t="s">
+        <v>182</v>
+      </c>
+      <c r="H3" s="369"/>
+      <c r="I3" s="114" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="18" customHeight="1">
+      <c r="A4" s="121" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="370" t="s">
+        <v>181</v>
+      </c>
+      <c r="H4" s="371"/>
+      <c r="I4" s="114" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18" customHeight="1">
+      <c r="A5" s="122" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="355"/>
-      <c r="C1" s="355"/>
-      <c r="D1" s="355"/>
-      <c r="E1" s="355"/>
-      <c r="G1" s="356" t="s">
-        <v>214</v>
-      </c>
-      <c r="H1" s="357"/>
-      <c r="I1" s="357"/>
-    </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1">
-      <c r="A2" s="368" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="365" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="366"/>
-      <c r="D2" s="367" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="365"/>
-      <c r="G2" s="358" t="s">
-        <v>216</v>
-      </c>
-      <c r="H2" s="359"/>
-      <c r="I2" s="123" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1">
-      <c r="A3" s="368"/>
-      <c r="B3" s="51" t="s">
+      <c r="B5" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18" customHeight="1">
+      <c r="A6" s="115" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18" customHeight="1">
+      <c r="A7" s="123" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="52" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C7" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="360" t="s">
-        <v>218</v>
-      </c>
-      <c r="H3" s="361"/>
-      <c r="I3" s="123" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1">
-      <c r="A4" s="130" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="52" t="s">
+      <c r="D7" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="363" t="s">
+        <v>189</v>
+      </c>
+      <c r="H7" s="363"/>
+      <c r="I7" s="363"/>
+    </row>
+    <row r="8" spans="1:9" ht="18" customHeight="1">
+      <c r="A8" s="124" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C8" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D8" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E8" s="52" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="362" t="s">
-        <v>217</v>
-      </c>
-      <c r="H4" s="363"/>
-      <c r="I4" s="123" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="18" customHeight="1">
-      <c r="A5" s="131" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="52" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="18" customHeight="1">
-      <c r="A6" s="124" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>141</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="52" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18" customHeight="1">
-      <c r="A7" s="132" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="355" t="s">
-        <v>231</v>
-      </c>
-      <c r="H7" s="355"/>
-      <c r="I7" s="355"/>
-    </row>
-    <row r="8" spans="1:9" ht="18" customHeight="1">
-      <c r="A8" s="133" t="s">
-        <v>120</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="G8" s="129" t="s">
-        <v>232</v>
-      </c>
-      <c r="H8" s="129" t="s">
-        <v>233</v>
-      </c>
-      <c r="I8" s="129" t="s">
-        <v>234</v>
+      <c r="G8" s="120" t="s">
+        <v>190</v>
+      </c>
+      <c r="H8" s="120" t="s">
+        <v>191</v>
+      </c>
+      <c r="I8" s="120" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1">
@@ -11999,14 +11273,14 @@
       <c r="C9" s="57"/>
       <c r="D9" s="57"/>
       <c r="E9" s="57"/>
-      <c r="G9" s="123" t="s">
-        <v>169</v>
-      </c>
-      <c r="H9" s="128" t="s">
-        <v>235</v>
-      </c>
-      <c r="I9" s="128" t="s">
-        <v>242</v>
+      <c r="G9" s="114" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9" s="119" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" s="119" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1">
@@ -12015,241 +11289,241 @@
       <c r="C10" s="59"/>
       <c r="D10" s="59"/>
       <c r="E10" s="59"/>
-      <c r="G10" s="123" t="s">
-        <v>170</v>
-      </c>
-      <c r="H10" s="128" t="s">
-        <v>236</v>
-      </c>
-      <c r="I10" s="128" t="s">
-        <v>243</v>
+      <c r="G10" s="114" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="119" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10" s="119" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1">
-      <c r="A11" s="355" t="s">
+      <c r="A11" s="363" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="372"/>
+      <c r="C11" s="372"/>
+      <c r="D11" s="372"/>
+      <c r="E11" s="372"/>
+      <c r="G11" s="114" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" s="119" t="s">
+        <v>195</v>
+      </c>
+      <c r="I11" s="119" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18" customHeight="1">
+      <c r="A12" s="376" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="373" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="374"/>
+      <c r="D12" s="375" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="373"/>
+      <c r="G12" s="114" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="119" t="s">
+        <v>196</v>
+      </c>
+      <c r="I12" s="119" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18" customHeight="1">
+      <c r="A13" s="376"/>
+      <c r="B13" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="114" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" s="119" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="119" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="18" customHeight="1">
+      <c r="A14" s="121" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="114" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="119" t="s">
+        <v>198</v>
+      </c>
+      <c r="I14" s="119" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="18" customHeight="1">
+      <c r="A15" s="122" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" s="114" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="119" t="s">
+        <v>199</v>
+      </c>
+      <c r="I15" s="119" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="18" customHeight="1">
+      <c r="A16" s="115" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="364"/>
-      <c r="C11" s="364"/>
-      <c r="D11" s="364"/>
-      <c r="E11" s="364"/>
-      <c r="G11" s="123" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" s="128" t="s">
-        <v>237</v>
-      </c>
-      <c r="I11" s="128" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18" customHeight="1">
-      <c r="A12" s="368" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="365" t="s">
+      <c r="B16" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1">
+      <c r="A17" s="123" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="18" customHeight="1">
+      <c r="A18" s="124" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="18" customHeight="1">
+      <c r="A21" s="363" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" s="363"/>
+      <c r="C21" s="363"/>
+      <c r="D21" s="363"/>
+    </row>
+    <row r="22" spans="1:5" ht="18" customHeight="1">
+      <c r="A22" s="125" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="377" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="377"/>
+      <c r="D22" s="377"/>
+    </row>
+    <row r="23" spans="1:5" ht="18" customHeight="1">
+      <c r="A23" s="125" t="s">
+        <v>208</v>
+      </c>
+      <c r="B23" s="126" t="s">
+        <v>209</v>
+      </c>
+      <c r="C23" s="125" t="s">
+        <v>210</v>
+      </c>
+      <c r="D23" s="125" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18" customHeight="1">
+      <c r="A24" s="125" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="366"/>
-      <c r="D12" s="367" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="365"/>
-      <c r="G12" s="123" t="s">
-        <v>172</v>
-      </c>
-      <c r="H12" s="128" t="s">
-        <v>238</v>
-      </c>
-      <c r="I12" s="128" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="18" customHeight="1">
-      <c r="A13" s="368"/>
-      <c r="B13" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="G13" s="123" t="s">
-        <v>173</v>
-      </c>
-      <c r="H13" s="128" t="s">
-        <v>239</v>
-      </c>
-      <c r="I13" s="128" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="18" customHeight="1">
-      <c r="A14" s="130" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="61" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" s="123" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" s="128" t="s">
-        <v>240</v>
-      </c>
-      <c r="I14" s="128" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="18" customHeight="1">
-      <c r="A15" s="131" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="E15" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="123" t="s">
-        <v>175</v>
-      </c>
-      <c r="H15" s="128" t="s">
-        <v>241</v>
-      </c>
-      <c r="I15" s="128" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="18" customHeight="1">
-      <c r="A16" s="124" t="s">
-        <v>118</v>
-      </c>
-      <c r="B16" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16" s="52" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1">
-      <c r="A17" s="132" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17" s="52" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1">
-      <c r="A18" s="133" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="61" t="s">
-        <v>160</v>
-      </c>
-      <c r="E18" s="52" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1">
-      <c r="A21" s="355" t="s">
-        <v>260</v>
-      </c>
-      <c r="B21" s="355"/>
-      <c r="C21" s="355"/>
-      <c r="D21" s="355"/>
-    </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1">
-      <c r="A22" s="134" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="369" t="s">
-        <v>249</v>
-      </c>
-      <c r="C22" s="369"/>
-      <c r="D22" s="369"/>
-    </row>
-    <row r="23" spans="1:5" ht="18" customHeight="1">
-      <c r="A23" s="134" t="s">
-        <v>250</v>
-      </c>
-      <c r="B23" s="135" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="134" t="s">
-        <v>252</v>
-      </c>
-      <c r="D23" s="134" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="18" customHeight="1">
-      <c r="A24" s="134" t="s">
-        <v>132</v>
-      </c>
-      <c r="B24" s="136" t="s">
-        <v>254</v>
-      </c>
-      <c r="C24" s="136" t="s">
-        <v>255</v>
-      </c>
-      <c r="D24" s="136" t="s">
-        <v>256</v>
+      <c r="B24" s="127" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="127" t="s">
+        <v>213</v>
+      </c>
+      <c r="D24" s="127" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="134" t="s">
-        <v>138</v>
-      </c>
-      <c r="B25" s="136" t="s">
-        <v>257</v>
-      </c>
-      <c r="C25" s="136" t="s">
-        <v>258</v>
-      </c>
-      <c r="D25" s="136" t="s">
-        <v>259</v>
+      <c r="A25" s="125" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="127" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="127" t="s">
+        <v>216</v>
+      </c>
+      <c r="D25" s="127" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -12275,289 +11549,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D5CA10-328B-4EAE-A42B-2B0FD827EEA2}">
-  <sheetPr codeName="Foglio5"/>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="15.3125" defaultRowHeight="19.899999999999999" customHeight="1"/>
-  <cols>
-    <col min="1" max="12" width="15.625" style="63" customWidth="1"/>
-    <col min="13" max="13" width="15.3125" style="63" customWidth="1"/>
-    <col min="14" max="16384" width="15.3125" style="63"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="373" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1" s="373"/>
-      <c r="C1" s="373"/>
-      <c r="D1" s="373"/>
-      <c r="E1" s="373"/>
-      <c r="F1" s="373"/>
-      <c r="G1" s="373"/>
-      <c r="H1" s="373"/>
-      <c r="I1" s="373"/>
-      <c r="J1" s="373"/>
-      <c r="K1" s="373"/>
-      <c r="L1" s="373"/>
-    </row>
-    <row r="2" spans="1:12" ht="60.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="122"/>
-      <c r="B2" s="375" t="s">
-        <v>227</v>
-      </c>
-      <c r="C2" s="376"/>
-      <c r="D2" s="376"/>
-      <c r="E2" s="376"/>
-      <c r="F2" s="376"/>
-      <c r="G2" s="376"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="374" t="s">
-        <v>230</v>
-      </c>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
-      <c r="L2" s="372"/>
-    </row>
-    <row r="3" spans="1:12" ht="60.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="66" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="378" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="379"/>
-      <c r="D3" s="380"/>
-      <c r="E3" s="381" t="s">
-        <v>228</v>
-      </c>
-      <c r="F3" s="380"/>
-      <c r="G3" s="381" t="s">
-        <v>229</v>
-      </c>
-      <c r="H3" s="380"/>
-      <c r="I3" s="381" t="s">
-        <v>197</v>
-      </c>
-      <c r="J3" s="380"/>
-      <c r="K3" s="381" t="s">
-        <v>187</v>
-      </c>
-      <c r="L3" s="379"/>
-    </row>
-    <row r="4" spans="1:12" ht="60.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="B4" s="382" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="372"/>
-      <c r="D4" s="371"/>
-      <c r="E4" s="370" t="s">
-        <v>189</v>
-      </c>
-      <c r="F4" s="371"/>
-      <c r="G4" s="370" t="s">
-        <v>190</v>
-      </c>
-      <c r="H4" s="371"/>
-      <c r="I4" s="370" t="s">
-        <v>191</v>
-      </c>
-      <c r="J4" s="371"/>
-      <c r="K4" s="370" t="s">
-        <v>192</v>
-      </c>
-      <c r="L4" s="372"/>
-    </row>
-    <row r="5" spans="1:12" ht="60.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="B5" s="64" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="D5" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="70" t="s">
-        <v>168</v>
-      </c>
-      <c r="F5" s="70" t="s">
-        <v>169</v>
-      </c>
-      <c r="G5" s="70" t="s">
-        <v>170</v>
-      </c>
-      <c r="H5" s="70" t="s">
-        <v>171</v>
-      </c>
-      <c r="I5" s="64" t="s">
-        <v>172</v>
-      </c>
-      <c r="J5" s="64" t="s">
-        <v>173</v>
-      </c>
-      <c r="K5" s="64" t="s">
-        <v>174</v>
-      </c>
-      <c r="L5" s="64" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="378" t="s">
-        <v>200</v>
-      </c>
-      <c r="B6" s="383" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="384" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="385"/>
-      <c r="E6" s="388" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" s="389"/>
-      <c r="G6" s="389"/>
-      <c r="H6" s="389"/>
-      <c r="I6" s="390" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="379"/>
-      <c r="K6" s="379"/>
-      <c r="L6" s="391"/>
-    </row>
-    <row r="7" spans="1:12" s="68" customFormat="1" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="379"/>
-      <c r="B7" s="380"/>
-      <c r="C7" s="386"/>
-      <c r="D7" s="387"/>
-      <c r="E7" s="393" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="394"/>
-      <c r="G7" s="395" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="394"/>
-      <c r="I7" s="392"/>
-      <c r="J7" s="379"/>
-      <c r="K7" s="379"/>
-      <c r="L7" s="391"/>
-    </row>
-    <row r="8" spans="1:12" s="69" customFormat="1" ht="60.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="65" t="s">
-        <v>196</v>
-      </c>
-      <c r="B8" s="67" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="396" t="s">
-        <v>181</v>
-      </c>
-      <c r="D8" s="397"/>
-      <c r="E8" s="398" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="399"/>
-      <c r="G8" s="398" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="371"/>
-      <c r="I8" s="398" t="s">
-        <v>184</v>
-      </c>
-      <c r="J8" s="372"/>
-      <c r="K8" s="400"/>
-      <c r="L8" s="372"/>
-    </row>
-    <row r="9" spans="1:12" ht="60.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="402"/>
-      <c r="C9" s="379"/>
-      <c r="D9" s="380"/>
-      <c r="E9" s="403"/>
-      <c r="F9" s="380"/>
-      <c r="G9" s="403"/>
-      <c r="H9" s="380"/>
-      <c r="I9" s="403"/>
-      <c r="J9" s="380"/>
-      <c r="K9" s="403"/>
-      <c r="L9" s="379"/>
-    </row>
-    <row r="10" spans="1:12" ht="60.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" s="401" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="372"/>
-      <c r="D10" s="372"/>
-      <c r="E10" s="372"/>
-      <c r="F10" s="401" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10" s="372"/>
-      <c r="H10" s="372"/>
-      <c r="I10" s="372"/>
-      <c r="J10" s="401" t="s">
-        <v>202</v>
-      </c>
-      <c r="K10" s="372"/>
-      <c r="L10" s="372"/>
-    </row>
-    <row r="11" spans="1:12" ht="19.899999999999999" customHeight="1" thickTop="1"/>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:L7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="B4:D4"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="1.5" bottom="0.25" header="0.25" footer="0.25"/>
-  <pageSetup scale="67" orientation="landscape"/>
-  <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>